--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCAF9C7-4F66-48BD-9003-E5697C602695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDCBACA-BED6-466D-A28C-5B93381C106C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
@@ -178,57 +178,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -569,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -1566,7 +1516,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>10109011</v>
+        <v>1010902</v>
       </c>
       <c r="B91" s="1">
         <v>1010901</v>
@@ -1577,10 +1527,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>10109012</v>
+        <v>1010903</v>
       </c>
       <c r="B92" s="1">
-        <v>10109011</v>
+        <v>1010902</v>
       </c>
       <c r="C92" s="1">
         <v>1</v>
@@ -1588,10 +1538,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>1010902</v>
+        <v>1010904</v>
       </c>
       <c r="B93" s="1">
-        <v>1010901</v>
+        <v>1010903</v>
       </c>
       <c r="C93" s="1">
         <v>1</v>
@@ -1599,10 +1549,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>1010903</v>
-      </c>
-      <c r="B94" s="1">
-        <v>1010902</v>
+        <v>1010905</v>
+      </c>
+      <c r="B94" s="5">
+        <v>1010904</v>
       </c>
       <c r="C94" s="1">
         <v>1</v>
@@ -1610,10 +1560,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>1010904</v>
+        <v>905010202</v>
       </c>
       <c r="B95" s="1">
-        <v>1010903</v>
+        <v>905010101</v>
       </c>
       <c r="C95" s="1">
         <v>1</v>
@@ -1621,10 +1571,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>1010905</v>
-      </c>
-      <c r="B96" s="5">
-        <v>1010904</v>
+        <v>905010302</v>
+      </c>
+      <c r="B96" s="1">
+        <v>905010202</v>
       </c>
       <c r="C96" s="1">
         <v>1</v>
@@ -1632,10 +1582,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>1010906</v>
-      </c>
-      <c r="B97" s="5">
-        <v>1010905</v>
+        <v>905010403</v>
+      </c>
+      <c r="B97" s="1">
+        <v>905010302</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
@@ -1643,10 +1593,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>1010907</v>
-      </c>
-      <c r="B98" s="5">
-        <v>1010906</v>
+        <v>905010503</v>
+      </c>
+      <c r="B98" s="1">
+        <v>905010403</v>
       </c>
       <c r="C98" s="1">
         <v>1</v>
@@ -1654,10 +1604,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>1010908</v>
-      </c>
-      <c r="B99" s="5">
-        <v>1010907</v>
+        <v>905010604</v>
+      </c>
+      <c r="B99" s="1">
+        <v>905010503</v>
       </c>
       <c r="C99" s="1">
         <v>1</v>
@@ -1665,10 +1615,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>1010909</v>
-      </c>
-      <c r="B100" s="5">
-        <v>1010908</v>
+        <v>905010704</v>
+      </c>
+      <c r="B100" s="1">
+        <v>905010604</v>
       </c>
       <c r="C100" s="1">
         <v>1</v>
@@ -1676,10 +1626,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>1010910</v>
-      </c>
-      <c r="B101" s="5">
-        <v>1010909</v>
+        <v>905010805</v>
+      </c>
+      <c r="B101" s="1">
+        <v>905010704</v>
       </c>
       <c r="C101" s="1">
         <v>1</v>
@@ -1687,10 +1637,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>905010202</v>
+        <v>901010202</v>
       </c>
       <c r="B102" s="1">
-        <v>905010101</v>
+        <v>901010101</v>
       </c>
       <c r="C102" s="1">
         <v>1</v>
@@ -1698,10 +1648,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>905010302</v>
+        <v>901010302</v>
       </c>
       <c r="B103" s="1">
-        <v>905010202</v>
+        <v>901010202</v>
       </c>
       <c r="C103" s="1">
         <v>1</v>
@@ -1709,10 +1659,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>905010403</v>
+        <v>901010403</v>
       </c>
       <c r="B104" s="1">
-        <v>905010302</v>
+        <v>901010302</v>
       </c>
       <c r="C104" s="1">
         <v>1</v>
@@ -1720,10 +1670,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>905010503</v>
+        <v>901010503</v>
       </c>
       <c r="B105" s="1">
-        <v>905010403</v>
+        <v>901010403</v>
       </c>
       <c r="C105" s="1">
         <v>1</v>
@@ -1731,10 +1681,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
-        <v>905010604</v>
+        <v>901010604</v>
       </c>
       <c r="B106" s="1">
-        <v>905010503</v>
+        <v>901010503</v>
       </c>
       <c r="C106" s="1">
         <v>1</v>
@@ -1742,10 +1692,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>905010704</v>
+        <v>901010704</v>
       </c>
       <c r="B107" s="1">
-        <v>905010604</v>
+        <v>901010604</v>
       </c>
       <c r="C107" s="1">
         <v>1</v>
@@ -1753,10 +1703,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
-        <v>905010805</v>
+        <v>901010805</v>
       </c>
       <c r="B108" s="1">
-        <v>905010704</v>
+        <v>901010704</v>
       </c>
       <c r="C108" s="1">
         <v>1</v>
@@ -1764,10 +1714,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>901010202</v>
+        <v>902010202</v>
       </c>
       <c r="B109" s="1">
-        <v>901010101</v>
+        <v>902010101</v>
       </c>
       <c r="C109" s="1">
         <v>1</v>
@@ -1775,10 +1725,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>901010302</v>
+        <v>902010302</v>
       </c>
       <c r="B110" s="1">
-        <v>901010202</v>
+        <v>902010202</v>
       </c>
       <c r="C110" s="1">
         <v>1</v>
@@ -1786,10 +1736,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>901010403</v>
+        <v>902010403</v>
       </c>
       <c r="B111" s="1">
-        <v>901010302</v>
+        <v>902010302</v>
       </c>
       <c r="C111" s="1">
         <v>1</v>
@@ -1797,10 +1747,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>901010503</v>
+        <v>902010503</v>
       </c>
       <c r="B112" s="1">
-        <v>901010403</v>
+        <v>902010403</v>
       </c>
       <c r="C112" s="1">
         <v>1</v>
@@ -1808,10 +1758,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>901010604</v>
+        <v>902010604</v>
       </c>
       <c r="B113" s="1">
-        <v>901010503</v>
+        <v>902010503</v>
       </c>
       <c r="C113" s="1">
         <v>1</v>
@@ -1819,10 +1769,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>901010704</v>
+        <v>902010704</v>
       </c>
       <c r="B114" s="1">
-        <v>901010604</v>
+        <v>902010604</v>
       </c>
       <c r="C114" s="1">
         <v>1</v>
@@ -1830,10 +1780,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>901010805</v>
+        <v>902010805</v>
       </c>
       <c r="B115" s="1">
-        <v>901010704</v>
+        <v>902010704</v>
       </c>
       <c r="C115" s="1">
         <v>1</v>
@@ -1841,10 +1791,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>902010202</v>
+        <v>903010202</v>
       </c>
       <c r="B116" s="1">
-        <v>902010101</v>
+        <v>903010101</v>
       </c>
       <c r="C116" s="1">
         <v>1</v>
@@ -1852,10 +1802,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>902010302</v>
+        <v>903010302</v>
       </c>
       <c r="B117" s="1">
-        <v>902010202</v>
+        <v>903010202</v>
       </c>
       <c r="C117" s="1">
         <v>1</v>
@@ -1863,10 +1813,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>902010403</v>
+        <v>903010403</v>
       </c>
       <c r="B118" s="1">
-        <v>902010302</v>
+        <v>903010302</v>
       </c>
       <c r="C118" s="1">
         <v>1</v>
@@ -1874,10 +1824,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>902010503</v>
+        <v>903010503</v>
       </c>
       <c r="B119" s="1">
-        <v>902010403</v>
+        <v>903010403</v>
       </c>
       <c r="C119" s="1">
         <v>1</v>
@@ -1885,10 +1835,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>902010604</v>
+        <v>903010604</v>
       </c>
       <c r="B120" s="1">
-        <v>902010503</v>
+        <v>903010503</v>
       </c>
       <c r="C120" s="1">
         <v>1</v>
@@ -1896,10 +1846,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>902010704</v>
+        <v>903010704</v>
       </c>
       <c r="B121" s="1">
-        <v>902010604</v>
+        <v>903010604</v>
       </c>
       <c r="C121" s="1">
         <v>1</v>
@@ -1907,10 +1857,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>902010805</v>
+        <v>903010805</v>
       </c>
       <c r="B122" s="1">
-        <v>902010704</v>
+        <v>903010704</v>
       </c>
       <c r="C122" s="1">
         <v>1</v>
@@ -1918,10 +1868,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>903010202</v>
+        <v>900010202</v>
       </c>
       <c r="B123" s="1">
-        <v>903010101</v>
+        <v>900010101</v>
       </c>
       <c r="C123" s="1">
         <v>1</v>
@@ -1929,10 +1879,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>903010302</v>
+        <v>900010302</v>
       </c>
       <c r="B124" s="1">
-        <v>903010202</v>
+        <v>900010202</v>
       </c>
       <c r="C124" s="1">
         <v>1</v>
@@ -1940,10 +1890,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>903010403</v>
+        <v>900010403</v>
       </c>
       <c r="B125" s="1">
-        <v>903010302</v>
+        <v>900010302</v>
       </c>
       <c r="C125" s="1">
         <v>1</v>
@@ -1951,10 +1901,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>903010503</v>
+        <v>900010503</v>
       </c>
       <c r="B126" s="1">
-        <v>903010403</v>
+        <v>900010403</v>
       </c>
       <c r="C126" s="1">
         <v>1</v>
@@ -1962,10 +1912,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>903010604</v>
+        <v>900010604</v>
       </c>
       <c r="B127" s="1">
-        <v>903010503</v>
+        <v>900010503</v>
       </c>
       <c r="C127" s="1">
         <v>1</v>
@@ -1973,10 +1923,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>903010704</v>
+        <v>900010704</v>
       </c>
       <c r="B128" s="1">
-        <v>903010604</v>
+        <v>900010604</v>
       </c>
       <c r="C128" s="1">
         <v>1</v>
@@ -1984,397 +1934,12 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>903010805</v>
+        <v>900010805</v>
       </c>
       <c r="B129" s="1">
-        <v>903010704</v>
+        <v>900010704</v>
       </c>
       <c r="C129" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A130" s="1">
-        <v>900010202</v>
-      </c>
-      <c r="B130" s="1">
-        <v>900010101</v>
-      </c>
-      <c r="C130" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A131" s="1">
-        <v>900010302</v>
-      </c>
-      <c r="B131" s="1">
-        <v>900010202</v>
-      </c>
-      <c r="C131" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A132" s="1">
-        <v>900010403</v>
-      </c>
-      <c r="B132" s="1">
-        <v>900010302</v>
-      </c>
-      <c r="C132" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A133" s="1">
-        <v>900010503</v>
-      </c>
-      <c r="B133" s="1">
-        <v>900010403</v>
-      </c>
-      <c r="C133" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A134" s="1">
-        <v>900010604</v>
-      </c>
-      <c r="B134" s="1">
-        <v>900010503</v>
-      </c>
-      <c r="C134" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A135" s="1">
-        <v>900010704</v>
-      </c>
-      <c r="B135" s="1">
-        <v>900010604</v>
-      </c>
-      <c r="C135" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A136" s="1">
-        <v>900010805</v>
-      </c>
-      <c r="B136" s="1">
-        <v>900010704</v>
-      </c>
-      <c r="C136" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A137" s="1">
-        <v>900020202</v>
-      </c>
-      <c r="B137" s="1">
-        <v>900020101</v>
-      </c>
-      <c r="C137" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A138" s="1">
-        <v>900020302</v>
-      </c>
-      <c r="B138" s="1">
-        <v>900020202</v>
-      </c>
-      <c r="C138" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A139" s="1">
-        <v>900020403</v>
-      </c>
-      <c r="B139" s="1">
-        <v>900020302</v>
-      </c>
-      <c r="C139" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A140" s="1">
-        <v>900020503</v>
-      </c>
-      <c r="B140" s="1">
-        <v>900020403</v>
-      </c>
-      <c r="C140" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A141" s="1">
-        <v>900020604</v>
-      </c>
-      <c r="B141" s="1">
-        <v>900020503</v>
-      </c>
-      <c r="C141" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A142" s="1">
-        <v>900020704</v>
-      </c>
-      <c r="B142" s="1">
-        <v>900020604</v>
-      </c>
-      <c r="C142" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A143" s="1">
-        <v>900020805</v>
-      </c>
-      <c r="B143" s="1">
-        <v>900020704</v>
-      </c>
-      <c r="C143" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A144" s="1">
-        <v>901020202</v>
-      </c>
-      <c r="B144" s="1">
-        <v>901020101</v>
-      </c>
-      <c r="C144" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A145" s="1">
-        <v>901020302</v>
-      </c>
-      <c r="B145" s="1">
-        <v>901020101</v>
-      </c>
-      <c r="C145" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A146" s="1">
-        <v>901020403</v>
-      </c>
-      <c r="B146" s="1">
-        <v>901020202</v>
-      </c>
-      <c r="C146" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A147" s="1">
-        <v>901020503</v>
-      </c>
-      <c r="B147" s="1">
-        <v>901020302</v>
-      </c>
-      <c r="C147" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A148" s="1">
-        <v>901020604</v>
-      </c>
-      <c r="B148" s="1">
-        <v>901020202</v>
-      </c>
-      <c r="C148" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A149" s="1">
-        <v>901020704</v>
-      </c>
-      <c r="B149" s="1">
-        <v>901020302</v>
-      </c>
-      <c r="C149" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A150" s="1">
-        <v>901020805</v>
-      </c>
-      <c r="B150" s="1">
-        <v>901020202</v>
-      </c>
-      <c r="C150" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A151" s="1">
-        <v>902020202</v>
-      </c>
-      <c r="B151" s="1">
-        <v>902020101</v>
-      </c>
-      <c r="C151" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A152" s="1">
-        <v>902020302</v>
-      </c>
-      <c r="B152" s="1">
-        <v>902020101</v>
-      </c>
-      <c r="C152" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A153" s="1">
-        <v>902020403</v>
-      </c>
-      <c r="B153" s="1">
-        <v>902020202</v>
-      </c>
-      <c r="C153" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A154" s="1">
-        <v>902020503</v>
-      </c>
-      <c r="B154" s="1">
-        <v>902020302</v>
-      </c>
-      <c r="C154" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A155" s="1">
-        <v>902020604</v>
-      </c>
-      <c r="B155" s="1">
-        <v>902020202</v>
-      </c>
-      <c r="C155" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A156" s="1">
-        <v>902020704</v>
-      </c>
-      <c r="B156" s="1">
-        <v>902020302</v>
-      </c>
-      <c r="C156" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A157" s="1">
-        <v>902020805</v>
-      </c>
-      <c r="B157" s="1">
-        <v>902020202</v>
-      </c>
-      <c r="C157" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A158" s="1">
-        <v>903020202</v>
-      </c>
-      <c r="B158" s="1">
-        <v>903020101</v>
-      </c>
-      <c r="C158" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A159" s="1">
-        <v>903020302</v>
-      </c>
-      <c r="B159" s="1">
-        <v>903020101</v>
-      </c>
-      <c r="C159" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A160" s="1">
-        <v>903020403</v>
-      </c>
-      <c r="B160" s="1">
-        <v>903020101</v>
-      </c>
-      <c r="C160" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A161" s="1">
-        <v>903020503</v>
-      </c>
-      <c r="B161" s="1">
-        <v>903020302</v>
-      </c>
-      <c r="C161" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A162" s="1">
-        <v>903020604</v>
-      </c>
-      <c r="B162" s="1">
-        <v>903020101</v>
-      </c>
-      <c r="C162" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A163" s="1">
-        <v>903020704</v>
-      </c>
-      <c r="B163" s="1">
-        <v>903020302</v>
-      </c>
-      <c r="C163" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A164" s="1">
-        <v>903020805</v>
-      </c>
-      <c r="B164" s="1">
-        <v>903020101</v>
-      </c>
-      <c r="C164" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2386,21 +1951,6 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDCBACA-BED6-466D-A28C-5B93381C106C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCAF9C7-4F66-48BD-9003-E5697C602695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
@@ -178,7 +178,57 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -519,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -1516,7 +1566,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>1010902</v>
+        <v>10109011</v>
       </c>
       <c r="B91" s="1">
         <v>1010901</v>
@@ -1527,10 +1577,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>1010903</v>
+        <v>10109012</v>
       </c>
       <c r="B92" s="1">
-        <v>1010902</v>
+        <v>10109011</v>
       </c>
       <c r="C92" s="1">
         <v>1</v>
@@ -1538,10 +1588,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>1010904</v>
+        <v>1010902</v>
       </c>
       <c r="B93" s="1">
-        <v>1010903</v>
+        <v>1010901</v>
       </c>
       <c r="C93" s="1">
         <v>1</v>
@@ -1549,10 +1599,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>1010905</v>
-      </c>
-      <c r="B94" s="5">
-        <v>1010904</v>
+        <v>1010903</v>
+      </c>
+      <c r="B94" s="1">
+        <v>1010902</v>
       </c>
       <c r="C94" s="1">
         <v>1</v>
@@ -1560,10 +1610,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>905010202</v>
+        <v>1010904</v>
       </c>
       <c r="B95" s="1">
-        <v>905010101</v>
+        <v>1010903</v>
       </c>
       <c r="C95" s="1">
         <v>1</v>
@@ -1571,10 +1621,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>905010302</v>
-      </c>
-      <c r="B96" s="1">
-        <v>905010202</v>
+        <v>1010905</v>
+      </c>
+      <c r="B96" s="5">
+        <v>1010904</v>
       </c>
       <c r="C96" s="1">
         <v>1</v>
@@ -1582,10 +1632,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>905010403</v>
-      </c>
-      <c r="B97" s="1">
-        <v>905010302</v>
+        <v>1010906</v>
+      </c>
+      <c r="B97" s="5">
+        <v>1010905</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
@@ -1593,10 +1643,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>905010503</v>
-      </c>
-      <c r="B98" s="1">
-        <v>905010403</v>
+        <v>1010907</v>
+      </c>
+      <c r="B98" s="5">
+        <v>1010906</v>
       </c>
       <c r="C98" s="1">
         <v>1</v>
@@ -1604,10 +1654,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>905010604</v>
-      </c>
-      <c r="B99" s="1">
-        <v>905010503</v>
+        <v>1010908</v>
+      </c>
+      <c r="B99" s="5">
+        <v>1010907</v>
       </c>
       <c r="C99" s="1">
         <v>1</v>
@@ -1615,10 +1665,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>905010704</v>
-      </c>
-      <c r="B100" s="1">
-        <v>905010604</v>
+        <v>1010909</v>
+      </c>
+      <c r="B100" s="5">
+        <v>1010908</v>
       </c>
       <c r="C100" s="1">
         <v>1</v>
@@ -1626,10 +1676,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>905010805</v>
-      </c>
-      <c r="B101" s="1">
-        <v>905010704</v>
+        <v>1010910</v>
+      </c>
+      <c r="B101" s="5">
+        <v>1010909</v>
       </c>
       <c r="C101" s="1">
         <v>1</v>
@@ -1637,10 +1687,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>901010202</v>
+        <v>905010202</v>
       </c>
       <c r="B102" s="1">
-        <v>901010101</v>
+        <v>905010101</v>
       </c>
       <c r="C102" s="1">
         <v>1</v>
@@ -1648,10 +1698,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>901010302</v>
+        <v>905010302</v>
       </c>
       <c r="B103" s="1">
-        <v>901010202</v>
+        <v>905010202</v>
       </c>
       <c r="C103" s="1">
         <v>1</v>
@@ -1659,10 +1709,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>901010403</v>
+        <v>905010403</v>
       </c>
       <c r="B104" s="1">
-        <v>901010302</v>
+        <v>905010302</v>
       </c>
       <c r="C104" s="1">
         <v>1</v>
@@ -1670,10 +1720,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>901010503</v>
+        <v>905010503</v>
       </c>
       <c r="B105" s="1">
-        <v>901010403</v>
+        <v>905010403</v>
       </c>
       <c r="C105" s="1">
         <v>1</v>
@@ -1681,10 +1731,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
-        <v>901010604</v>
+        <v>905010604</v>
       </c>
       <c r="B106" s="1">
-        <v>901010503</v>
+        <v>905010503</v>
       </c>
       <c r="C106" s="1">
         <v>1</v>
@@ -1692,10 +1742,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>901010704</v>
+        <v>905010704</v>
       </c>
       <c r="B107" s="1">
-        <v>901010604</v>
+        <v>905010604</v>
       </c>
       <c r="C107" s="1">
         <v>1</v>
@@ -1703,10 +1753,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
-        <v>901010805</v>
+        <v>905010805</v>
       </c>
       <c r="B108" s="1">
-        <v>901010704</v>
+        <v>905010704</v>
       </c>
       <c r="C108" s="1">
         <v>1</v>
@@ -1714,10 +1764,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>902010202</v>
+        <v>901010202</v>
       </c>
       <c r="B109" s="1">
-        <v>902010101</v>
+        <v>901010101</v>
       </c>
       <c r="C109" s="1">
         <v>1</v>
@@ -1725,10 +1775,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>902010302</v>
+        <v>901010302</v>
       </c>
       <c r="B110" s="1">
-        <v>902010202</v>
+        <v>901010202</v>
       </c>
       <c r="C110" s="1">
         <v>1</v>
@@ -1736,10 +1786,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>902010403</v>
+        <v>901010403</v>
       </c>
       <c r="B111" s="1">
-        <v>902010302</v>
+        <v>901010302</v>
       </c>
       <c r="C111" s="1">
         <v>1</v>
@@ -1747,10 +1797,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>902010503</v>
+        <v>901010503</v>
       </c>
       <c r="B112" s="1">
-        <v>902010403</v>
+        <v>901010403</v>
       </c>
       <c r="C112" s="1">
         <v>1</v>
@@ -1758,10 +1808,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>902010604</v>
+        <v>901010604</v>
       </c>
       <c r="B113" s="1">
-        <v>902010503</v>
+        <v>901010503</v>
       </c>
       <c r="C113" s="1">
         <v>1</v>
@@ -1769,10 +1819,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>902010704</v>
+        <v>901010704</v>
       </c>
       <c r="B114" s="1">
-        <v>902010604</v>
+        <v>901010604</v>
       </c>
       <c r="C114" s="1">
         <v>1</v>
@@ -1780,10 +1830,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>902010805</v>
+        <v>901010805</v>
       </c>
       <c r="B115" s="1">
-        <v>902010704</v>
+        <v>901010704</v>
       </c>
       <c r="C115" s="1">
         <v>1</v>
@@ -1791,10 +1841,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>903010202</v>
+        <v>902010202</v>
       </c>
       <c r="B116" s="1">
-        <v>903010101</v>
+        <v>902010101</v>
       </c>
       <c r="C116" s="1">
         <v>1</v>
@@ -1802,10 +1852,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>903010302</v>
+        <v>902010302</v>
       </c>
       <c r="B117" s="1">
-        <v>903010202</v>
+        <v>902010202</v>
       </c>
       <c r="C117" s="1">
         <v>1</v>
@@ -1813,10 +1863,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>903010403</v>
+        <v>902010403</v>
       </c>
       <c r="B118" s="1">
-        <v>903010302</v>
+        <v>902010302</v>
       </c>
       <c r="C118" s="1">
         <v>1</v>
@@ -1824,10 +1874,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>903010503</v>
+        <v>902010503</v>
       </c>
       <c r="B119" s="1">
-        <v>903010403</v>
+        <v>902010403</v>
       </c>
       <c r="C119" s="1">
         <v>1</v>
@@ -1835,10 +1885,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>903010604</v>
+        <v>902010604</v>
       </c>
       <c r="B120" s="1">
-        <v>903010503</v>
+        <v>902010503</v>
       </c>
       <c r="C120" s="1">
         <v>1</v>
@@ -1846,10 +1896,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>903010704</v>
+        <v>902010704</v>
       </c>
       <c r="B121" s="1">
-        <v>903010604</v>
+        <v>902010604</v>
       </c>
       <c r="C121" s="1">
         <v>1</v>
@@ -1857,10 +1907,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>903010805</v>
+        <v>902010805</v>
       </c>
       <c r="B122" s="1">
-        <v>903010704</v>
+        <v>902010704</v>
       </c>
       <c r="C122" s="1">
         <v>1</v>
@@ -1868,10 +1918,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>900010202</v>
+        <v>903010202</v>
       </c>
       <c r="B123" s="1">
-        <v>900010101</v>
+        <v>903010101</v>
       </c>
       <c r="C123" s="1">
         <v>1</v>
@@ -1879,10 +1929,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>900010302</v>
+        <v>903010302</v>
       </c>
       <c r="B124" s="1">
-        <v>900010202</v>
+        <v>903010202</v>
       </c>
       <c r="C124" s="1">
         <v>1</v>
@@ -1890,10 +1940,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>900010403</v>
+        <v>903010403</v>
       </c>
       <c r="B125" s="1">
-        <v>900010302</v>
+        <v>903010302</v>
       </c>
       <c r="C125" s="1">
         <v>1</v>
@@ -1901,10 +1951,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>900010503</v>
+        <v>903010503</v>
       </c>
       <c r="B126" s="1">
-        <v>900010403</v>
+        <v>903010403</v>
       </c>
       <c r="C126" s="1">
         <v>1</v>
@@ -1912,10 +1962,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>900010604</v>
+        <v>903010604</v>
       </c>
       <c r="B127" s="1">
-        <v>900010503</v>
+        <v>903010503</v>
       </c>
       <c r="C127" s="1">
         <v>1</v>
@@ -1923,10 +1973,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>900010704</v>
+        <v>903010704</v>
       </c>
       <c r="B128" s="1">
-        <v>900010604</v>
+        <v>903010604</v>
       </c>
       <c r="C128" s="1">
         <v>1</v>
@@ -1934,12 +1984,397 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
+        <v>903010805</v>
+      </c>
+      <c r="B129" s="1">
+        <v>903010704</v>
+      </c>
+      <c r="C129" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A130" s="1">
+        <v>900010202</v>
+      </c>
+      <c r="B130" s="1">
+        <v>900010101</v>
+      </c>
+      <c r="C130" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A131" s="1">
+        <v>900010302</v>
+      </c>
+      <c r="B131" s="1">
+        <v>900010202</v>
+      </c>
+      <c r="C131" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A132" s="1">
+        <v>900010403</v>
+      </c>
+      <c r="B132" s="1">
+        <v>900010302</v>
+      </c>
+      <c r="C132" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A133" s="1">
+        <v>900010503</v>
+      </c>
+      <c r="B133" s="1">
+        <v>900010403</v>
+      </c>
+      <c r="C133" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A134" s="1">
+        <v>900010604</v>
+      </c>
+      <c r="B134" s="1">
+        <v>900010503</v>
+      </c>
+      <c r="C134" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A135" s="1">
+        <v>900010704</v>
+      </c>
+      <c r="B135" s="1">
+        <v>900010604</v>
+      </c>
+      <c r="C135" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A136" s="1">
         <v>900010805</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B136" s="1">
         <v>900010704</v>
       </c>
-      <c r="C129" s="1">
+      <c r="C136" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A137" s="1">
+        <v>900020202</v>
+      </c>
+      <c r="B137" s="1">
+        <v>900020101</v>
+      </c>
+      <c r="C137" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A138" s="1">
+        <v>900020302</v>
+      </c>
+      <c r="B138" s="1">
+        <v>900020202</v>
+      </c>
+      <c r="C138" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A139" s="1">
+        <v>900020403</v>
+      </c>
+      <c r="B139" s="1">
+        <v>900020302</v>
+      </c>
+      <c r="C139" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A140" s="1">
+        <v>900020503</v>
+      </c>
+      <c r="B140" s="1">
+        <v>900020403</v>
+      </c>
+      <c r="C140" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A141" s="1">
+        <v>900020604</v>
+      </c>
+      <c r="B141" s="1">
+        <v>900020503</v>
+      </c>
+      <c r="C141" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A142" s="1">
+        <v>900020704</v>
+      </c>
+      <c r="B142" s="1">
+        <v>900020604</v>
+      </c>
+      <c r="C142" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A143" s="1">
+        <v>900020805</v>
+      </c>
+      <c r="B143" s="1">
+        <v>900020704</v>
+      </c>
+      <c r="C143" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A144" s="1">
+        <v>901020202</v>
+      </c>
+      <c r="B144" s="1">
+        <v>901020101</v>
+      </c>
+      <c r="C144" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A145" s="1">
+        <v>901020302</v>
+      </c>
+      <c r="B145" s="1">
+        <v>901020101</v>
+      </c>
+      <c r="C145" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A146" s="1">
+        <v>901020403</v>
+      </c>
+      <c r="B146" s="1">
+        <v>901020202</v>
+      </c>
+      <c r="C146" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A147" s="1">
+        <v>901020503</v>
+      </c>
+      <c r="B147" s="1">
+        <v>901020302</v>
+      </c>
+      <c r="C147" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A148" s="1">
+        <v>901020604</v>
+      </c>
+      <c r="B148" s="1">
+        <v>901020202</v>
+      </c>
+      <c r="C148" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A149" s="1">
+        <v>901020704</v>
+      </c>
+      <c r="B149" s="1">
+        <v>901020302</v>
+      </c>
+      <c r="C149" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A150" s="1">
+        <v>901020805</v>
+      </c>
+      <c r="B150" s="1">
+        <v>901020202</v>
+      </c>
+      <c r="C150" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A151" s="1">
+        <v>902020202</v>
+      </c>
+      <c r="B151" s="1">
+        <v>902020101</v>
+      </c>
+      <c r="C151" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A152" s="1">
+        <v>902020302</v>
+      </c>
+      <c r="B152" s="1">
+        <v>902020101</v>
+      </c>
+      <c r="C152" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A153" s="1">
+        <v>902020403</v>
+      </c>
+      <c r="B153" s="1">
+        <v>902020202</v>
+      </c>
+      <c r="C153" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A154" s="1">
+        <v>902020503</v>
+      </c>
+      <c r="B154" s="1">
+        <v>902020302</v>
+      </c>
+      <c r="C154" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A155" s="1">
+        <v>902020604</v>
+      </c>
+      <c r="B155" s="1">
+        <v>902020202</v>
+      </c>
+      <c r="C155" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A156" s="1">
+        <v>902020704</v>
+      </c>
+      <c r="B156" s="1">
+        <v>902020302</v>
+      </c>
+      <c r="C156" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A157" s="1">
+        <v>902020805</v>
+      </c>
+      <c r="B157" s="1">
+        <v>902020202</v>
+      </c>
+      <c r="C157" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A158" s="1">
+        <v>903020202</v>
+      </c>
+      <c r="B158" s="1">
+        <v>903020101</v>
+      </c>
+      <c r="C158" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A159" s="1">
+        <v>903020302</v>
+      </c>
+      <c r="B159" s="1">
+        <v>903020101</v>
+      </c>
+      <c r="C159" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A160" s="1">
+        <v>903020403</v>
+      </c>
+      <c r="B160" s="1">
+        <v>903020101</v>
+      </c>
+      <c r="C160" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A161" s="1">
+        <v>903020503</v>
+      </c>
+      <c r="B161" s="1">
+        <v>903020302</v>
+      </c>
+      <c r="C161" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A162" s="1">
+        <v>903020604</v>
+      </c>
+      <c r="B162" s="1">
+        <v>903020101</v>
+      </c>
+      <c r="C162" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A163" s="1">
+        <v>903020704</v>
+      </c>
+      <c r="B163" s="1">
+        <v>903020302</v>
+      </c>
+      <c r="C163" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A164" s="1">
+        <v>903020805</v>
+      </c>
+      <c r="B164" s="1">
+        <v>903020101</v>
+      </c>
+      <c r="C164" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1951,6 +2386,21 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B139">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B140">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B141">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B142">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCAF9C7-4F66-48BD-9003-E5697C602695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5AF679-D243-454C-85F0-0BC7764C996C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_front_v8" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,47 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -569,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C209"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2378,6 +2418,501 @@
         <v>1</v>
       </c>
     </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A165" s="1">
+        <v>800010101</v>
+      </c>
+      <c r="B165" s="1">
+        <v>800000001</v>
+      </c>
+      <c r="C165" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A166" s="1">
+        <v>800010102</v>
+      </c>
+      <c r="B166" s="1">
+        <v>800010101</v>
+      </c>
+      <c r="C166" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A167" s="1">
+        <v>800010201</v>
+      </c>
+      <c r="B167" s="1">
+        <v>800000001</v>
+      </c>
+      <c r="C167" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A168" s="1">
+        <v>800010202</v>
+      </c>
+      <c r="B168" s="1">
+        <v>800010201</v>
+      </c>
+      <c r="C168" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A169" s="1">
+        <v>800010301</v>
+      </c>
+      <c r="B169" s="1">
+        <v>800000001</v>
+      </c>
+      <c r="C169" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A170" s="1">
+        <v>800010302</v>
+      </c>
+      <c r="B170" s="1">
+        <v>800010301</v>
+      </c>
+      <c r="C170" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A171" s="1">
+        <v>800030101</v>
+      </c>
+      <c r="B171" s="1">
+        <v>800010101</v>
+      </c>
+      <c r="C171" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A172" s="1">
+        <v>800030102</v>
+      </c>
+      <c r="B172" s="1">
+        <v>800030101</v>
+      </c>
+      <c r="C172" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A173" s="1">
+        <v>800030201</v>
+      </c>
+      <c r="B173" s="1">
+        <v>800030101</v>
+      </c>
+      <c r="C173" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A174" s="1">
+        <v>800030202</v>
+      </c>
+      <c r="B174" s="1">
+        <v>800030201</v>
+      </c>
+      <c r="C174" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A175" s="1">
+        <v>800110101</v>
+      </c>
+      <c r="B175" s="1">
+        <v>800100001</v>
+      </c>
+      <c r="C175" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A176" s="1">
+        <v>800110102</v>
+      </c>
+      <c r="B176" s="1">
+        <v>800110101</v>
+      </c>
+      <c r="C176" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A177" s="1">
+        <v>800110201</v>
+      </c>
+      <c r="B177" s="1">
+        <v>800100001</v>
+      </c>
+      <c r="C177" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A178" s="1">
+        <v>800110202</v>
+      </c>
+      <c r="B178" s="1">
+        <v>800110201</v>
+      </c>
+      <c r="C178" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A179" s="1">
+        <v>800110301</v>
+      </c>
+      <c r="B179" s="1">
+        <v>800100001</v>
+      </c>
+      <c r="C179" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A180" s="1">
+        <v>800110302</v>
+      </c>
+      <c r="B180" s="1">
+        <v>800110301</v>
+      </c>
+      <c r="C180" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A181" s="1">
+        <v>800130101</v>
+      </c>
+      <c r="B181" s="1">
+        <v>800110101</v>
+      </c>
+      <c r="C181" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A182" s="1">
+        <v>800130102</v>
+      </c>
+      <c r="B182" s="1">
+        <v>800130101</v>
+      </c>
+      <c r="C182" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A183" s="1">
+        <v>800130201</v>
+      </c>
+      <c r="B183" s="1">
+        <v>800130101</v>
+      </c>
+      <c r="C183" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A184" s="1">
+        <v>800130202</v>
+      </c>
+      <c r="B184" s="1">
+        <v>800130201</v>
+      </c>
+      <c r="C184" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A185" s="1">
+        <v>800210101</v>
+      </c>
+      <c r="B185" s="1">
+        <v>800200001</v>
+      </c>
+      <c r="C185" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A186" s="1">
+        <v>800210102</v>
+      </c>
+      <c r="B186" s="1">
+        <v>800210101</v>
+      </c>
+      <c r="C186" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A187" s="1">
+        <v>800210201</v>
+      </c>
+      <c r="B187" s="1">
+        <v>800200001</v>
+      </c>
+      <c r="C187" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A188" s="1">
+        <v>800210202</v>
+      </c>
+      <c r="B188" s="1">
+        <v>800210201</v>
+      </c>
+      <c r="C188" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A189" s="1">
+        <v>800210301</v>
+      </c>
+      <c r="B189" s="1">
+        <v>800200001</v>
+      </c>
+      <c r="C189" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A190" s="1">
+        <v>800210302</v>
+      </c>
+      <c r="B190" s="1">
+        <v>800210301</v>
+      </c>
+      <c r="C190" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A191" s="1">
+        <v>800230101</v>
+      </c>
+      <c r="B191" s="1">
+        <v>800210201</v>
+      </c>
+      <c r="C191" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A192" s="1">
+        <v>800230102</v>
+      </c>
+      <c r="B192" s="1">
+        <v>800230101</v>
+      </c>
+      <c r="C192" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A193" s="1">
+        <v>800230201</v>
+      </c>
+      <c r="B193" s="1">
+        <v>800230101</v>
+      </c>
+      <c r="C193" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A194" s="1">
+        <v>800230202</v>
+      </c>
+      <c r="B194" s="1">
+        <v>800230201</v>
+      </c>
+      <c r="C194" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A195" s="1">
+        <v>801100101</v>
+      </c>
+      <c r="B195" s="1">
+        <v>801100001</v>
+      </c>
+      <c r="C195" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A196" s="1">
+        <v>801100102</v>
+      </c>
+      <c r="B196" s="1">
+        <v>801100101</v>
+      </c>
+      <c r="C196" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A197" s="1">
+        <v>801100103</v>
+      </c>
+      <c r="B197" s="1">
+        <v>801100102</v>
+      </c>
+      <c r="C197" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A198" s="1">
+        <v>801100201</v>
+      </c>
+      <c r="B198" s="1">
+        <v>801100001</v>
+      </c>
+      <c r="C198" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A199" s="1">
+        <v>801100202</v>
+      </c>
+      <c r="B199" s="1">
+        <v>801100201</v>
+      </c>
+      <c r="C199" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A200" s="1">
+        <v>801100203</v>
+      </c>
+      <c r="B200" s="1">
+        <v>801100202</v>
+      </c>
+      <c r="C200" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A201" s="1">
+        <v>801100301</v>
+      </c>
+      <c r="B201" s="1">
+        <v>801100001</v>
+      </c>
+      <c r="C201" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A202" s="1">
+        <v>801100302</v>
+      </c>
+      <c r="B202" s="1">
+        <v>801100301</v>
+      </c>
+      <c r="C202" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A203" s="1">
+        <v>801100303</v>
+      </c>
+      <c r="B203" s="1">
+        <v>801100302</v>
+      </c>
+      <c r="C203" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A204" s="1">
+        <v>801200101</v>
+      </c>
+      <c r="B204" s="1">
+        <v>801200001</v>
+      </c>
+      <c r="C204" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A205" s="1">
+        <v>801200102</v>
+      </c>
+      <c r="B205" s="1">
+        <v>801200101</v>
+      </c>
+      <c r="C205" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A206" s="1">
+        <v>801200103</v>
+      </c>
+      <c r="B206" s="1">
+        <v>801200102</v>
+      </c>
+      <c r="C206" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A207" s="1">
+        <v>801200201</v>
+      </c>
+      <c r="B207" s="1">
+        <v>801200001</v>
+      </c>
+      <c r="C207" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A208" s="1">
+        <v>801200202</v>
+      </c>
+      <c r="B208" s="1">
+        <v>801200201</v>
+      </c>
+      <c r="C208" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A209" s="1">
+        <v>801200203</v>
+      </c>
+      <c r="B209" s="1">
+        <v>801200202</v>
+      </c>
+      <c r="C209" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:C4" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:C5">
@@ -2386,21 +2921,33 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B139">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B140">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B141">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B142">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B139">
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B140">
+  <conditionalFormatting sqref="B173">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
+  <conditionalFormatting sqref="B183">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
+  <conditionalFormatting sqref="B193">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
+  <conditionalFormatting sqref="B205:B206 B208:B209">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5AF679-D243-454C-85F0-0BC7764C996C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E1F2D3-3C23-4C21-94F5-F5DE619BFFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_front_v8" sheetId="1" r:id="rId1"/>
@@ -178,37 +178,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -609,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:C209"/>
+  <dimension ref="A1:C208"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2489,7 +2459,7 @@
         <v>800030101</v>
       </c>
       <c r="B171" s="1">
-        <v>800010101</v>
+        <v>800000001</v>
       </c>
       <c r="C171" s="1">
         <v>1</v>
@@ -2511,7 +2481,7 @@
         <v>800030201</v>
       </c>
       <c r="B173" s="1">
-        <v>800030101</v>
+        <v>800000001</v>
       </c>
       <c r="C173" s="1">
         <v>1</v>
@@ -2599,7 +2569,7 @@
         <v>800130101</v>
       </c>
       <c r="B181" s="1">
-        <v>800110101</v>
+        <v>800100001</v>
       </c>
       <c r="C181" s="1">
         <v>1</v>
@@ -2621,7 +2591,7 @@
         <v>800130201</v>
       </c>
       <c r="B183" s="1">
-        <v>800130101</v>
+        <v>800100001</v>
       </c>
       <c r="C183" s="1">
         <v>1</v>
@@ -2709,7 +2679,7 @@
         <v>800230101</v>
       </c>
       <c r="B191" s="1">
-        <v>800210201</v>
+        <v>800200001</v>
       </c>
       <c r="C191" s="1">
         <v>1</v>
@@ -2731,7 +2701,7 @@
         <v>800230201</v>
       </c>
       <c r="B193" s="1">
-        <v>800230101</v>
+        <v>800200001</v>
       </c>
       <c r="C193" s="1">
         <v>1</v>
@@ -2750,10 +2720,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
+        <v>801100102</v>
+      </c>
+      <c r="B195" s="1">
         <v>801100101</v>
-      </c>
-      <c r="B195" s="1">
-        <v>801100001</v>
       </c>
       <c r="C195" s="1">
         <v>1</v>
@@ -2761,10 +2731,10 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
+        <v>801100103</v>
+      </c>
+      <c r="B196" s="1">
         <v>801100102</v>
-      </c>
-      <c r="B196" s="1">
-        <v>801100101</v>
       </c>
       <c r="C196" s="1">
         <v>1</v>
@@ -2772,10 +2742,10 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>801100103</v>
+        <v>801100201</v>
       </c>
       <c r="B197" s="1">
-        <v>801100102</v>
+        <v>801100001</v>
       </c>
       <c r="C197" s="1">
         <v>1</v>
@@ -2783,10 +2753,10 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
+        <v>801100202</v>
+      </c>
+      <c r="B198" s="1">
         <v>801100201</v>
-      </c>
-      <c r="B198" s="1">
-        <v>801100001</v>
       </c>
       <c r="C198" s="1">
         <v>1</v>
@@ -2794,10 +2764,10 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
+        <v>801100203</v>
+      </c>
+      <c r="B199" s="1">
         <v>801100202</v>
-      </c>
-      <c r="B199" s="1">
-        <v>801100201</v>
       </c>
       <c r="C199" s="1">
         <v>1</v>
@@ -2805,10 +2775,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>801100203</v>
+        <v>801100301</v>
       </c>
       <c r="B200" s="1">
-        <v>801100202</v>
+        <v>801100001</v>
       </c>
       <c r="C200" s="1">
         <v>1</v>
@@ -2816,10 +2786,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
+        <v>801100302</v>
+      </c>
+      <c r="B201" s="1">
         <v>801100301</v>
-      </c>
-      <c r="B201" s="1">
-        <v>801100001</v>
       </c>
       <c r="C201" s="1">
         <v>1</v>
@@ -2827,10 +2797,10 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
+        <v>801100303</v>
+      </c>
+      <c r="B202" s="1">
         <v>801100302</v>
-      </c>
-      <c r="B202" s="1">
-        <v>801100301</v>
       </c>
       <c r="C202" s="1">
         <v>1</v>
@@ -2838,10 +2808,10 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>801100303</v>
+        <v>801200101</v>
       </c>
       <c r="B203" s="1">
-        <v>801100302</v>
+        <v>801200001</v>
       </c>
       <c r="C203" s="1">
         <v>1</v>
@@ -2849,10 +2819,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
+        <v>801200102</v>
+      </c>
+      <c r="B204" s="1">
         <v>801200101</v>
-      </c>
-      <c r="B204" s="1">
-        <v>801200001</v>
       </c>
       <c r="C204" s="1">
         <v>1</v>
@@ -2860,10 +2830,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
+        <v>801200103</v>
+      </c>
+      <c r="B205" s="1">
         <v>801200102</v>
-      </c>
-      <c r="B205" s="1">
-        <v>801200101</v>
       </c>
       <c r="C205" s="1">
         <v>1</v>
@@ -2871,10 +2841,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>801200103</v>
+        <v>801200201</v>
       </c>
       <c r="B206" s="1">
-        <v>801200102</v>
+        <v>801200001</v>
       </c>
       <c r="C206" s="1">
         <v>1</v>
@@ -2882,10 +2852,10 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
+        <v>801200202</v>
+      </c>
+      <c r="B207" s="1">
         <v>801200201</v>
-      </c>
-      <c r="B207" s="1">
-        <v>801200001</v>
       </c>
       <c r="C207" s="1">
         <v>1</v>
@@ -2893,23 +2863,12 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
+        <v>801200203</v>
+      </c>
+      <c r="B208" s="1">
         <v>801200202</v>
       </c>
-      <c r="B208" s="1">
-        <v>801200201</v>
-      </c>
       <c r="C208" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A209" s="1">
-        <v>801200203</v>
-      </c>
-      <c r="B209" s="1">
-        <v>801200202</v>
-      </c>
-      <c r="C209" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2921,33 +2880,24 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B183">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B205:B206 B208:B209">
+  <conditionalFormatting sqref="B204:B205 B207:B208">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E1F2D3-3C23-4C21-94F5-F5DE619BFFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56410161-CE60-4F96-8D34-D84F5587A9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>词条组id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -88,6 +88,16 @@
   </si>
   <si>
     <t>5010101,5010102,5010103,5010104,5010105</t>
+  </si>
+  <si>
+    <t>700010105,700010106,700010107</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>700110105,700110106,700110107</t>
+  </si>
+  <si>
+    <t>700210105,700210106,700210107</t>
   </si>
 </sst>
 </file>
@@ -163,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -174,11 +184,52 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -579,11 +630,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:C208"/>
+  <dimension ref="A1:C238"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
@@ -2869,6 +2920,336 @@
         <v>801200202</v>
       </c>
       <c r="C208" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A209" s="1">
+        <v>700010101</v>
+      </c>
+      <c r="B209" s="1">
+        <v>700000001</v>
+      </c>
+      <c r="C209" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A210" s="1">
+        <v>700010102</v>
+      </c>
+      <c r="B210" s="1">
+        <v>700010101</v>
+      </c>
+      <c r="C210" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A211" s="1">
+        <v>700010103</v>
+      </c>
+      <c r="B211" s="1">
+        <v>700000001</v>
+      </c>
+      <c r="C211" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A212" s="1">
+        <v>700010104</v>
+      </c>
+      <c r="B212" s="1">
+        <v>700010102</v>
+      </c>
+      <c r="C212" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A213" s="1">
+        <v>700010105</v>
+      </c>
+      <c r="B213" s="1">
+        <v>700010104</v>
+      </c>
+      <c r="C213" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A214" s="1">
+        <v>700010106</v>
+      </c>
+      <c r="B214" s="1">
+        <v>700010104</v>
+      </c>
+      <c r="C214" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A215" s="1">
+        <v>700010107</v>
+      </c>
+      <c r="B215" s="1">
+        <v>700010104</v>
+      </c>
+      <c r="C215" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A216" s="1">
+        <v>700010108</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C216" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A217" s="1">
+        <v>700100101</v>
+      </c>
+      <c r="B217" s="1">
+        <v>700100001</v>
+      </c>
+      <c r="C217" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A218" s="1">
+        <v>700100102</v>
+      </c>
+      <c r="B218" s="1">
+        <v>700110101</v>
+      </c>
+      <c r="C218" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A219" s="1">
+        <v>700100103</v>
+      </c>
+      <c r="B219" s="1">
+        <v>700100001</v>
+      </c>
+      <c r="C219" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A220" s="1">
+        <v>700100104</v>
+      </c>
+      <c r="B220" s="1">
+        <v>700110102</v>
+      </c>
+      <c r="C220" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A221" s="1">
+        <v>700100105</v>
+      </c>
+      <c r="B221" s="1">
+        <v>700110104</v>
+      </c>
+      <c r="C221" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A222" s="1">
+        <v>700100106</v>
+      </c>
+      <c r="B222" s="1">
+        <v>700110104</v>
+      </c>
+      <c r="C222" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A223" s="1">
+        <v>700100107</v>
+      </c>
+      <c r="B223" s="1">
+        <v>700110104</v>
+      </c>
+      <c r="C223" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A224" s="1">
+        <v>700100108</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C224" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A225" s="1">
+        <v>700200101</v>
+      </c>
+      <c r="B225" s="1">
+        <v>700200001</v>
+      </c>
+      <c r="C225" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A226" s="1">
+        <v>700200102</v>
+      </c>
+      <c r="B226" s="1">
+        <v>700210101</v>
+      </c>
+      <c r="C226" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A227" s="1">
+        <v>700200103</v>
+      </c>
+      <c r="B227" s="1">
+        <v>700200001</v>
+      </c>
+      <c r="C227" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A228" s="1">
+        <v>700200104</v>
+      </c>
+      <c r="B228" s="1">
+        <v>700210102</v>
+      </c>
+      <c r="C228" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A229" s="1">
+        <v>700200105</v>
+      </c>
+      <c r="B229" s="1">
+        <v>700210104</v>
+      </c>
+      <c r="C229" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A230" s="1">
+        <v>700200106</v>
+      </c>
+      <c r="B230" s="1">
+        <v>700210104</v>
+      </c>
+      <c r="C230" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A231" s="1">
+        <v>700200107</v>
+      </c>
+      <c r="B231" s="1">
+        <v>700210104</v>
+      </c>
+      <c r="C231" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A232" s="1">
+        <v>700200108</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C232" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A233" s="1">
+        <v>700400002</v>
+      </c>
+      <c r="B233" s="1">
+        <v>700400001</v>
+      </c>
+      <c r="C233" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A234" s="1">
+        <v>700400003</v>
+      </c>
+      <c r="B234" s="1">
+        <v>700400002</v>
+      </c>
+      <c r="C234" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A235" s="1">
+        <v>700400004</v>
+      </c>
+      <c r="B235" s="1">
+        <v>700400003</v>
+      </c>
+      <c r="C235" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A236" s="1">
+        <v>700400102</v>
+      </c>
+      <c r="B236" s="1">
+        <v>700400101</v>
+      </c>
+      <c r="C236" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A237" s="1">
+        <v>700400103</v>
+      </c>
+      <c r="B237" s="1">
+        <v>700400102</v>
+      </c>
+      <c r="C237" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A238" s="1">
+        <v>700400104</v>
+      </c>
+      <c r="B238" s="1">
+        <v>700400103</v>
+      </c>
+      <c r="C238" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2880,24 +3261,33 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B139">
+    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B140">
+    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B141">
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B142">
     <cfRule type="duplicateValues" dxfId="6" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B139">
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="5" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+  <conditionalFormatting sqref="B204:B205 B207:B208">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+  <conditionalFormatting sqref="B233:B235">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+  <conditionalFormatting sqref="B236">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B204:B205 B207:B208">
+  <conditionalFormatting sqref="B237:B238">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56410161-CE60-4F96-8D34-D84F5587A9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBFD416-B391-45E5-8701-2357F0D7C7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
@@ -94,10 +94,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>700110105,700110106,700110107</t>
+    <t>700100105,700100106,700100107</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>700210105,700210106,700210107</t>
+    <t>700200105,700200106,700200107</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -189,17 +191,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3027,7 +3019,7 @@
         <v>700100102</v>
       </c>
       <c r="B218" s="1">
-        <v>700110101</v>
+        <v>700100101</v>
       </c>
       <c r="C218" s="1">
         <v>1</v>
@@ -3049,7 +3041,7 @@
         <v>700100104</v>
       </c>
       <c r="B220" s="1">
-        <v>700110102</v>
+        <v>700100102</v>
       </c>
       <c r="C220" s="1">
         <v>1</v>
@@ -3060,7 +3052,7 @@
         <v>700100105</v>
       </c>
       <c r="B221" s="1">
-        <v>700110104</v>
+        <v>700100104</v>
       </c>
       <c r="C221" s="1">
         <v>1</v>
@@ -3071,7 +3063,7 @@
         <v>700100106</v>
       </c>
       <c r="B222" s="1">
-        <v>700110104</v>
+        <v>700100104</v>
       </c>
       <c r="C222" s="1">
         <v>1</v>
@@ -3082,7 +3074,7 @@
         <v>700100107</v>
       </c>
       <c r="B223" s="1">
-        <v>700110104</v>
+        <v>700100104</v>
       </c>
       <c r="C223" s="1">
         <v>1</v>
@@ -3115,7 +3107,7 @@
         <v>700200102</v>
       </c>
       <c r="B226" s="1">
-        <v>700210101</v>
+        <v>700200101</v>
       </c>
       <c r="C226" s="1">
         <v>1</v>
@@ -3137,7 +3129,7 @@
         <v>700200104</v>
       </c>
       <c r="B228" s="1">
-        <v>700210102</v>
+        <v>700200102</v>
       </c>
       <c r="C228" s="1">
         <v>1</v>
@@ -3148,7 +3140,7 @@
         <v>700200105</v>
       </c>
       <c r="B229" s="1">
-        <v>700210104</v>
+        <v>700200104</v>
       </c>
       <c r="C229" s="1">
         <v>1</v>
@@ -3159,7 +3151,7 @@
         <v>700200106</v>
       </c>
       <c r="B230" s="1">
-        <v>700210104</v>
+        <v>700200104</v>
       </c>
       <c r="C230" s="1">
         <v>1</v>
@@ -3170,7 +3162,7 @@
         <v>700200107</v>
       </c>
       <c r="B231" s="1">
-        <v>700210104</v>
+        <v>700200104</v>
       </c>
       <c r="C231" s="1">
         <v>1</v>
@@ -3261,25 +3253,25 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204:B205 B207:B208">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233:B235">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBFD416-B391-45E5-8701-2357F0D7C7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0C1592-BEA7-4065-B99E-3E6340D9D9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
@@ -191,7 +191,37 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -622,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:C238"/>
+  <dimension ref="A1:C247"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2939,10 +2969,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>700010103</v>
+        <v>700010112</v>
       </c>
       <c r="B211" s="1">
-        <v>700000001</v>
+        <v>700010102</v>
       </c>
       <c r="C211" s="1">
         <v>1</v>
@@ -2950,10 +2980,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>700010104</v>
+        <v>700010122</v>
       </c>
       <c r="B212" s="1">
-        <v>700010102</v>
+        <v>700010112</v>
       </c>
       <c r="C212" s="1">
         <v>1</v>
@@ -2961,10 +2991,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>700010105</v>
+        <v>700010132</v>
       </c>
       <c r="B213" s="1">
-        <v>700010104</v>
+        <v>700010122</v>
       </c>
       <c r="C213" s="1">
         <v>1</v>
@@ -2972,10 +3002,10 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>700010106</v>
+        <v>700010103</v>
       </c>
       <c r="B214" s="1">
-        <v>700010104</v>
+        <v>700000001</v>
       </c>
       <c r="C214" s="1">
         <v>1</v>
@@ -2983,10 +3013,10 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>700010107</v>
+        <v>700010104</v>
       </c>
       <c r="B215" s="1">
-        <v>700010104</v>
+        <v>700010102</v>
       </c>
       <c r="C215" s="1">
         <v>1</v>
@@ -2994,21 +3024,21 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>700010108</v>
-      </c>
-      <c r="B216" s="6" t="s">
-        <v>14</v>
+        <v>700010105</v>
+      </c>
+      <c r="B216" s="1">
+        <v>700010104</v>
       </c>
       <c r="C216" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>700100101</v>
+        <v>700010106</v>
       </c>
       <c r="B217" s="1">
-        <v>700100001</v>
+        <v>700010104</v>
       </c>
       <c r="C217" s="1">
         <v>1</v>
@@ -3016,10 +3046,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>700100102</v>
+        <v>700010107</v>
       </c>
       <c r="B218" s="1">
-        <v>700100101</v>
+        <v>700010104</v>
       </c>
       <c r="C218" s="1">
         <v>1</v>
@@ -3027,21 +3057,21 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>700100103</v>
-      </c>
-      <c r="B219" s="1">
-        <v>700100001</v>
+        <v>700010108</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="C219" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>700100104</v>
+        <v>700100101</v>
       </c>
       <c r="B220" s="1">
-        <v>700100102</v>
+        <v>700100001</v>
       </c>
       <c r="C220" s="1">
         <v>1</v>
@@ -3049,10 +3079,10 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>700100105</v>
+        <v>700100102</v>
       </c>
       <c r="B221" s="1">
-        <v>700100104</v>
+        <v>700100101</v>
       </c>
       <c r="C221" s="1">
         <v>1</v>
@@ -3060,10 +3090,10 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>700100106</v>
+        <v>700100112</v>
       </c>
       <c r="B222" s="1">
-        <v>700100104</v>
+        <v>700100102</v>
       </c>
       <c r="C222" s="1">
         <v>1</v>
@@ -3071,10 +3101,10 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>700100107</v>
+        <v>700100122</v>
       </c>
       <c r="B223" s="1">
-        <v>700100104</v>
+        <v>700100112</v>
       </c>
       <c r="C223" s="1">
         <v>1</v>
@@ -3082,21 +3112,21 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>700100108</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>15</v>
+        <v>700100132</v>
+      </c>
+      <c r="B224" s="1">
+        <v>700100122</v>
       </c>
       <c r="C224" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>700200101</v>
+        <v>700100103</v>
       </c>
       <c r="B225" s="1">
-        <v>700200001</v>
+        <v>700100001</v>
       </c>
       <c r="C225" s="1">
         <v>1</v>
@@ -3104,10 +3134,10 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>700200102</v>
+        <v>700100104</v>
       </c>
       <c r="B226" s="1">
-        <v>700200101</v>
+        <v>700100102</v>
       </c>
       <c r="C226" s="1">
         <v>1</v>
@@ -3115,10 +3145,10 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>700200103</v>
+        <v>700100105</v>
       </c>
       <c r="B227" s="1">
-        <v>700200001</v>
+        <v>700100104</v>
       </c>
       <c r="C227" s="1">
         <v>1</v>
@@ -3126,10 +3156,10 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>700200104</v>
+        <v>700100106</v>
       </c>
       <c r="B228" s="1">
-        <v>700200102</v>
+        <v>700100104</v>
       </c>
       <c r="C228" s="1">
         <v>1</v>
@@ -3137,10 +3167,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>700200105</v>
+        <v>700100107</v>
       </c>
       <c r="B229" s="1">
-        <v>700200104</v>
+        <v>700100104</v>
       </c>
       <c r="C229" s="1">
         <v>1</v>
@@ -3148,21 +3178,21 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>700200106</v>
-      </c>
-      <c r="B230" s="1">
-        <v>700200104</v>
+        <v>700100108</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="C230" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>700200107</v>
+        <v>700200101</v>
       </c>
       <c r="B231" s="1">
-        <v>700200104</v>
+        <v>700200001</v>
       </c>
       <c r="C231" s="1">
         <v>1</v>
@@ -3170,21 +3200,21 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>700200108</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>16</v>
+        <v>700200102</v>
+      </c>
+      <c r="B232" s="1">
+        <v>700200101</v>
       </c>
       <c r="C232" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>700400002</v>
+        <v>700200112</v>
       </c>
       <c r="B233" s="1">
-        <v>700400001</v>
+        <v>700200102</v>
       </c>
       <c r="C233" s="1">
         <v>1</v>
@@ -3192,10 +3222,10 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>700400003</v>
+        <v>700200122</v>
       </c>
       <c r="B234" s="1">
-        <v>700400002</v>
+        <v>700200112</v>
       </c>
       <c r="C234" s="1">
         <v>1</v>
@@ -3203,10 +3233,10 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>700400004</v>
+        <v>700200132</v>
       </c>
       <c r="B235" s="1">
-        <v>700400003</v>
+        <v>700200122</v>
       </c>
       <c r="C235" s="1">
         <v>1</v>
@@ -3214,10 +3244,10 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>700400102</v>
+        <v>700200103</v>
       </c>
       <c r="B236" s="1">
-        <v>700400101</v>
+        <v>700200001</v>
       </c>
       <c r="C236" s="1">
         <v>1</v>
@@ -3225,10 +3255,10 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>700400103</v>
+        <v>700200104</v>
       </c>
       <c r="B237" s="1">
-        <v>700400102</v>
+        <v>700200102</v>
       </c>
       <c r="C237" s="1">
         <v>1</v>
@@ -3236,12 +3266,111 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
+        <v>700200105</v>
+      </c>
+      <c r="B238" s="1">
+        <v>700200104</v>
+      </c>
+      <c r="C238" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A239" s="1">
+        <v>700200106</v>
+      </c>
+      <c r="B239" s="1">
+        <v>700200104</v>
+      </c>
+      <c r="C239" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A240" s="1">
+        <v>700200107</v>
+      </c>
+      <c r="B240" s="1">
+        <v>700200104</v>
+      </c>
+      <c r="C240" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A241" s="1">
+        <v>700200108</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C241" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A242" s="1">
+        <v>700400002</v>
+      </c>
+      <c r="B242" s="1">
+        <v>700400001</v>
+      </c>
+      <c r="C242" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A243" s="1">
+        <v>700400003</v>
+      </c>
+      <c r="B243" s="1">
+        <v>700400002</v>
+      </c>
+      <c r="C243" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A244" s="1">
+        <v>700400004</v>
+      </c>
+      <c r="B244" s="1">
+        <v>700400003</v>
+      </c>
+      <c r="C244" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A245" s="1">
+        <v>700400102</v>
+      </c>
+      <c r="B245" s="1">
+        <v>700400101</v>
+      </c>
+      <c r="C245" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A246" s="1">
+        <v>700400103</v>
+      </c>
+      <c r="B246" s="1">
+        <v>700400102</v>
+      </c>
+      <c r="C246" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A247" s="1">
         <v>700400104</v>
       </c>
-      <c r="B238" s="1">
+      <c r="B247" s="1">
         <v>700400103</v>
       </c>
-      <c r="C238" s="1">
+      <c r="C247" s="1">
         <v>1</v>
       </c>
     </row>
@@ -3253,33 +3382,42 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B139">
+    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B140">
+    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B141">
     <cfRule type="duplicateValues" dxfId="9" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B139">
+  <conditionalFormatting sqref="B142">
     <cfRule type="duplicateValues" dxfId="8" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B140">
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
+  <conditionalFormatting sqref="B204:B205 B207:B208">
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+  <conditionalFormatting sqref="B242:B244">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+  <conditionalFormatting sqref="B245">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B204:B205 B207:B208">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+  <conditionalFormatting sqref="B246:B247">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B211:B213">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B222:B224">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233:B235">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B237:B238">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0C1592-BEA7-4065-B99E-3E6340D9D9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E36B80-46CD-440C-995E-F70E00879EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_front_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="22">
   <si>
     <t>词条组id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -99,6 +99,26 @@
   </si>
   <si>
     <t>700200105,700200106,700200107</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>affix_group_num</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>词条前置所需词条组id:总数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7002:8</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -175,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -187,6 +207,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -652,23 +678,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:C247"/>
+  <dimension ref="A1:D247"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="12.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -678,8 +705,11 @@
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D2" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -689,8 +719,11 @@
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D3" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -700,8 +733,11 @@
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D4" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1010201</v>
       </c>
@@ -711,8 +747,11 @@
       <c r="C5" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D5" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>1010202</v>
       </c>
@@ -722,8 +761,11 @@
       <c r="C6" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D6" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>1010203</v>
       </c>
@@ -733,8 +775,11 @@
       <c r="C7" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D7" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>1010204</v>
       </c>
@@ -744,8 +789,11 @@
       <c r="C8" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D8" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>1010501</v>
       </c>
@@ -755,8 +803,11 @@
       <c r="C9" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D9" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>1010502</v>
       </c>
@@ -766,8 +817,11 @@
       <c r="C10" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D10" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>1010503</v>
       </c>
@@ -777,8 +831,11 @@
       <c r="C11" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D11" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>1010504</v>
       </c>
@@ -788,8 +845,11 @@
       <c r="C12" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D12" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>1010701</v>
       </c>
@@ -799,8 +859,11 @@
       <c r="C13" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D13" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>1010702</v>
       </c>
@@ -810,8 +873,11 @@
       <c r="C14" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D14" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>1010703</v>
       </c>
@@ -821,8 +887,11 @@
       <c r="C15" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D15" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>1010704</v>
       </c>
@@ -832,8 +901,11 @@
       <c r="C16" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D16" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>1010801</v>
       </c>
@@ -843,8 +915,11 @@
       <c r="C17" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D17" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>1010802</v>
       </c>
@@ -854,8 +929,11 @@
       <c r="C18" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D18" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>1010803</v>
       </c>
@@ -865,8 +943,11 @@
       <c r="C19" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D19" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>1010804</v>
       </c>
@@ -876,8 +957,11 @@
       <c r="C20" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D20" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>1011001</v>
       </c>
@@ -887,8 +971,11 @@
       <c r="C21" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D21" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>1011002</v>
       </c>
@@ -898,8 +985,11 @@
       <c r="C22" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D22" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>1011003</v>
       </c>
@@ -909,8 +999,11 @@
       <c r="C23" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D23" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>1011004</v>
       </c>
@@ -920,8 +1013,11 @@
       <c r="C24" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D24" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>1011101</v>
       </c>
@@ -931,8 +1027,11 @@
       <c r="C25" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D25" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>1011102</v>
       </c>
@@ -942,8 +1041,11 @@
       <c r="C26" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D26" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>1011103</v>
       </c>
@@ -953,8 +1055,11 @@
       <c r="C27" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D27" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>1011104</v>
       </c>
@@ -964,8 +1069,11 @@
       <c r="C28" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D28" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>1011201</v>
       </c>
@@ -975,8 +1083,11 @@
       <c r="C29" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D29" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>1011202</v>
       </c>
@@ -986,8 +1097,11 @@
       <c r="C30" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D30" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>1011203</v>
       </c>
@@ -997,8 +1111,11 @@
       <c r="C31" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D31" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>1011204</v>
       </c>
@@ -1008,8 +1125,11 @@
       <c r="C32" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D32" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>2010101</v>
       </c>
@@ -1019,8 +1139,11 @@
       <c r="C33" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D33" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>2010102</v>
       </c>
@@ -1030,8 +1153,11 @@
       <c r="C34" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D34" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>2010103</v>
       </c>
@@ -1041,8 +1167,11 @@
       <c r="C35" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D35" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>2010104</v>
       </c>
@@ -1052,8 +1181,11 @@
       <c r="C36" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D36" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>2010301</v>
       </c>
@@ -1063,8 +1195,11 @@
       <c r="C37" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D37" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>2010302</v>
       </c>
@@ -1074,8 +1209,11 @@
       <c r="C38" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D38" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>2010303</v>
       </c>
@@ -1085,8 +1223,11 @@
       <c r="C39" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D39" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>2010304</v>
       </c>
@@ -1096,8 +1237,11 @@
       <c r="C40" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D40" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>2010401</v>
       </c>
@@ -1107,8 +1251,11 @@
       <c r="C41" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D41" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>2010402</v>
       </c>
@@ -1118,8 +1265,11 @@
       <c r="C42" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D42" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>2010403</v>
       </c>
@@ -1129,8 +1279,11 @@
       <c r="C43" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D43" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>2010404</v>
       </c>
@@ -1140,8 +1293,11 @@
       <c r="C44" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D44" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>3010101</v>
       </c>
@@ -1151,8 +1307,11 @@
       <c r="C45" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D45" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>3010102</v>
       </c>
@@ -1162,8 +1321,11 @@
       <c r="C46" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D46" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>3010103</v>
       </c>
@@ -1173,8 +1335,11 @@
       <c r="C47" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D47" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>3010104</v>
       </c>
@@ -1184,8 +1349,11 @@
       <c r="C48" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D48" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>3010301</v>
       </c>
@@ -1195,8 +1363,11 @@
       <c r="C49" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D49" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>3010302</v>
       </c>
@@ -1206,8 +1377,11 @@
       <c r="C50" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D50" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>3010303</v>
       </c>
@@ -1217,8 +1391,11 @@
       <c r="C51" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D51" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>3010304</v>
       </c>
@@ -1228,8 +1405,11 @@
       <c r="C52" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D52" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>3010401</v>
       </c>
@@ -1239,8 +1419,11 @@
       <c r="C53" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D53" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>3010402</v>
       </c>
@@ -1250,8 +1433,11 @@
       <c r="C54" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D54" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>3010403</v>
       </c>
@@ -1261,8 +1447,11 @@
       <c r="C55" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D55" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>3010404</v>
       </c>
@@ -1272,8 +1461,11 @@
       <c r="C56" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D56" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>4010101</v>
       </c>
@@ -1283,8 +1475,11 @@
       <c r="C57" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D57" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>4010102</v>
       </c>
@@ -1294,8 +1489,11 @@
       <c r="C58" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D58" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>4010103</v>
       </c>
@@ -1305,8 +1503,11 @@
       <c r="C59" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D59" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>4010104</v>
       </c>
@@ -1316,8 +1517,11 @@
       <c r="C60" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D60" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>4010301</v>
       </c>
@@ -1327,8 +1531,11 @@
       <c r="C61" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D61" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>4010302</v>
       </c>
@@ -1338,8 +1545,11 @@
       <c r="C62" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D62" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>4010303</v>
       </c>
@@ -1349,8 +1559,11 @@
       <c r="C63" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D63" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>4010304</v>
       </c>
@@ -1360,8 +1573,11 @@
       <c r="C64" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D64" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>4010401</v>
       </c>
@@ -1371,8 +1587,11 @@
       <c r="C65" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D65" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>4010402</v>
       </c>
@@ -1382,8 +1601,11 @@
       <c r="C66" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D66" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>4010403</v>
       </c>
@@ -1393,8 +1615,11 @@
       <c r="C67" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D67" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>4010404</v>
       </c>
@@ -1404,8 +1629,11 @@
       <c r="C68" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D68" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>5010101</v>
       </c>
@@ -1415,8 +1643,11 @@
       <c r="C69" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D69" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>5010102</v>
       </c>
@@ -1426,8 +1657,11 @@
       <c r="C70" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D70" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>5010103</v>
       </c>
@@ -1437,8 +1671,11 @@
       <c r="C71" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D71" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>5010104</v>
       </c>
@@ -1448,8 +1685,11 @@
       <c r="C72" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D72" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>5010301</v>
       </c>
@@ -1459,8 +1699,11 @@
       <c r="C73" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D73" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>5010302</v>
       </c>
@@ -1470,8 +1713,11 @@
       <c r="C74" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D74" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>5010303</v>
       </c>
@@ -1481,8 +1727,11 @@
       <c r="C75" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D75" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>5010304</v>
       </c>
@@ -1492,8 +1741,11 @@
       <c r="C76" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D76" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>5010401</v>
       </c>
@@ -1503,8 +1755,11 @@
       <c r="C77" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D77" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>5010402</v>
       </c>
@@ -1514,8 +1769,11 @@
       <c r="C78" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D78" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>5010403</v>
       </c>
@@ -1525,8 +1783,11 @@
       <c r="C79" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D79" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>5010404</v>
       </c>
@@ -1536,8 +1797,11 @@
       <c r="C80" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D80" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>9000101</v>
       </c>
@@ -1547,8 +1811,11 @@
       <c r="C81" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D81" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>9000102</v>
       </c>
@@ -1558,8 +1825,11 @@
       <c r="C82" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D82" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>9000103</v>
       </c>
@@ -1569,8 +1839,11 @@
       <c r="C83" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D83" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>906010202</v>
       </c>
@@ -1580,8 +1853,11 @@
       <c r="C84" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D84" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>906010403</v>
       </c>
@@ -1591,8 +1867,11 @@
       <c r="C85" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D85" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>20101</v>
       </c>
@@ -1602,8 +1881,11 @@
       <c r="C86" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D86" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>30101</v>
       </c>
@@ -1613,8 +1895,11 @@
       <c r="C87" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D87" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>40101</v>
       </c>
@@ -1624,8 +1909,11 @@
       <c r="C88" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D88" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>50101</v>
       </c>
@@ -1635,8 +1923,11 @@
       <c r="C89" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D89" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>1010901</v>
       </c>
@@ -1646,8 +1937,11 @@
       <c r="C90" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D90" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>10109011</v>
       </c>
@@ -1657,8 +1951,11 @@
       <c r="C91" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D91" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>10109012</v>
       </c>
@@ -1668,8 +1965,11 @@
       <c r="C92" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D92" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>1010902</v>
       </c>
@@ -1679,8 +1979,11 @@
       <c r="C93" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D93" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>1010903</v>
       </c>
@@ -1690,8 +1993,11 @@
       <c r="C94" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D94" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>1010904</v>
       </c>
@@ -1701,8 +2007,11 @@
       <c r="C95" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D95" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>1010905</v>
       </c>
@@ -1712,8 +2021,11 @@
       <c r="C96" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D96" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>1010906</v>
       </c>
@@ -1723,8 +2035,11 @@
       <c r="C97" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D97" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>1010907</v>
       </c>
@@ -1734,8 +2049,11 @@
       <c r="C98" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D98" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>1010908</v>
       </c>
@@ -1745,8 +2063,11 @@
       <c r="C99" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D99" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>1010909</v>
       </c>
@@ -1756,8 +2077,11 @@
       <c r="C100" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D100" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>1010910</v>
       </c>
@@ -1767,8 +2091,11 @@
       <c r="C101" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D101" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>905010202</v>
       </c>
@@ -1778,8 +2105,11 @@
       <c r="C102" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D102" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>905010302</v>
       </c>
@@ -1789,8 +2119,11 @@
       <c r="C103" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D103" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>905010403</v>
       </c>
@@ -1800,8 +2133,11 @@
       <c r="C104" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D104" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>905010503</v>
       </c>
@@ -1811,8 +2147,11 @@
       <c r="C105" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D105" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>905010604</v>
       </c>
@@ -1822,8 +2161,11 @@
       <c r="C106" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D106" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>905010704</v>
       </c>
@@ -1833,8 +2175,11 @@
       <c r="C107" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D107" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>905010805</v>
       </c>
@@ -1844,8 +2189,11 @@
       <c r="C108" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D108" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>901010202</v>
       </c>
@@ -1855,8 +2203,11 @@
       <c r="C109" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D109" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>901010302</v>
       </c>
@@ -1866,8 +2217,11 @@
       <c r="C110" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D110" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>901010403</v>
       </c>
@@ -1877,8 +2231,11 @@
       <c r="C111" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D111" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>901010503</v>
       </c>
@@ -1888,8 +2245,11 @@
       <c r="C112" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D112" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>901010604</v>
       </c>
@@ -1899,8 +2259,11 @@
       <c r="C113" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D113" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>901010704</v>
       </c>
@@ -1910,8 +2273,11 @@
       <c r="C114" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D114" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>901010805</v>
       </c>
@@ -1921,8 +2287,11 @@
       <c r="C115" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D115" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>902010202</v>
       </c>
@@ -1932,8 +2301,11 @@
       <c r="C116" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D116" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>902010302</v>
       </c>
@@ -1943,8 +2315,11 @@
       <c r="C117" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D117" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>902010403</v>
       </c>
@@ -1954,8 +2329,11 @@
       <c r="C118" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D118" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>902010503</v>
       </c>
@@ -1965,8 +2343,11 @@
       <c r="C119" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D119" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>902010604</v>
       </c>
@@ -1976,8 +2357,11 @@
       <c r="C120" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D120" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>902010704</v>
       </c>
@@ -1987,8 +2371,11 @@
       <c r="C121" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D121" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>902010805</v>
       </c>
@@ -1998,8 +2385,11 @@
       <c r="C122" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D122" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>903010202</v>
       </c>
@@ -2009,8 +2399,11 @@
       <c r="C123" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D123" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>903010302</v>
       </c>
@@ -2020,8 +2413,11 @@
       <c r="C124" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D124" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>903010403</v>
       </c>
@@ -2031,8 +2427,11 @@
       <c r="C125" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D125" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>903010503</v>
       </c>
@@ -2042,8 +2441,11 @@
       <c r="C126" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D126" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>903010604</v>
       </c>
@@ -2053,8 +2455,11 @@
       <c r="C127" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D127" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>903010704</v>
       </c>
@@ -2064,8 +2469,11 @@
       <c r="C128" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D128" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>903010805</v>
       </c>
@@ -2075,8 +2483,11 @@
       <c r="C129" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D129" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>900010202</v>
       </c>
@@ -2086,8 +2497,11 @@
       <c r="C130" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D130" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>900010302</v>
       </c>
@@ -2097,8 +2511,11 @@
       <c r="C131" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D131" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>900010403</v>
       </c>
@@ -2108,8 +2525,11 @@
       <c r="C132" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D132" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>900010503</v>
       </c>
@@ -2119,8 +2539,11 @@
       <c r="C133" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D133" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>900010604</v>
       </c>
@@ -2130,8 +2553,11 @@
       <c r="C134" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D134" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>900010704</v>
       </c>
@@ -2141,8 +2567,11 @@
       <c r="C135" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D135" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>900010805</v>
       </c>
@@ -2152,8 +2581,11 @@
       <c r="C136" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D136" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>900020202</v>
       </c>
@@ -2163,8 +2595,11 @@
       <c r="C137" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D137" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>900020302</v>
       </c>
@@ -2174,8 +2609,11 @@
       <c r="C138" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D138" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>900020403</v>
       </c>
@@ -2185,8 +2623,11 @@
       <c r="C139" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D139" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>900020503</v>
       </c>
@@ -2196,8 +2637,11 @@
       <c r="C140" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D140" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>900020604</v>
       </c>
@@ -2207,8 +2651,11 @@
       <c r="C141" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D141" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>900020704</v>
       </c>
@@ -2218,8 +2665,11 @@
       <c r="C142" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D142" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>900020805</v>
       </c>
@@ -2229,8 +2679,11 @@
       <c r="C143" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D143" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>901020202</v>
       </c>
@@ -2240,8 +2693,11 @@
       <c r="C144" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D144" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>901020302</v>
       </c>
@@ -2251,8 +2707,11 @@
       <c r="C145" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D145" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>901020403</v>
       </c>
@@ -2262,8 +2721,11 @@
       <c r="C146" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D146" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>901020503</v>
       </c>
@@ -2273,8 +2735,11 @@
       <c r="C147" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D147" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>901020604</v>
       </c>
@@ -2284,8 +2749,11 @@
       <c r="C148" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D148" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>901020704</v>
       </c>
@@ -2295,8 +2763,11 @@
       <c r="C149" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D149" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>901020805</v>
       </c>
@@ -2306,8 +2777,11 @@
       <c r="C150" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D150" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>902020202</v>
       </c>
@@ -2317,8 +2791,11 @@
       <c r="C151" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D151" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>902020302</v>
       </c>
@@ -2328,8 +2805,11 @@
       <c r="C152" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D152" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>902020403</v>
       </c>
@@ -2339,8 +2819,11 @@
       <c r="C153" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D153" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>902020503</v>
       </c>
@@ -2350,8 +2833,11 @@
       <c r="C154" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D154" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>902020604</v>
       </c>
@@ -2361,8 +2847,11 @@
       <c r="C155" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D155" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>902020704</v>
       </c>
@@ -2372,8 +2861,11 @@
       <c r="C156" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D156" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>902020805</v>
       </c>
@@ -2383,8 +2875,11 @@
       <c r="C157" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D157" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>903020202</v>
       </c>
@@ -2394,8 +2889,11 @@
       <c r="C158" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D158" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>903020302</v>
       </c>
@@ -2405,8 +2903,11 @@
       <c r="C159" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D159" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>903020403</v>
       </c>
@@ -2416,8 +2917,11 @@
       <c r="C160" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D160" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>903020503</v>
       </c>
@@ -2427,8 +2931,11 @@
       <c r="C161" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D161" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>903020604</v>
       </c>
@@ -2438,8 +2945,11 @@
       <c r="C162" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D162" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>903020704</v>
       </c>
@@ -2449,8 +2959,11 @@
       <c r="C163" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D163" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>903020805</v>
       </c>
@@ -2460,8 +2973,11 @@
       <c r="C164" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D164" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
         <v>800010101</v>
       </c>
@@ -2471,8 +2987,11 @@
       <c r="C165" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D165" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
         <v>800010102</v>
       </c>
@@ -2482,8 +3001,11 @@
       <c r="C166" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D166" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
         <v>800010201</v>
       </c>
@@ -2493,8 +3015,11 @@
       <c r="C167" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D167" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
         <v>800010202</v>
       </c>
@@ -2504,8 +3029,11 @@
       <c r="C168" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D168" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
         <v>800010301</v>
       </c>
@@ -2515,8 +3043,11 @@
       <c r="C169" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D169" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
         <v>800010302</v>
       </c>
@@ -2526,8 +3057,11 @@
       <c r="C170" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D170" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
         <v>800030101</v>
       </c>
@@ -2537,8 +3071,11 @@
       <c r="C171" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D171" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
         <v>800030102</v>
       </c>
@@ -2548,8 +3085,11 @@
       <c r="C172" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D172" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
         <v>800030201</v>
       </c>
@@ -2559,8 +3099,11 @@
       <c r="C173" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D173" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
         <v>800030202</v>
       </c>
@@ -2570,8 +3113,11 @@
       <c r="C174" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D174" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
         <v>800110101</v>
       </c>
@@ -2581,8 +3127,11 @@
       <c r="C175" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D175" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
         <v>800110102</v>
       </c>
@@ -2592,8 +3141,11 @@
       <c r="C176" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D176" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
         <v>800110201</v>
       </c>
@@ -2603,8 +3155,11 @@
       <c r="C177" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D177" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
         <v>800110202</v>
       </c>
@@ -2614,8 +3169,11 @@
       <c r="C178" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D178" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
         <v>800110301</v>
       </c>
@@ -2625,8 +3183,11 @@
       <c r="C179" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D179" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
         <v>800110302</v>
       </c>
@@ -2636,8 +3197,11 @@
       <c r="C180" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D180" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
         <v>800130101</v>
       </c>
@@ -2647,8 +3211,11 @@
       <c r="C181" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D181" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
         <v>800130102</v>
       </c>
@@ -2658,8 +3225,11 @@
       <c r="C182" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D182" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
         <v>800130201</v>
       </c>
@@ -2669,8 +3239,11 @@
       <c r="C183" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D183" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
         <v>800130202</v>
       </c>
@@ -2680,8 +3253,11 @@
       <c r="C184" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D184" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
         <v>800210101</v>
       </c>
@@ -2691,8 +3267,11 @@
       <c r="C185" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D185" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
         <v>800210102</v>
       </c>
@@ -2702,8 +3281,11 @@
       <c r="C186" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D186" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
         <v>800210201</v>
       </c>
@@ -2713,8 +3295,11 @@
       <c r="C187" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D187" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
         <v>800210202</v>
       </c>
@@ -2724,8 +3309,11 @@
       <c r="C188" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D188" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
         <v>800210301</v>
       </c>
@@ -2735,8 +3323,11 @@
       <c r="C189" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D189" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
         <v>800210302</v>
       </c>
@@ -2746,8 +3337,11 @@
       <c r="C190" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D190" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
         <v>800230101</v>
       </c>
@@ -2757,8 +3351,11 @@
       <c r="C191" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D191" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
         <v>800230102</v>
       </c>
@@ -2768,8 +3365,11 @@
       <c r="C192" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D192" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
         <v>800230201</v>
       </c>
@@ -2779,8 +3379,11 @@
       <c r="C193" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D193" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
         <v>800230202</v>
       </c>
@@ -2790,8 +3393,11 @@
       <c r="C194" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D194" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
         <v>801100102</v>
       </c>
@@ -2801,8 +3407,11 @@
       <c r="C195" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D195" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
         <v>801100103</v>
       </c>
@@ -2812,8 +3421,11 @@
       <c r="C196" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D196" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
         <v>801100201</v>
       </c>
@@ -2823,8 +3435,11 @@
       <c r="C197" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D197" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
         <v>801100202</v>
       </c>
@@ -2834,8 +3449,11 @@
       <c r="C198" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D198" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
         <v>801100203</v>
       </c>
@@ -2845,8 +3463,11 @@
       <c r="C199" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D199" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
         <v>801100301</v>
       </c>
@@ -2856,8 +3477,11 @@
       <c r="C200" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D200" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
         <v>801100302</v>
       </c>
@@ -2867,8 +3491,11 @@
       <c r="C201" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D201" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
         <v>801100303</v>
       </c>
@@ -2878,8 +3505,11 @@
       <c r="C202" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D202" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
         <v>801200101</v>
       </c>
@@ -2889,8 +3519,11 @@
       <c r="C203" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D203" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
         <v>801200102</v>
       </c>
@@ -2900,8 +3533,11 @@
       <c r="C204" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D204" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
         <v>801200103</v>
       </c>
@@ -2911,8 +3547,11 @@
       <c r="C205" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D205" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
         <v>801200201</v>
       </c>
@@ -2922,8 +3561,11 @@
       <c r="C206" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D206" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
         <v>801200202</v>
       </c>
@@ -2933,8 +3575,11 @@
       <c r="C207" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D207" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
         <v>801200203</v>
       </c>
@@ -2944,8 +3589,11 @@
       <c r="C208" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D208" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
         <v>700010101</v>
       </c>
@@ -2955,8 +3603,11 @@
       <c r="C209" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D209" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
         <v>700010102</v>
       </c>
@@ -2966,8 +3617,11 @@
       <c r="C210" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D210" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
         <v>700010112</v>
       </c>
@@ -2977,8 +3631,11 @@
       <c r="C211" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D211" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
         <v>700010122</v>
       </c>
@@ -2988,8 +3645,11 @@
       <c r="C212" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D212" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
         <v>700010132</v>
       </c>
@@ -2999,8 +3659,11 @@
       <c r="C213" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D213" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
         <v>700010103</v>
       </c>
@@ -3010,8 +3673,11 @@
       <c r="C214" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D214" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
         <v>700010104</v>
       </c>
@@ -3021,8 +3687,11 @@
       <c r="C215" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D215" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
         <v>700010105</v>
       </c>
@@ -3032,8 +3701,11 @@
       <c r="C216" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D216" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
         <v>700010106</v>
       </c>
@@ -3043,8 +3715,11 @@
       <c r="C217" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D217" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
         <v>700010107</v>
       </c>
@@ -3054,8 +3729,11 @@
       <c r="C218" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D218" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
         <v>700010108</v>
       </c>
@@ -3065,8 +3743,11 @@
       <c r="C219" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D219" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
         <v>700100101</v>
       </c>
@@ -3076,8 +3757,11 @@
       <c r="C220" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D220" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
         <v>700100102</v>
       </c>
@@ -3087,8 +3771,11 @@
       <c r="C221" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D221" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
         <v>700100112</v>
       </c>
@@ -3098,8 +3785,11 @@
       <c r="C222" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D222" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
         <v>700100122</v>
       </c>
@@ -3109,8 +3799,11 @@
       <c r="C223" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D223" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
         <v>700100132</v>
       </c>
@@ -3120,8 +3813,11 @@
       <c r="C224" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D224" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
         <v>700100103</v>
       </c>
@@ -3131,8 +3827,11 @@
       <c r="C225" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D225" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
         <v>700100104</v>
       </c>
@@ -3142,8 +3841,11 @@
       <c r="C226" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D226" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
         <v>700100105</v>
       </c>
@@ -3153,8 +3855,11 @@
       <c r="C227" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D227" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
         <v>700100106</v>
       </c>
@@ -3164,8 +3869,11 @@
       <c r="C228" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D228" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
         <v>700100107</v>
       </c>
@@ -3175,8 +3883,11 @@
       <c r="C229" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D229" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
         <v>700100108</v>
       </c>
@@ -3186,8 +3897,11 @@
       <c r="C230" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D230" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
         <v>700200101</v>
       </c>
@@ -3197,8 +3911,11 @@
       <c r="C231" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D231" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
         <v>700200102</v>
       </c>
@@ -3208,8 +3925,11 @@
       <c r="C232" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D232" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
         <v>700200112</v>
       </c>
@@ -3219,8 +3939,11 @@
       <c r="C233" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D233" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
         <v>700200122</v>
       </c>
@@ -3230,8 +3953,11 @@
       <c r="C234" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D234" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
         <v>700200132</v>
       </c>
@@ -3241,8 +3967,11 @@
       <c r="C235" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D235" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
         <v>700200103</v>
       </c>
@@ -3252,8 +3981,11 @@
       <c r="C236" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D236" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
         <v>700200104</v>
       </c>
@@ -3263,8 +3995,11 @@
       <c r="C237" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D237" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
         <v>700200105</v>
       </c>
@@ -3274,8 +4009,11 @@
       <c r="C238" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D238" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
         <v>700200106</v>
       </c>
@@ -3285,8 +4023,11 @@
       <c r="C239" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D239" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
         <v>700200107</v>
       </c>
@@ -3296,8 +4037,11 @@
       <c r="C240" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D240" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
         <v>700200108</v>
       </c>
@@ -3307,8 +4051,11 @@
       <c r="C241" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D241" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
         <v>700400002</v>
       </c>
@@ -3318,8 +4065,11 @@
       <c r="C242" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D242" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
         <v>700400003</v>
       </c>
@@ -3329,8 +4079,11 @@
       <c r="C243" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D243" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
         <v>700400004</v>
       </c>
@@ -3340,8 +4093,11 @@
       <c r="C244" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D244" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
         <v>700400102</v>
       </c>
@@ -3351,8 +4107,11 @@
       <c r="C245" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D245" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
         <v>700400103</v>
       </c>
@@ -3362,8 +4121,11 @@
       <c r="C246" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="D246" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
         <v>700400104</v>
       </c>
@@ -3373,13 +4135,11 @@
       <c r="C247" s="1">
         <v>1</v>
       </c>
+      <c r="D247" s="8" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C4" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:C5">
-      <sortCondition ref="B4"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="12" priority="17"/>
@@ -3402,23 +4162,23 @@
   <conditionalFormatting sqref="B204:B205 B207:B208">
     <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B211:B213">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B222:B224">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B233:B235">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B242:B244">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246:B247">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B211:B213">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B222:B224">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B233:B235">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E36B80-46CD-440C-995E-F70E00879EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64CD0CD-9122-410A-9F93-C4E3C97B9D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="32">
   <si>
     <t>词条组id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -119,6 +119,43 @@
   </si>
   <si>
     <t>7002:8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600100101,600100102</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6001:4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6001:7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6001:12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600100302,600100303</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6002:4</t>
+  </si>
+  <si>
+    <t>6002:7</t>
+  </si>
+  <si>
+    <t>6002:12</t>
+  </si>
+  <si>
+    <t>600200301,600200302</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600200302,600100203</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -217,7 +254,67 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -678,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:D247"/>
+  <dimension ref="A1:D269"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -4139,46 +4236,363 @@
         <v>20</v>
       </c>
     </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A248" s="1">
+        <v>600100101</v>
+      </c>
+      <c r="B248" s="1">
+        <v>600100001</v>
+      </c>
+      <c r="C248" s="1">
+        <v>1</v>
+      </c>
+      <c r="D248" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A249" s="1">
+        <v>600100102</v>
+      </c>
+      <c r="B249" s="1">
+        <v>600100001</v>
+      </c>
+      <c r="C249" s="1">
+        <v>1</v>
+      </c>
+      <c r="D249" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A250" s="1">
+        <v>600100103</v>
+      </c>
+      <c r="B250" s="1">
+        <v>600100001</v>
+      </c>
+      <c r="C250" s="1">
+        <v>1</v>
+      </c>
+      <c r="D250" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A251" s="1">
+        <v>600100201</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C251" s="1">
+        <v>1</v>
+      </c>
+      <c r="D251" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A252" s="1">
+        <v>600100202</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C252" s="1">
+        <v>1</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A253" s="1">
+        <v>600100203</v>
+      </c>
+      <c r="B253" s="1">
+        <v>600100103</v>
+      </c>
+      <c r="C253" s="1">
+        <v>1</v>
+      </c>
+      <c r="D253" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A254" s="1">
+        <v>600100301</v>
+      </c>
+      <c r="B254" s="1">
+        <v>600100202</v>
+      </c>
+      <c r="C254" s="1">
+        <v>1</v>
+      </c>
+      <c r="D254" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A255" s="1">
+        <v>600100302</v>
+      </c>
+      <c r="B255" s="1">
+        <v>600100202</v>
+      </c>
+      <c r="C255" s="1">
+        <v>1</v>
+      </c>
+      <c r="D255" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A256" s="1">
+        <v>600100303</v>
+      </c>
+      <c r="B256" s="1">
+        <v>600100203</v>
+      </c>
+      <c r="C256" s="1">
+        <v>1</v>
+      </c>
+      <c r="D256" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A257" s="1">
+        <v>600100401</v>
+      </c>
+      <c r="B257" s="1">
+        <v>600100302</v>
+      </c>
+      <c r="C257" s="1">
+        <v>1</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A258" s="1">
+        <v>600100501</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C258" s="1">
+        <v>1</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A259" s="1">
+        <v>600200101</v>
+      </c>
+      <c r="B259" s="1">
+        <v>600200001</v>
+      </c>
+      <c r="C259" s="1">
+        <v>1</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A260" s="1">
+        <v>600200102</v>
+      </c>
+      <c r="B260" s="1">
+        <v>600200001</v>
+      </c>
+      <c r="C260" s="1">
+        <v>1</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A261" s="1">
+        <v>600200103</v>
+      </c>
+      <c r="B261" s="1">
+        <v>600200001</v>
+      </c>
+      <c r="C261" s="1">
+        <v>1</v>
+      </c>
+      <c r="D261" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A262" s="1">
+        <v>600200201</v>
+      </c>
+      <c r="B262" s="1">
+        <v>600200102</v>
+      </c>
+      <c r="C262" s="1">
+        <v>1</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A263" s="1">
+        <v>600200202</v>
+      </c>
+      <c r="B263" s="1">
+        <v>600200102</v>
+      </c>
+      <c r="C263" s="1">
+        <v>1</v>
+      </c>
+      <c r="D263" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A264" s="1">
+        <v>600200203</v>
+      </c>
+      <c r="B264" s="1">
+        <v>600200103</v>
+      </c>
+      <c r="C264" s="1">
+        <v>1</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A265" s="1">
+        <v>600200301</v>
+      </c>
+      <c r="B265" s="1">
+        <v>600200202</v>
+      </c>
+      <c r="C265" s="1">
+        <v>1</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A266" s="1">
+        <v>600200302</v>
+      </c>
+      <c r="B266" s="1">
+        <v>600200202</v>
+      </c>
+      <c r="C266" s="1">
+        <v>1</v>
+      </c>
+      <c r="D266" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A267" s="1">
+        <v>600200303</v>
+      </c>
+      <c r="B267" s="1">
+        <v>600200203</v>
+      </c>
+      <c r="C267" s="1">
+        <v>1</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A268" s="1">
+        <v>600200401</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C268" s="1">
+        <v>1</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A269" s="1">
+        <v>600200501</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C269" s="1">
+        <v>1</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204:B205 B207:B208">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211:B213">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B222:B224">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233:B235">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B242:B244">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246:B247">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B253">
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B256">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B264">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64CD0CD-9122-410A-9F93-C4E3C97B9D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE89599-A36A-4562-8FB1-5383D621651A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_front_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="66">
   <si>
     <t>词条组id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -156,6 +156,112 @@
   </si>
   <si>
     <t>600200302,600100203</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600300101,600300102</t>
+  </si>
+  <si>
+    <t>6003:4</t>
+  </si>
+  <si>
+    <t>6003:7</t>
+  </si>
+  <si>
+    <t>600300302,600300303</t>
+  </si>
+  <si>
+    <t>6003:12</t>
+  </si>
+  <si>
+    <t>6004:4</t>
+  </si>
+  <si>
+    <t>600400301,600400302</t>
+  </si>
+  <si>
+    <t>6004:7</t>
+  </si>
+  <si>
+    <t>600400302,600300203</t>
+  </si>
+  <si>
+    <t>6004:12</t>
+  </si>
+  <si>
+    <t>6006:4</t>
+  </si>
+  <si>
+    <t>600600301,600600302</t>
+  </si>
+  <si>
+    <t>6006:7</t>
+  </si>
+  <si>
+    <t>600600302,600100203</t>
+  </si>
+  <si>
+    <t>6006:12</t>
+  </si>
+  <si>
+    <t>600500101,600500102</t>
+  </si>
+  <si>
+    <t>6005:4</t>
+  </si>
+  <si>
+    <t>6005:7</t>
+  </si>
+  <si>
+    <t>600500302,600500303</t>
+  </si>
+  <si>
+    <t>6005:12</t>
+  </si>
+  <si>
+    <t>600700101,600700102</t>
+  </si>
+  <si>
+    <t>6007:4</t>
+  </si>
+  <si>
+    <t>6007:7</t>
+  </si>
+  <si>
+    <t>600700302,600700303</t>
+  </si>
+  <si>
+    <t>6007:12</t>
+  </si>
+  <si>
+    <t>6008:4</t>
+  </si>
+  <si>
+    <t>600800301,600800302</t>
+  </si>
+  <si>
+    <t>6008:7</t>
+  </si>
+  <si>
+    <t>600800302,600700203</t>
+  </si>
+  <si>
+    <t>6008:12</t>
+  </si>
+  <si>
+    <t>600100301,600100302</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600300301,600300302</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600500301,600500302</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600700301,600700302</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -254,7 +360,187 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -775,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:D269"/>
+  <dimension ref="A1:D339"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -4366,8 +4652,8 @@
       <c r="A257" s="1">
         <v>600100401</v>
       </c>
-      <c r="B257" s="1">
-        <v>600100302</v>
+      <c r="B257" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="C257" s="1">
         <v>1</v>
@@ -4420,10 +4706,10 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>600200103</v>
+        <v>600200112</v>
       </c>
       <c r="B261" s="1">
-        <v>600200001</v>
+        <v>600200102</v>
       </c>
       <c r="C261" s="1">
         <v>1</v>
@@ -4434,10 +4720,10 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>600200201</v>
+        <v>600200103</v>
       </c>
       <c r="B262" s="1">
-        <v>600200102</v>
+        <v>600200001</v>
       </c>
       <c r="C262" s="1">
         <v>1</v>
@@ -4448,7 +4734,7 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>600200202</v>
+        <v>600200201</v>
       </c>
       <c r="B263" s="1">
         <v>600200102</v>
@@ -4462,10 +4748,10 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>600200203</v>
+        <v>600200202</v>
       </c>
       <c r="B264" s="1">
-        <v>600200103</v>
+        <v>600200102</v>
       </c>
       <c r="C264" s="1">
         <v>1</v>
@@ -4476,21 +4762,21 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>600200301</v>
+        <v>600200203</v>
       </c>
       <c r="B265" s="1">
-        <v>600200202</v>
+        <v>600200103</v>
       </c>
       <c r="C265" s="1">
         <v>1</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>600200302</v>
+        <v>600200301</v>
       </c>
       <c r="B266" s="1">
         <v>600200202</v>
@@ -4504,10 +4790,10 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>600200303</v>
+        <v>600200302</v>
       </c>
       <c r="B267" s="1">
-        <v>600200203</v>
+        <v>600200202</v>
       </c>
       <c r="C267" s="1">
         <v>1</v>
@@ -4518,81 +4804,1100 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>600200401</v>
-      </c>
-      <c r="B268" s="6" t="s">
-        <v>30</v>
+        <v>600200303</v>
+      </c>
+      <c r="B268" s="1">
+        <v>600200203</v>
       </c>
       <c r="C268" s="1">
         <v>1</v>
       </c>
       <c r="D268" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
+        <v>600200401</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C269" s="1">
+        <v>1</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A270" s="1">
         <v>600200501</v>
       </c>
-      <c r="B269" s="6" t="s">
+      <c r="B270" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C269" s="1">
-        <v>1</v>
-      </c>
-      <c r="D269" s="8" t="s">
+      <c r="C270" s="1">
+        <v>1</v>
+      </c>
+      <c r="D270" s="8" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A271" s="1">
+        <v>600300101</v>
+      </c>
+      <c r="B271" s="1">
+        <v>600300001</v>
+      </c>
+      <c r="C271" s="1">
+        <v>1</v>
+      </c>
+      <c r="D271" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A272" s="1">
+        <v>600300102</v>
+      </c>
+      <c r="B272" s="1">
+        <v>600300001</v>
+      </c>
+      <c r="C272" s="1">
+        <v>1</v>
+      </c>
+      <c r="D272" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A273" s="1">
+        <v>600300103</v>
+      </c>
+      <c r="B273" s="1">
+        <v>600300001</v>
+      </c>
+      <c r="C273" s="1">
+        <v>1</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A274" s="1">
+        <v>600300201</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C274" s="1">
+        <v>1</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A275" s="1">
+        <v>600300202</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C275" s="1">
+        <v>1</v>
+      </c>
+      <c r="D275" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A276" s="1">
+        <v>600300203</v>
+      </c>
+      <c r="B276" s="1">
+        <v>600300103</v>
+      </c>
+      <c r="C276" s="1">
+        <v>1</v>
+      </c>
+      <c r="D276" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A277" s="1">
+        <v>600300301</v>
+      </c>
+      <c r="B277" s="1">
+        <v>600300202</v>
+      </c>
+      <c r="C277" s="1">
+        <v>1</v>
+      </c>
+      <c r="D277" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A278" s="1">
+        <v>600300302</v>
+      </c>
+      <c r="B278" s="1">
+        <v>600300202</v>
+      </c>
+      <c r="C278" s="1">
+        <v>1</v>
+      </c>
+      <c r="D278" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A279" s="1">
+        <v>600300303</v>
+      </c>
+      <c r="B279" s="1">
+        <v>600300203</v>
+      </c>
+      <c r="C279" s="1">
+        <v>1</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A280" s="1">
+        <v>600300401</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C280" s="1">
+        <v>1</v>
+      </c>
+      <c r="D280" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A281" s="1">
+        <v>600300501</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C281" s="1">
+        <v>1</v>
+      </c>
+      <c r="D281" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A282" s="1">
+        <v>600400101</v>
+      </c>
+      <c r="B282" s="1">
+        <v>600400001</v>
+      </c>
+      <c r="C282" s="1">
+        <v>1</v>
+      </c>
+      <c r="D282" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A283" s="1">
+        <v>600400102</v>
+      </c>
+      <c r="B283" s="1">
+        <v>600400001</v>
+      </c>
+      <c r="C283" s="1">
+        <v>1</v>
+      </c>
+      <c r="D283" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A284" s="1">
+        <v>600400112</v>
+      </c>
+      <c r="B284" s="1">
+        <v>600400102</v>
+      </c>
+      <c r="C284" s="1">
+        <v>1</v>
+      </c>
+      <c r="D284" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A285" s="1">
+        <v>600400103</v>
+      </c>
+      <c r="B285" s="1">
+        <v>600400001</v>
+      </c>
+      <c r="C285" s="1">
+        <v>1</v>
+      </c>
+      <c r="D285" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A286" s="1">
+        <v>600400201</v>
+      </c>
+      <c r="B286" s="1">
+        <v>600400102</v>
+      </c>
+      <c r="C286" s="1">
+        <v>1</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A287" s="1">
+        <v>600400202</v>
+      </c>
+      <c r="B287" s="1">
+        <v>600400102</v>
+      </c>
+      <c r="C287" s="1">
+        <v>1</v>
+      </c>
+      <c r="D287" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A288" s="1">
+        <v>600400203</v>
+      </c>
+      <c r="B288" s="1">
+        <v>600400103</v>
+      </c>
+      <c r="C288" s="1">
+        <v>1</v>
+      </c>
+      <c r="D288" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A289" s="1">
+        <v>600400301</v>
+      </c>
+      <c r="B289" s="1">
+        <v>600400202</v>
+      </c>
+      <c r="C289" s="1">
+        <v>1</v>
+      </c>
+      <c r="D289" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A290" s="1">
+        <v>600400302</v>
+      </c>
+      <c r="B290" s="1">
+        <v>600400202</v>
+      </c>
+      <c r="C290" s="1">
+        <v>1</v>
+      </c>
+      <c r="D290" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A291" s="1">
+        <v>600400303</v>
+      </c>
+      <c r="B291" s="1">
+        <v>600400203</v>
+      </c>
+      <c r="C291" s="1">
+        <v>1</v>
+      </c>
+      <c r="D291" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A292" s="1">
+        <v>600400401</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C292" s="1">
+        <v>1</v>
+      </c>
+      <c r="D292" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A293" s="1">
+        <v>600400501</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C293" s="1">
+        <v>1</v>
+      </c>
+      <c r="D293" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A294" s="1">
+        <v>600500101</v>
+      </c>
+      <c r="B294" s="1">
+        <v>600500001</v>
+      </c>
+      <c r="C294" s="1">
+        <v>1</v>
+      </c>
+      <c r="D294" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A295" s="1">
+        <v>600500102</v>
+      </c>
+      <c r="B295" s="1">
+        <v>600500001</v>
+      </c>
+      <c r="C295" s="1">
+        <v>1</v>
+      </c>
+      <c r="D295" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A296" s="1">
+        <v>600500103</v>
+      </c>
+      <c r="B296" s="1">
+        <v>600500001</v>
+      </c>
+      <c r="C296" s="1">
+        <v>1</v>
+      </c>
+      <c r="D296" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A297" s="1">
+        <v>600500201</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C297" s="1">
+        <v>1</v>
+      </c>
+      <c r="D297" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A298" s="1">
+        <v>600500202</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C298" s="1">
+        <v>1</v>
+      </c>
+      <c r="D298" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A299" s="1">
+        <v>600500203</v>
+      </c>
+      <c r="B299" s="1">
+        <v>600500103</v>
+      </c>
+      <c r="C299" s="1">
+        <v>1</v>
+      </c>
+      <c r="D299" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A300" s="1">
+        <v>600500301</v>
+      </c>
+      <c r="B300" s="1">
+        <v>600500202</v>
+      </c>
+      <c r="C300" s="1">
+        <v>1</v>
+      </c>
+      <c r="D300" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A301" s="1">
+        <v>600500302</v>
+      </c>
+      <c r="B301" s="1">
+        <v>600500202</v>
+      </c>
+      <c r="C301" s="1">
+        <v>1</v>
+      </c>
+      <c r="D301" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A302" s="1">
+        <v>600500303</v>
+      </c>
+      <c r="B302" s="1">
+        <v>600500203</v>
+      </c>
+      <c r="C302" s="1">
+        <v>1</v>
+      </c>
+      <c r="D302" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A303" s="1">
+        <v>600500401</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C303" s="1">
+        <v>1</v>
+      </c>
+      <c r="D303" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A304" s="1">
+        <v>600500501</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C304" s="1">
+        <v>1</v>
+      </c>
+      <c r="D304" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A305" s="1">
+        <v>600600101</v>
+      </c>
+      <c r="B305" s="1">
+        <v>600600001</v>
+      </c>
+      <c r="C305" s="1">
+        <v>1</v>
+      </c>
+      <c r="D305" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A306" s="1">
+        <v>600600102</v>
+      </c>
+      <c r="B306" s="1">
+        <v>600600001</v>
+      </c>
+      <c r="C306" s="1">
+        <v>1</v>
+      </c>
+      <c r="D306" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A307" s="1">
+        <v>600600112</v>
+      </c>
+      <c r="B307" s="1">
+        <v>600600102</v>
+      </c>
+      <c r="C307" s="1">
+        <v>1</v>
+      </c>
+      <c r="D307" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A308" s="1">
+        <v>600600103</v>
+      </c>
+      <c r="B308" s="1">
+        <v>600600001</v>
+      </c>
+      <c r="C308" s="1">
+        <v>1</v>
+      </c>
+      <c r="D308" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A309" s="1">
+        <v>600600201</v>
+      </c>
+      <c r="B309" s="1">
+        <v>600600102</v>
+      </c>
+      <c r="C309" s="1">
+        <v>1</v>
+      </c>
+      <c r="D309" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A310" s="1">
+        <v>600600202</v>
+      </c>
+      <c r="B310" s="1">
+        <v>600600102</v>
+      </c>
+      <c r="C310" s="1">
+        <v>1</v>
+      </c>
+      <c r="D310" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A311" s="1">
+        <v>600600203</v>
+      </c>
+      <c r="B311" s="1">
+        <v>600600103</v>
+      </c>
+      <c r="C311" s="1">
+        <v>1</v>
+      </c>
+      <c r="D311" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A312" s="1">
+        <v>600600301</v>
+      </c>
+      <c r="B312" s="1">
+        <v>600600202</v>
+      </c>
+      <c r="C312" s="1">
+        <v>1</v>
+      </c>
+      <c r="D312" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A313" s="1">
+        <v>600600302</v>
+      </c>
+      <c r="B313" s="1">
+        <v>600600202</v>
+      </c>
+      <c r="C313" s="1">
+        <v>1</v>
+      </c>
+      <c r="D313" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A314" s="1">
+        <v>600600303</v>
+      </c>
+      <c r="B314" s="1">
+        <v>600600203</v>
+      </c>
+      <c r="C314" s="1">
+        <v>1</v>
+      </c>
+      <c r="D314" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A315" s="1">
+        <v>600600401</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C315" s="1">
+        <v>1</v>
+      </c>
+      <c r="D315" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A316" s="1">
+        <v>600600501</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C316" s="1">
+        <v>1</v>
+      </c>
+      <c r="D316" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A317" s="1">
+        <v>600700101</v>
+      </c>
+      <c r="B317" s="1">
+        <v>600700001</v>
+      </c>
+      <c r="C317" s="1">
+        <v>1</v>
+      </c>
+      <c r="D317" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A318" s="1">
+        <v>600700102</v>
+      </c>
+      <c r="B318" s="1">
+        <v>600700001</v>
+      </c>
+      <c r="C318" s="1">
+        <v>1</v>
+      </c>
+      <c r="D318" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A319" s="1">
+        <v>600700103</v>
+      </c>
+      <c r="B319" s="1">
+        <v>600700001</v>
+      </c>
+      <c r="C319" s="1">
+        <v>1</v>
+      </c>
+      <c r="D319" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A320" s="1">
+        <v>600700201</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C320" s="1">
+        <v>1</v>
+      </c>
+      <c r="D320" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A321" s="1">
+        <v>600700202</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C321" s="1">
+        <v>1</v>
+      </c>
+      <c r="D321" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A322" s="1">
+        <v>600700203</v>
+      </c>
+      <c r="B322" s="1">
+        <v>600700103</v>
+      </c>
+      <c r="C322" s="1">
+        <v>1</v>
+      </c>
+      <c r="D322" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A323" s="1">
+        <v>600700301</v>
+      </c>
+      <c r="B323" s="1">
+        <v>600700202</v>
+      </c>
+      <c r="C323" s="1">
+        <v>1</v>
+      </c>
+      <c r="D323" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A324" s="1">
+        <v>600700302</v>
+      </c>
+      <c r="B324" s="1">
+        <v>600700202</v>
+      </c>
+      <c r="C324" s="1">
+        <v>1</v>
+      </c>
+      <c r="D324" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A325" s="1">
+        <v>600700303</v>
+      </c>
+      <c r="B325" s="1">
+        <v>600700203</v>
+      </c>
+      <c r="C325" s="1">
+        <v>1</v>
+      </c>
+      <c r="D325" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A326" s="1">
+        <v>600700401</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C326" s="1">
+        <v>1</v>
+      </c>
+      <c r="D326" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A327" s="1">
+        <v>600700501</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C327" s="1">
+        <v>1</v>
+      </c>
+      <c r="D327" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A328" s="1">
+        <v>600800101</v>
+      </c>
+      <c r="B328" s="1">
+        <v>600800001</v>
+      </c>
+      <c r="C328" s="1">
+        <v>1</v>
+      </c>
+      <c r="D328" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A329" s="1">
+        <v>600800102</v>
+      </c>
+      <c r="B329" s="1">
+        <v>600800001</v>
+      </c>
+      <c r="C329" s="1">
+        <v>1</v>
+      </c>
+      <c r="D329" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A330" s="1">
+        <v>600800112</v>
+      </c>
+      <c r="B330" s="1">
+        <v>600800102</v>
+      </c>
+      <c r="C330" s="1">
+        <v>1</v>
+      </c>
+      <c r="D330" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A331" s="1">
+        <v>600800103</v>
+      </c>
+      <c r="B331" s="1">
+        <v>600800001</v>
+      </c>
+      <c r="C331" s="1">
+        <v>1</v>
+      </c>
+      <c r="D331" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A332" s="1">
+        <v>600800201</v>
+      </c>
+      <c r="B332" s="1">
+        <v>600800102</v>
+      </c>
+      <c r="C332" s="1">
+        <v>1</v>
+      </c>
+      <c r="D332" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A333" s="1">
+        <v>600800202</v>
+      </c>
+      <c r="B333" s="1">
+        <v>600800102</v>
+      </c>
+      <c r="C333" s="1">
+        <v>1</v>
+      </c>
+      <c r="D333" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A334" s="1">
+        <v>600800203</v>
+      </c>
+      <c r="B334" s="1">
+        <v>600800103</v>
+      </c>
+      <c r="C334" s="1">
+        <v>1</v>
+      </c>
+      <c r="D334" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A335" s="1">
+        <v>600800301</v>
+      </c>
+      <c r="B335" s="1">
+        <v>600800202</v>
+      </c>
+      <c r="C335" s="1">
+        <v>1</v>
+      </c>
+      <c r="D335" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A336" s="1">
+        <v>600800302</v>
+      </c>
+      <c r="B336" s="1">
+        <v>600800202</v>
+      </c>
+      <c r="C336" s="1">
+        <v>1</v>
+      </c>
+      <c r="D336" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A337" s="1">
+        <v>600800303</v>
+      </c>
+      <c r="B337" s="1">
+        <v>600800203</v>
+      </c>
+      <c r="C337" s="1">
+        <v>1</v>
+      </c>
+      <c r="D337" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A338" s="1">
+        <v>600800401</v>
+      </c>
+      <c r="B338" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C338" s="1">
+        <v>1</v>
+      </c>
+      <c r="D338" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A339" s="1">
+        <v>600800501</v>
+      </c>
+      <c r="B339" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C339" s="1">
+        <v>1</v>
+      </c>
+      <c r="D339" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204:B205 B207:B208">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211:B213">
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B222:B224">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233:B235">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B242:B244">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246:B247">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B264">
+  <conditionalFormatting sqref="B265">
+    <cfRule type="duplicateValues" dxfId="22" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B261">
+    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B276">
+    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B279">
+    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B288">
+    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B284">
+    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B299">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B302">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B311">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B307">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B322">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B325">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B334">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B330">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE89599-A36A-4562-8FB1-5383D621651A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0995C1D3-A4F4-4C8C-89BD-8E4435E79F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="66">
   <si>
     <t>词条组id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -360,77 +360,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="30">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1061,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:D339"/>
+  <dimension ref="A1:D341"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -5810,93 +5740,124 @@
         <v>61</v>
       </c>
     </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A340" s="1">
+        <v>600900101</v>
+      </c>
+      <c r="B340" s="1">
+        <v>600900001</v>
+      </c>
+      <c r="C340" s="1">
+        <v>1</v>
+      </c>
+      <c r="D340" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A341" s="1">
+        <v>600900102</v>
+      </c>
+      <c r="B341" s="1">
+        <v>600900101</v>
+      </c>
+      <c r="C341" s="1">
+        <v>1</v>
+      </c>
+      <c r="D341" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204:B205 B207:B208">
-    <cfRule type="duplicateValues" dxfId="31" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211:B213">
-    <cfRule type="duplicateValues" dxfId="30" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B222:B224">
-    <cfRule type="duplicateValues" dxfId="29" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233:B235">
-    <cfRule type="duplicateValues" dxfId="28" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B242:B244">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246:B247">
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="23" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B261">
+    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B265">
-    <cfRule type="duplicateValues" dxfId="22" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B261">
-    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B284">
+    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B288">
-    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B299">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B302">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  <conditionalFormatting sqref="B307">
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B307">
+  <conditionalFormatting sqref="B322">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B322">
+  <conditionalFormatting sqref="B325">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="B330">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B330">
+  <conditionalFormatting sqref="B341">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0995C1D3-A4F4-4C8C-89BD-8E4435E79F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C73568-D20A-43B8-A322-31DFA39B5942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="70">
   <si>
     <t>词条组id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -262,6 +262,22 @@
   </si>
   <si>
     <t>600700301,600700302</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>互斥词条id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外词条组id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>extra_affix_group_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>exclusive_affix__id</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -338,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -356,11 +372,54 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="34">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -991,24 +1050,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:D341"/>
+  <dimension ref="A1:F341"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="16.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1021,8 +1082,14 @@
       <c r="D2" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1035,8 +1102,14 @@
       <c r="D3" s="7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1049,8 +1122,14 @@
       <c r="D4" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1010201</v>
       </c>
@@ -1064,7 +1143,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>1010202</v>
       </c>
@@ -1078,7 +1157,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>1010203</v>
       </c>
@@ -1092,7 +1171,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>1010204</v>
       </c>
@@ -1106,7 +1185,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>1010501</v>
       </c>
@@ -1120,7 +1199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>1010502</v>
       </c>
@@ -1134,7 +1213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>1010503</v>
       </c>
@@ -1148,7 +1227,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>1010504</v>
       </c>
@@ -1162,7 +1241,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>1010701</v>
       </c>
@@ -1176,7 +1255,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>1010702</v>
       </c>
@@ -1190,7 +1269,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>1010703</v>
       </c>
@@ -1204,7 +1283,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>1010704</v>
       </c>
@@ -4354,7 +4433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
         <v>700200108</v>
       </c>
@@ -4368,7 +4447,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
         <v>700400002</v>
       </c>
@@ -4382,7 +4461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
         <v>700400003</v>
       </c>
@@ -4396,7 +4475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
         <v>700400004</v>
       </c>
@@ -4410,7 +4489,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
         <v>700400102</v>
       </c>
@@ -4424,7 +4503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
         <v>700400103</v>
       </c>
@@ -4438,7 +4517,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
         <v>700400104</v>
       </c>
@@ -4452,7 +4531,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
         <v>600100101</v>
       </c>
@@ -4465,8 +4544,14 @@
       <c r="D248" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E248" s="7">
+        <v>600200101</v>
+      </c>
+      <c r="F248" s="7">
+        <v>6002</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
         <v>600100102</v>
       </c>
@@ -4480,7 +4565,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
         <v>600100103</v>
       </c>
@@ -4494,7 +4579,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
         <v>600100201</v>
       </c>
@@ -4508,7 +4593,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
         <v>600100202</v>
       </c>
@@ -4522,7 +4607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
         <v>600100203</v>
       </c>
@@ -4536,7 +4621,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
         <v>600100301</v>
       </c>
@@ -4550,7 +4635,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
         <v>600100302</v>
       </c>
@@ -4564,7 +4649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
         <v>600100303</v>
       </c>
@@ -4578,7 +4663,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
         <v>600100401</v>
       </c>
@@ -4592,7 +4677,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
         <v>600100501</v>
       </c>
@@ -4606,7 +4691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
         <v>600200101</v>
       </c>
@@ -4619,8 +4704,14 @@
       <c r="D259" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E259" s="7">
+        <v>600100101</v>
+      </c>
+      <c r="F259" s="7">
+        <v>6001</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
         <v>600200102</v>
       </c>
@@ -4634,7 +4725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
         <v>600200112</v>
       </c>
@@ -4648,7 +4739,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
         <v>600200103</v>
       </c>
@@ -4662,7 +4753,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
         <v>600200201</v>
       </c>
@@ -4676,7 +4767,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
         <v>600200202</v>
       </c>
@@ -4690,7 +4781,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
         <v>600200203</v>
       </c>
@@ -4704,7 +4795,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
         <v>600200301</v>
       </c>
@@ -4718,7 +4809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
         <v>600200302</v>
       </c>
@@ -4732,7 +4823,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
         <v>600200303</v>
       </c>
@@ -4746,7 +4837,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
         <v>600200401</v>
       </c>
@@ -4760,7 +4851,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
         <v>600200501</v>
       </c>
@@ -4774,7 +4865,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
         <v>600300101</v>
       </c>
@@ -4787,8 +4878,14 @@
       <c r="D271" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E271" s="7">
+        <v>600400101</v>
+      </c>
+      <c r="F271" s="7">
+        <v>6004</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
         <v>600300102</v>
       </c>
@@ -4802,7 +4899,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
         <v>600300103</v>
       </c>
@@ -4816,7 +4913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
         <v>600300201</v>
       </c>
@@ -4830,7 +4927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
         <v>600300202</v>
       </c>
@@ -4844,7 +4941,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
         <v>600300203</v>
       </c>
@@ -4858,7 +4955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
         <v>600300301</v>
       </c>
@@ -4872,7 +4969,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
         <v>600300302</v>
       </c>
@@ -4886,7 +4983,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
         <v>600300303</v>
       </c>
@@ -4900,7 +4997,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
         <v>600300401</v>
       </c>
@@ -4914,7 +5011,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
         <v>600300501</v>
       </c>
@@ -4928,7 +5025,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
         <v>600400101</v>
       </c>
@@ -4941,8 +5038,14 @@
       <c r="D282" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E282" s="7">
+        <v>600300101</v>
+      </c>
+      <c r="F282" s="7">
+        <v>6003</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
         <v>600400102</v>
       </c>
@@ -4956,7 +5059,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
         <v>600400112</v>
       </c>
@@ -4970,7 +5073,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
         <v>600400103</v>
       </c>
@@ -4984,7 +5087,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
         <v>600400201</v>
       </c>
@@ -4998,7 +5101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
         <v>600400202</v>
       </c>
@@ -5012,7 +5115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
         <v>600400203</v>
       </c>
@@ -5026,7 +5129,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
         <v>600400301</v>
       </c>
@@ -5040,7 +5143,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
         <v>600400302</v>
       </c>
@@ -5054,7 +5157,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
         <v>600400303</v>
       </c>
@@ -5068,7 +5171,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
         <v>600400401</v>
       </c>
@@ -5082,7 +5185,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
         <v>600400501</v>
       </c>
@@ -5096,7 +5199,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
         <v>600500101</v>
       </c>
@@ -5109,8 +5212,14 @@
       <c r="D294" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E294" s="7">
+        <v>600600101</v>
+      </c>
+      <c r="F294" s="7">
+        <v>6006</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
         <v>600500102</v>
       </c>
@@ -5124,7 +5233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
         <v>600500103</v>
       </c>
@@ -5138,7 +5247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
         <v>600500201</v>
       </c>
@@ -5152,7 +5261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
         <v>600500202</v>
       </c>
@@ -5166,7 +5275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
         <v>600500203</v>
       </c>
@@ -5180,7 +5289,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
         <v>600500301</v>
       </c>
@@ -5194,7 +5303,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
         <v>600500302</v>
       </c>
@@ -5208,7 +5317,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
         <v>600500303</v>
       </c>
@@ -5222,7 +5331,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
         <v>600500401</v>
       </c>
@@ -5236,7 +5345,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
         <v>600500501</v>
       </c>
@@ -5250,7 +5359,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
         <v>600600101</v>
       </c>
@@ -5263,8 +5372,14 @@
       <c r="D305" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E305" s="7">
+        <v>600500101</v>
+      </c>
+      <c r="F305" s="7">
+        <v>6005</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
         <v>600600102</v>
       </c>
@@ -5278,7 +5393,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
         <v>600600112</v>
       </c>
@@ -5292,7 +5407,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
         <v>600600103</v>
       </c>
@@ -5306,7 +5421,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
         <v>600600201</v>
       </c>
@@ -5320,7 +5435,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
         <v>600600202</v>
       </c>
@@ -5334,7 +5449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
         <v>600600203</v>
       </c>
@@ -5348,7 +5463,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
         <v>600600301</v>
       </c>
@@ -5362,7 +5477,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
         <v>600600302</v>
       </c>
@@ -5376,7 +5491,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
         <v>600600303</v>
       </c>
@@ -5390,7 +5505,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
         <v>600600401</v>
       </c>
@@ -5404,7 +5519,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
         <v>600600501</v>
       </c>
@@ -5418,7 +5533,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
         <v>600700101</v>
       </c>
@@ -5431,8 +5546,14 @@
       <c r="D317" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E317" s="7">
+        <v>600800101</v>
+      </c>
+      <c r="F317" s="7">
+        <v>6008</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
         <v>600700102</v>
       </c>
@@ -5446,7 +5567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
         <v>600700103</v>
       </c>
@@ -5460,7 +5581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
         <v>600700201</v>
       </c>
@@ -5474,7 +5595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
         <v>600700202</v>
       </c>
@@ -5488,7 +5609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
         <v>600700203</v>
       </c>
@@ -5502,7 +5623,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
         <v>600700301</v>
       </c>
@@ -5516,7 +5637,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
         <v>600700302</v>
       </c>
@@ -5530,7 +5651,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
         <v>600700303</v>
       </c>
@@ -5544,7 +5665,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
         <v>600700401</v>
       </c>
@@ -5558,7 +5679,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
         <v>600700501</v>
       </c>
@@ -5572,7 +5693,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
         <v>600800101</v>
       </c>
@@ -5585,8 +5706,14 @@
       <c r="D328" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E328" s="7">
+        <v>600700101</v>
+      </c>
+      <c r="F328" s="7">
+        <v>6007</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
         <v>600800102</v>
       </c>
@@ -5600,7 +5727,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
         <v>600800112</v>
       </c>
@@ -5614,7 +5741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
         <v>600800103</v>
       </c>
@@ -5628,7 +5755,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
         <v>600800201</v>
       </c>
@@ -5642,7 +5769,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
         <v>600800202</v>
       </c>
@@ -5656,7 +5783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
         <v>600800203</v>
       </c>
@@ -5670,7 +5797,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
         <v>600800301</v>
       </c>
@@ -5684,7 +5811,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
         <v>600800302</v>
       </c>
@@ -5771,93 +5898,105 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="33" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B139">
+    <cfRule type="duplicateValues" dxfId="32" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B140">
+    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B141">
+    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B142">
     <cfRule type="duplicateValues" dxfId="29" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B139">
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="28" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="27" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="26" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="25" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="24" priority="35"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B204:B205 B207:B208">
-    <cfRule type="duplicateValues" dxfId="23" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211:B213">
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B222:B224">
-    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233:B235">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B242:B244">
-    <cfRule type="duplicateValues" dxfId="19" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="18" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246:B247">
-    <cfRule type="duplicateValues" dxfId="17" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B261">
+    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B265">
+    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B276">
+    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B279">
+    <cfRule type="duplicateValues" dxfId="15" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B284">
     <cfRule type="duplicateValues" dxfId="14" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B265">
-    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B288">
-    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B299">
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B302">
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B307">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B311">
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B322">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B302">
+  <conditionalFormatting sqref="B325">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B307">
+  <conditionalFormatting sqref="B330">
     <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B311">
+  <conditionalFormatting sqref="B334">
     <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B322">
+  <conditionalFormatting sqref="B341">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B325">
+  <conditionalFormatting sqref="E248">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  <conditionalFormatting sqref="E271">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <conditionalFormatting sqref="E294">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B341">
+  <conditionalFormatting sqref="E317">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C73568-D20A-43B8-A322-31DFA39B5942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
+    <workbookView windowWidth="27870" windowHeight="12225"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_front_v8" sheetId="1" r:id="rId1"/>
@@ -20,9 +14,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,43 +32,58 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="70">
   <si>
+    <t>paipaiworld_config</t>
+  </si>
+  <si>
+    <t>INT_K</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S</t>
+  </si>
+  <si>
+    <t>INT_S</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>affix_id_set</t>
+  </si>
+  <si>
+    <t>must_num</t>
+  </si>
+  <si>
+    <t>affix_group_num</t>
+  </si>
+  <si>
+    <t>exclusive_affix__id</t>
+  </si>
+  <si>
+    <t>extra_affix_group_id</t>
+  </si>
+  <si>
+    <t>词条前置组id</t>
+  </si>
+  <si>
     <t>词条组id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>order</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_K</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>paipaiworld_config</t>
-  </si>
-  <si>
-    <t>must_num</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>必须拥有的词条数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>affix_id_set</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>词条前置组id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>词条前置所需词条组id:总数量</t>
+  </si>
+  <si>
+    <t>互斥词条id</t>
+  </si>
+  <si>
+    <t>额外词条组id</t>
+  </si>
+  <si>
+    <t>0:0</t>
   </si>
   <si>
     <t>2010101,2010102,2010103,2010104,2010105</t>
@@ -91,80 +99,59 @@
   </si>
   <si>
     <t>700010105,700010106,700010107</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>700100105,700100106,700100107</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7002:8</t>
   </si>
   <si>
     <t>700200105,700200106,700200107</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>affix_group_num</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>词条前置所需词条组id:总数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>7002:8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>600100101,600100102</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>6001:4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600100301,600100302</t>
   </si>
   <si>
     <t>6001:7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600100302,600100303</t>
   </si>
   <si>
     <t>6001:12</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>600100302,600100303</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>6002:4</t>
   </si>
   <si>
+    <t>600200301,600200302</t>
+  </si>
+  <si>
     <t>6002:7</t>
   </si>
   <si>
+    <t>600200302,600100203</t>
+  </si>
+  <si>
     <t>6002:12</t>
   </si>
   <si>
-    <t>600200301,600200302</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>600200302,600100203</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>600300101,600300102</t>
   </si>
   <si>
     <t>6003:4</t>
   </si>
   <si>
+    <t>600300301,600300302</t>
+  </si>
+  <si>
     <t>6003:7</t>
   </si>
   <si>
@@ -177,7 +164,7 @@
     <t>6004:4</t>
   </si>
   <si>
-    <t>600400301,600400302</t>
+    <t>600400302</t>
   </si>
   <si>
     <t>6004:7</t>
@@ -189,6 +176,24 @@
     <t>6004:12</t>
   </si>
   <si>
+    <t>600500101,600500102</t>
+  </si>
+  <si>
+    <t>6005:4</t>
+  </si>
+  <si>
+    <t>600500302</t>
+  </si>
+  <si>
+    <t>6005:7</t>
+  </si>
+  <si>
+    <t>600500302,600500303</t>
+  </si>
+  <si>
+    <t>6005:12</t>
+  </si>
+  <si>
     <t>6006:4</t>
   </si>
   <si>
@@ -204,27 +209,15 @@
     <t>6006:12</t>
   </si>
   <si>
-    <t>600500101,600500102</t>
-  </si>
-  <si>
-    <t>6005:4</t>
-  </si>
-  <si>
-    <t>6005:7</t>
-  </si>
-  <si>
-    <t>600500302,600500303</t>
-  </si>
-  <si>
-    <t>6005:12</t>
-  </si>
-  <si>
     <t>600700101,600700102</t>
   </si>
   <si>
     <t>6007:4</t>
   </si>
   <si>
+    <t>600700301,600700302</t>
+  </si>
+  <si>
     <t>6007:7</t>
   </si>
   <si>
@@ -247,90 +240,382 @@
   </si>
   <si>
     <t>6008:12</t>
-  </si>
-  <si>
-    <t>600100301,600100302</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>600300301,600300302</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>600500301,600500302</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>600700301,600700302</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>互斥词条id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外词条组id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>extra_affix_group_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>exclusive_affix__id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDEE0E3"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -350,372 +635,343 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -725,9 +981,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -776,7 +1029,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -809,26 +1062,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -861,23 +1097,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1039,39 +1258,34 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F341"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.25" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
+    <row r="1" spans="1:3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -1079,57 +1293,57 @@
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1">
         <v>1010201</v>
       </c>
@@ -1140,10 +1354,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1">
         <v>1010202</v>
       </c>
@@ -1154,10 +1368,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1">
         <v>1010203</v>
       </c>
@@ -1168,10 +1382,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1">
         <v>1010204</v>
       </c>
@@ -1182,10 +1396,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1">
         <v>1010501</v>
       </c>
@@ -1196,10 +1410,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1">
         <v>1010502</v>
       </c>
@@ -1210,10 +1424,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1">
         <v>1010503</v>
       </c>
@@ -1224,10 +1438,10 @@
         <v>1</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1">
         <v>1010504</v>
       </c>
@@ -1238,10 +1452,10 @@
         <v>1</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1">
         <v>1010701</v>
       </c>
@@ -1252,10 +1466,10 @@
         <v>1</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="1">
         <v>1010702</v>
       </c>
@@ -1266,10 +1480,10 @@
         <v>1</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="1">
         <v>1010703</v>
       </c>
@@ -1280,10 +1494,10 @@
         <v>1</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="1">
         <v>1010704</v>
       </c>
@@ -1294,10 +1508,10 @@
         <v>1</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="1">
         <v>1010801</v>
       </c>
@@ -1308,10 +1522,10 @@
         <v>1</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="1">
         <v>1010802</v>
       </c>
@@ -1322,10 +1536,10 @@
         <v>1</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="1">
         <v>1010803</v>
       </c>
@@ -1336,10 +1550,10 @@
         <v>1</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="1">
         <v>1010804</v>
       </c>
@@ -1350,10 +1564,10 @@
         <v>1</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="1">
         <v>1011001</v>
       </c>
@@ -1364,10 +1578,10 @@
         <v>1</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="1">
         <v>1011002</v>
       </c>
@@ -1378,10 +1592,10 @@
         <v>1</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="1">
         <v>1011003</v>
       </c>
@@ -1392,10 +1606,10 @@
         <v>1</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="1">
         <v>1011004</v>
       </c>
@@ -1406,10 +1620,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="1">
         <v>1011101</v>
       </c>
@@ -1420,10 +1634,10 @@
         <v>1</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="1">
         <v>1011102</v>
       </c>
@@ -1434,10 +1648,10 @@
         <v>1</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="1">
         <v>1011103</v>
       </c>
@@ -1448,10 +1662,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="1">
         <v>1011104</v>
       </c>
@@ -1462,10 +1676,10 @@
         <v>1</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="1">
         <v>1011201</v>
       </c>
@@ -1476,10 +1690,10 @@
         <v>1</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="1">
         <v>1011202</v>
       </c>
@@ -1490,10 +1704,10 @@
         <v>1</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="1">
         <v>1011203</v>
       </c>
@@ -1504,10 +1718,10 @@
         <v>1</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="1">
         <v>1011204</v>
       </c>
@@ -1518,10 +1732,10 @@
         <v>1</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="1">
         <v>2010101</v>
       </c>
@@ -1532,10 +1746,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="1">
         <v>2010102</v>
       </c>
@@ -1546,10 +1760,10 @@
         <v>1</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="1">
         <v>2010103</v>
       </c>
@@ -1560,10 +1774,10 @@
         <v>1</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="1">
         <v>2010104</v>
       </c>
@@ -1574,10 +1788,10 @@
         <v>1</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="1">
         <v>2010301</v>
       </c>
@@ -1588,10 +1802,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" s="1">
         <v>2010302</v>
       </c>
@@ -1602,10 +1816,10 @@
         <v>1</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" s="1">
         <v>2010303</v>
       </c>
@@ -1616,10 +1830,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="1">
         <v>2010304</v>
       </c>
@@ -1630,10 +1844,10 @@
         <v>1</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="1">
         <v>2010401</v>
       </c>
@@ -1644,10 +1858,10 @@
         <v>1</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="1">
         <v>2010402</v>
       </c>
@@ -1658,10 +1872,10 @@
         <v>1</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" s="1">
         <v>2010403</v>
       </c>
@@ -1672,10 +1886,10 @@
         <v>1</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" s="1">
         <v>2010404</v>
       </c>
@@ -1686,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" s="1">
         <v>3010101</v>
       </c>
@@ -1700,10 +1914,10 @@
         <v>1</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" s="1">
         <v>3010102</v>
       </c>
@@ -1714,10 +1928,10 @@
         <v>1</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" s="1">
         <v>3010103</v>
       </c>
@@ -1728,10 +1942,10 @@
         <v>1</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" s="1">
         <v>3010104</v>
       </c>
@@ -1742,10 +1956,10 @@
         <v>1</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" s="1">
         <v>3010301</v>
       </c>
@@ -1756,10 +1970,10 @@
         <v>1</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" s="1">
         <v>3010302</v>
       </c>
@@ -1770,10 +1984,10 @@
         <v>1</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" s="1">
         <v>3010303</v>
       </c>
@@ -1784,10 +1998,10 @@
         <v>1</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" s="1">
         <v>3010304</v>
       </c>
@@ -1798,10 +2012,10 @@
         <v>1</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" s="1">
         <v>3010401</v>
       </c>
@@ -1812,10 +2026,10 @@
         <v>1</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" s="1">
         <v>3010402</v>
       </c>
@@ -1826,10 +2040,10 @@
         <v>1</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" s="1">
         <v>3010403</v>
       </c>
@@ -1840,10 +2054,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" s="1">
         <v>3010404</v>
       </c>
@@ -1854,10 +2068,10 @@
         <v>1</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" s="1">
         <v>4010101</v>
       </c>
@@ -1868,10 +2082,10 @@
         <v>1</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" s="1">
         <v>4010102</v>
       </c>
@@ -1882,10 +2096,10 @@
         <v>1</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" s="1">
         <v>4010103</v>
       </c>
@@ -1896,10 +2110,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" s="1">
         <v>4010104</v>
       </c>
@@ -1910,10 +2124,10 @@
         <v>1</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" s="1">
         <v>4010301</v>
       </c>
@@ -1924,10 +2138,10 @@
         <v>1</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" s="1">
         <v>4010302</v>
       </c>
@@ -1938,10 +2152,10 @@
         <v>1</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" s="1">
         <v>4010303</v>
       </c>
@@ -1952,10 +2166,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" s="1">
         <v>4010304</v>
       </c>
@@ -1966,10 +2180,10 @@
         <v>1</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" s="1">
         <v>4010401</v>
       </c>
@@ -1980,10 +2194,10 @@
         <v>1</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" s="1">
         <v>4010402</v>
       </c>
@@ -1994,10 +2208,10 @@
         <v>1</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" s="1">
         <v>4010403</v>
       </c>
@@ -2008,10 +2222,10 @@
         <v>1</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" s="1">
         <v>4010404</v>
       </c>
@@ -2022,10 +2236,10 @@
         <v>1</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" s="1">
         <v>5010101</v>
       </c>
@@ -2036,10 +2250,10 @@
         <v>1</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" s="1">
         <v>5010102</v>
       </c>
@@ -2050,10 +2264,10 @@
         <v>1</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" s="1">
         <v>5010103</v>
       </c>
@@ -2064,10 +2278,10 @@
         <v>1</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" s="1">
         <v>5010104</v>
       </c>
@@ -2078,10 +2292,10 @@
         <v>1</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" s="1">
         <v>5010301</v>
       </c>
@@ -2092,10 +2306,10 @@
         <v>1</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" s="1">
         <v>5010302</v>
       </c>
@@ -2106,10 +2320,10 @@
         <v>1</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" s="1">
         <v>5010303</v>
       </c>
@@ -2120,10 +2334,10 @@
         <v>1</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" s="1">
         <v>5010304</v>
       </c>
@@ -2134,10 +2348,10 @@
         <v>1</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" s="1">
         <v>5010401</v>
       </c>
@@ -2148,10 +2362,10 @@
         <v>1</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" s="1">
         <v>5010402</v>
       </c>
@@ -2162,10 +2376,10 @@
         <v>1</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" s="1">
         <v>5010403</v>
       </c>
@@ -2176,10 +2390,10 @@
         <v>1</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" s="1">
         <v>5010404</v>
       </c>
@@ -2190,10 +2404,10 @@
         <v>1</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" s="1">
         <v>9000101</v>
       </c>
@@ -2204,10 +2418,10 @@
         <v>1</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" s="1">
         <v>9000102</v>
       </c>
@@ -2218,10 +2432,10 @@
         <v>1</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" s="1">
         <v>9000103</v>
       </c>
@@ -2232,10 +2446,10 @@
         <v>1</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" s="1">
         <v>906010202</v>
       </c>
@@ -2246,10 +2460,10 @@
         <v>1</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" s="1">
         <v>906010403</v>
       </c>
@@ -2260,66 +2474,66 @@
         <v>1</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" s="1">
         <v>20101</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C86" s="1">
         <v>1</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" s="1">
         <v>30101</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C87" s="1">
         <v>1</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88" s="1">
         <v>40101</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C88" s="1">
         <v>1</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" s="1">
         <v>50101</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C89" s="1">
         <v>1</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" s="1">
         <v>1010901</v>
       </c>
@@ -2330,10 +2544,10 @@
         <v>1</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" s="1">
         <v>10109011</v>
       </c>
@@ -2344,10 +2558,10 @@
         <v>1</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
       <c r="A92" s="1">
         <v>10109012</v>
       </c>
@@ -2358,10 +2572,10 @@
         <v>1</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" s="1">
         <v>1010902</v>
       </c>
@@ -2372,10 +2586,10 @@
         <v>1</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" s="1">
         <v>1010903</v>
       </c>
@@ -2386,10 +2600,10 @@
         <v>1</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95" s="1">
         <v>1010904</v>
       </c>
@@ -2400,94 +2614,94 @@
         <v>1</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" s="1">
         <v>1010905</v>
       </c>
-      <c r="B96" s="5">
+      <c r="B96" s="7">
         <v>1010904</v>
       </c>
       <c r="C96" s="1">
         <v>1</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97" s="1">
         <v>1010906</v>
       </c>
-      <c r="B97" s="5">
+      <c r="B97" s="7">
         <v>1010905</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98" s="1">
         <v>1010907</v>
       </c>
-      <c r="B98" s="5">
+      <c r="B98" s="7">
         <v>1010906</v>
       </c>
       <c r="C98" s="1">
         <v>1</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" s="1">
         <v>1010908</v>
       </c>
-      <c r="B99" s="5">
+      <c r="B99" s="7">
         <v>1010907</v>
       </c>
       <c r="C99" s="1">
         <v>1</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
       <c r="A100" s="1">
         <v>1010909</v>
       </c>
-      <c r="B100" s="5">
+      <c r="B100" s="7">
         <v>1010908</v>
       </c>
       <c r="C100" s="1">
         <v>1</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
       <c r="A101" s="1">
         <v>1010910</v>
       </c>
-      <c r="B101" s="5">
+      <c r="B101" s="7">
         <v>1010909</v>
       </c>
       <c r="C101" s="1">
         <v>1</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102" s="1">
         <v>905010202</v>
       </c>
@@ -2498,10 +2712,10 @@
         <v>1</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103" s="1">
         <v>905010302</v>
       </c>
@@ -2512,10 +2726,10 @@
         <v>1</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
       <c r="A104" s="1">
         <v>905010403</v>
       </c>
@@ -2526,10 +2740,10 @@
         <v>1</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
       <c r="A105" s="1">
         <v>905010503</v>
       </c>
@@ -2540,10 +2754,10 @@
         <v>1</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
       <c r="A106" s="1">
         <v>905010604</v>
       </c>
@@ -2554,10 +2768,10 @@
         <v>1</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
       <c r="A107" s="1">
         <v>905010704</v>
       </c>
@@ -2568,10 +2782,10 @@
         <v>1</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
       <c r="A108" s="1">
         <v>905010805</v>
       </c>
@@ -2582,10 +2796,10 @@
         <v>1</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109" s="1">
         <v>901010202</v>
       </c>
@@ -2596,10 +2810,10 @@
         <v>1</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
       <c r="A110" s="1">
         <v>901010302</v>
       </c>
@@ -2610,10 +2824,10 @@
         <v>1</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
       <c r="A111" s="1">
         <v>901010403</v>
       </c>
@@ -2624,10 +2838,10 @@
         <v>1</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
       <c r="A112" s="1">
         <v>901010503</v>
       </c>
@@ -2638,10 +2852,10 @@
         <v>1</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
       <c r="A113" s="1">
         <v>901010604</v>
       </c>
@@ -2652,10 +2866,10 @@
         <v>1</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
       <c r="A114" s="1">
         <v>901010704</v>
       </c>
@@ -2666,10 +2880,10 @@
         <v>1</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
       <c r="A115" s="1">
         <v>901010805</v>
       </c>
@@ -2680,10 +2894,10 @@
         <v>1</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
       <c r="A116" s="1">
         <v>902010202</v>
       </c>
@@ -2694,10 +2908,10 @@
         <v>1</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
       <c r="A117" s="1">
         <v>902010302</v>
       </c>
@@ -2708,10 +2922,10 @@
         <v>1</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
       <c r="A118" s="1">
         <v>902010403</v>
       </c>
@@ -2722,10 +2936,10 @@
         <v>1</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
       <c r="A119" s="1">
         <v>902010503</v>
       </c>
@@ -2736,10 +2950,10 @@
         <v>1</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
       <c r="A120" s="1">
         <v>902010604</v>
       </c>
@@ -2750,10 +2964,10 @@
         <v>1</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
       <c r="A121" s="1">
         <v>902010704</v>
       </c>
@@ -2764,10 +2978,10 @@
         <v>1</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
       <c r="A122" s="1">
         <v>902010805</v>
       </c>
@@ -2778,10 +2992,10 @@
         <v>1</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
       <c r="A123" s="1">
         <v>903010202</v>
       </c>
@@ -2792,10 +3006,10 @@
         <v>1</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
       <c r="A124" s="1">
         <v>903010302</v>
       </c>
@@ -2806,10 +3020,10 @@
         <v>1</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
       <c r="A125" s="1">
         <v>903010403</v>
       </c>
@@ -2820,10 +3034,10 @@
         <v>1</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
       <c r="A126" s="1">
         <v>903010503</v>
       </c>
@@ -2834,10 +3048,10 @@
         <v>1</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
       <c r="A127" s="1">
         <v>903010604</v>
       </c>
@@ -2848,10 +3062,10 @@
         <v>1</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
       <c r="A128" s="1">
         <v>903010704</v>
       </c>
@@ -2862,10 +3076,10 @@
         <v>1</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
       <c r="A129" s="1">
         <v>903010805</v>
       </c>
@@ -2876,10 +3090,10 @@
         <v>1</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
       <c r="A130" s="1">
         <v>900010202</v>
       </c>
@@ -2890,10 +3104,10 @@
         <v>1</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
       <c r="A131" s="1">
         <v>900010302</v>
       </c>
@@ -2904,10 +3118,10 @@
         <v>1</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
       <c r="A132" s="1">
         <v>900010403</v>
       </c>
@@ -2918,10 +3132,10 @@
         <v>1</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
       <c r="A133" s="1">
         <v>900010503</v>
       </c>
@@ -2932,10 +3146,10 @@
         <v>1</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
       <c r="A134" s="1">
         <v>900010604</v>
       </c>
@@ -2946,10 +3160,10 @@
         <v>1</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
       <c r="A135" s="1">
         <v>900010704</v>
       </c>
@@ -2960,10 +3174,10 @@
         <v>1</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
       <c r="A136" s="1">
         <v>900010805</v>
       </c>
@@ -2974,10 +3188,10 @@
         <v>1</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
       <c r="A137" s="1">
         <v>900020202</v>
       </c>
@@ -2988,10 +3202,10 @@
         <v>1</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
       <c r="A138" s="1">
         <v>900020302</v>
       </c>
@@ -3002,10 +3216,10 @@
         <v>1</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
       <c r="A139" s="1">
         <v>900020403</v>
       </c>
@@ -3016,10 +3230,10 @@
         <v>1</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
       <c r="A140" s="1">
         <v>900020503</v>
       </c>
@@ -3030,10 +3244,10 @@
         <v>1</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
       <c r="A141" s="1">
         <v>900020604</v>
       </c>
@@ -3044,10 +3258,10 @@
         <v>1</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
       <c r="A142" s="1">
         <v>900020704</v>
       </c>
@@ -3058,10 +3272,10 @@
         <v>1</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
       <c r="A143" s="1">
         <v>900020805</v>
       </c>
@@ -3072,10 +3286,10 @@
         <v>1</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
       <c r="A144" s="1">
         <v>901020202</v>
       </c>
@@ -3086,10 +3300,10 @@
         <v>1</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
       <c r="A145" s="1">
         <v>901020302</v>
       </c>
@@ -3100,10 +3314,10 @@
         <v>1</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
       <c r="A146" s="1">
         <v>901020403</v>
       </c>
@@ -3114,10 +3328,10 @@
         <v>1</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
       <c r="A147" s="1">
         <v>901020503</v>
       </c>
@@ -3128,10 +3342,10 @@
         <v>1</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
       <c r="A148" s="1">
         <v>901020604</v>
       </c>
@@ -3142,10 +3356,10 @@
         <v>1</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
       <c r="A149" s="1">
         <v>901020704</v>
       </c>
@@ -3156,10 +3370,10 @@
         <v>1</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
       <c r="A150" s="1">
         <v>901020805</v>
       </c>
@@ -3170,10 +3384,10 @@
         <v>1</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
       <c r="A151" s="1">
         <v>902020202</v>
       </c>
@@ -3184,10 +3398,10 @@
         <v>1</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
       <c r="A152" s="1">
         <v>902020302</v>
       </c>
@@ -3198,10 +3412,10 @@
         <v>1</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
       <c r="A153" s="1">
         <v>902020403</v>
       </c>
@@ -3212,10 +3426,10 @@
         <v>1</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
       <c r="A154" s="1">
         <v>902020503</v>
       </c>
@@ -3226,10 +3440,10 @@
         <v>1</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
       <c r="A155" s="1">
         <v>902020604</v>
       </c>
@@ -3240,10 +3454,10 @@
         <v>1</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
       <c r="A156" s="1">
         <v>902020704</v>
       </c>
@@ -3254,10 +3468,10 @@
         <v>1</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
       <c r="A157" s="1">
         <v>902020805</v>
       </c>
@@ -3268,10 +3482,10 @@
         <v>1</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
       <c r="A158" s="1">
         <v>903020202</v>
       </c>
@@ -3282,10 +3496,10 @@
         <v>1</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
       <c r="A159" s="1">
         <v>903020302</v>
       </c>
@@ -3296,10 +3510,10 @@
         <v>1</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
       <c r="A160" s="1">
         <v>903020403</v>
       </c>
@@ -3310,10 +3524,10 @@
         <v>1</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
       <c r="A161" s="1">
         <v>903020503</v>
       </c>
@@ -3324,10 +3538,10 @@
         <v>1</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
       <c r="A162" s="1">
         <v>903020604</v>
       </c>
@@ -3338,10 +3552,10 @@
         <v>1</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
       <c r="A163" s="1">
         <v>903020704</v>
       </c>
@@ -3352,10 +3566,10 @@
         <v>1</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
       <c r="A164" s="1">
         <v>903020805</v>
       </c>
@@ -3366,10 +3580,10 @@
         <v>1</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
       <c r="A165" s="1">
         <v>800010101</v>
       </c>
@@ -3380,10 +3594,10 @@
         <v>1</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
       <c r="A166" s="1">
         <v>800010102</v>
       </c>
@@ -3394,10 +3608,10 @@
         <v>1</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
       <c r="A167" s="1">
         <v>800010201</v>
       </c>
@@ -3408,10 +3622,10 @@
         <v>1</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
       <c r="A168" s="1">
         <v>800010202</v>
       </c>
@@ -3422,10 +3636,10 @@
         <v>1</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
       <c r="A169" s="1">
         <v>800010301</v>
       </c>
@@ -3436,10 +3650,10 @@
         <v>1</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
       <c r="A170" s="1">
         <v>800010302</v>
       </c>
@@ -3450,10 +3664,10 @@
         <v>1</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
       <c r="A171" s="1">
         <v>800030101</v>
       </c>
@@ -3464,10 +3678,10 @@
         <v>1</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
       <c r="A172" s="1">
         <v>800030102</v>
       </c>
@@ -3478,10 +3692,10 @@
         <v>1</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
       <c r="A173" s="1">
         <v>800030201</v>
       </c>
@@ -3492,10 +3706,10 @@
         <v>1</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
       <c r="A174" s="1">
         <v>800030202</v>
       </c>
@@ -3506,10 +3720,10 @@
         <v>1</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
       <c r="A175" s="1">
         <v>800110101</v>
       </c>
@@ -3520,10 +3734,10 @@
         <v>1</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
       <c r="A176" s="1">
         <v>800110102</v>
       </c>
@@ -3534,10 +3748,10 @@
         <v>1</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
       <c r="A177" s="1">
         <v>800110201</v>
       </c>
@@ -3548,10 +3762,10 @@
         <v>1</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
       <c r="A178" s="1">
         <v>800110202</v>
       </c>
@@ -3562,10 +3776,10 @@
         <v>1</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
       <c r="A179" s="1">
         <v>800110301</v>
       </c>
@@ -3576,10 +3790,10 @@
         <v>1</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
       <c r="A180" s="1">
         <v>800110302</v>
       </c>
@@ -3590,10 +3804,10 @@
         <v>1</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
       <c r="A181" s="1">
         <v>800130101</v>
       </c>
@@ -3604,10 +3818,10 @@
         <v>1</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
       <c r="A182" s="1">
         <v>800130102</v>
       </c>
@@ -3618,10 +3832,10 @@
         <v>1</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
       <c r="A183" s="1">
         <v>800130201</v>
       </c>
@@ -3632,10 +3846,10 @@
         <v>1</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
       <c r="A184" s="1">
         <v>800130202</v>
       </c>
@@ -3646,10 +3860,10 @@
         <v>1</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
       <c r="A185" s="1">
         <v>800210101</v>
       </c>
@@ -3660,10 +3874,10 @@
         <v>1</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
       <c r="A186" s="1">
         <v>800210102</v>
       </c>
@@ -3674,10 +3888,10 @@
         <v>1</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
       <c r="A187" s="1">
         <v>800210201</v>
       </c>
@@ -3688,10 +3902,10 @@
         <v>1</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
       <c r="A188" s="1">
         <v>800210202</v>
       </c>
@@ -3702,10 +3916,10 @@
         <v>1</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
       <c r="A189" s="1">
         <v>800210301</v>
       </c>
@@ -3716,10 +3930,10 @@
         <v>1</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
       <c r="A190" s="1">
         <v>800210302</v>
       </c>
@@ -3730,10 +3944,10 @@
         <v>1</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
       <c r="A191" s="1">
         <v>800230101</v>
       </c>
@@ -3744,10 +3958,10 @@
         <v>1</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
       <c r="A192" s="1">
         <v>800230102</v>
       </c>
@@ -3758,10 +3972,10 @@
         <v>1</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
       <c r="A193" s="1">
         <v>800230201</v>
       </c>
@@ -3772,10 +3986,10 @@
         <v>1</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
       <c r="A194" s="1">
         <v>800230202</v>
       </c>
@@ -3786,10 +4000,10 @@
         <v>1</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
       <c r="A195" s="1">
         <v>801100102</v>
       </c>
@@ -3800,10 +4014,10 @@
         <v>1</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
       <c r="A196" s="1">
         <v>801100103</v>
       </c>
@@ -3814,10 +4028,10 @@
         <v>1</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
       <c r="A197" s="1">
         <v>801100201</v>
       </c>
@@ -3828,10 +4042,10 @@
         <v>1</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
       <c r="A198" s="1">
         <v>801100202</v>
       </c>
@@ -3842,10 +4056,10 @@
         <v>1</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
       <c r="A199" s="1">
         <v>801100203</v>
       </c>
@@ -3856,10 +4070,10 @@
         <v>1</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
       <c r="A200" s="1">
         <v>801100301</v>
       </c>
@@ -3870,10 +4084,10 @@
         <v>1</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
       <c r="A201" s="1">
         <v>801100302</v>
       </c>
@@ -3884,10 +4098,10 @@
         <v>1</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
       <c r="A202" s="1">
         <v>801100303</v>
       </c>
@@ -3898,10 +4112,10 @@
         <v>1</v>
       </c>
       <c r="D202" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
       <c r="A203" s="1">
         <v>801200101</v>
       </c>
@@ -3912,10 +4126,10 @@
         <v>1</v>
       </c>
       <c r="D203" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
       <c r="A204" s="1">
         <v>801200102</v>
       </c>
@@ -3926,10 +4140,10 @@
         <v>1</v>
       </c>
       <c r="D204" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
       <c r="A205" s="1">
         <v>801200103</v>
       </c>
@@ -3940,10 +4154,10 @@
         <v>1</v>
       </c>
       <c r="D205" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
       <c r="A206" s="1">
         <v>801200201</v>
       </c>
@@ -3954,10 +4168,10 @@
         <v>1</v>
       </c>
       <c r="D206" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
       <c r="A207" s="1">
         <v>801200202</v>
       </c>
@@ -3968,10 +4182,10 @@
         <v>1</v>
       </c>
       <c r="D207" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
       <c r="A208" s="1">
         <v>801200203</v>
       </c>
@@ -3982,10 +4196,10 @@
         <v>1</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
       <c r="A209" s="1">
         <v>700010101</v>
       </c>
@@ -3996,10 +4210,10 @@
         <v>1</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
       <c r="A210" s="1">
         <v>700010102</v>
       </c>
@@ -4010,10 +4224,10 @@
         <v>1</v>
       </c>
       <c r="D210" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
       <c r="A211" s="1">
         <v>700010112</v>
       </c>
@@ -4024,10 +4238,10 @@
         <v>1</v>
       </c>
       <c r="D211" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
       <c r="A212" s="1">
         <v>700010122</v>
       </c>
@@ -4038,10 +4252,10 @@
         <v>1</v>
       </c>
       <c r="D212" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
       <c r="A213" s="1">
         <v>700010132</v>
       </c>
@@ -4052,10 +4266,10 @@
         <v>1</v>
       </c>
       <c r="D213" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
       <c r="A214" s="1">
         <v>700010103</v>
       </c>
@@ -4066,10 +4280,10 @@
         <v>1</v>
       </c>
       <c r="D214" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
       <c r="A215" s="1">
         <v>700010104</v>
       </c>
@@ -4080,10 +4294,10 @@
         <v>1</v>
       </c>
       <c r="D215" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
       <c r="A216" s="1">
         <v>700010105</v>
       </c>
@@ -4094,10 +4308,10 @@
         <v>1</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
       <c r="A217" s="1">
         <v>700010106</v>
       </c>
@@ -4108,10 +4322,10 @@
         <v>1</v>
       </c>
       <c r="D217" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
       <c r="A218" s="1">
         <v>700010107</v>
       </c>
@@ -4122,24 +4336,24 @@
         <v>1</v>
       </c>
       <c r="D218" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
       <c r="A219" s="1">
         <v>700010108</v>
       </c>
-      <c r="B219" s="6" t="s">
-        <v>14</v>
+      <c r="B219" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="C219" s="1">
         <v>2</v>
       </c>
       <c r="D219" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
       <c r="A220" s="1">
         <v>700100101</v>
       </c>
@@ -4150,10 +4364,10 @@
         <v>1</v>
       </c>
       <c r="D220" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
       <c r="A221" s="1">
         <v>700100102</v>
       </c>
@@ -4164,10 +4378,10 @@
         <v>1</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
       <c r="A222" s="1">
         <v>700100112</v>
       </c>
@@ -4178,10 +4392,10 @@
         <v>1</v>
       </c>
       <c r="D222" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
       <c r="A223" s="1">
         <v>700100122</v>
       </c>
@@ -4192,10 +4406,10 @@
         <v>1</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
       <c r="A224" s="1">
         <v>700100132</v>
       </c>
@@ -4206,10 +4420,10 @@
         <v>1</v>
       </c>
       <c r="D224" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
       <c r="A225" s="1">
         <v>700100103</v>
       </c>
@@ -4220,10 +4434,10 @@
         <v>1</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
       <c r="A226" s="1">
         <v>700100104</v>
       </c>
@@ -4234,10 +4448,10 @@
         <v>1</v>
       </c>
       <c r="D226" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
       <c r="A227" s="1">
         <v>700100105</v>
       </c>
@@ -4248,10 +4462,10 @@
         <v>1</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
       <c r="A228" s="1">
         <v>700100106</v>
       </c>
@@ -4262,10 +4476,10 @@
         <v>1</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
       <c r="A229" s="1">
         <v>700100107</v>
       </c>
@@ -4276,24 +4490,24 @@
         <v>1</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
       <c r="A230" s="1">
         <v>700100108</v>
       </c>
-      <c r="B230" s="6" t="s">
-        <v>15</v>
+      <c r="B230" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="C230" s="1">
         <v>2</v>
       </c>
       <c r="D230" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
       <c r="A231" s="1">
         <v>700200101</v>
       </c>
@@ -4304,10 +4518,10 @@
         <v>1</v>
       </c>
       <c r="D231" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
       <c r="A232" s="1">
         <v>700200102</v>
       </c>
@@ -4318,10 +4532,10 @@
         <v>1</v>
       </c>
       <c r="D232" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
       <c r="A233" s="1">
         <v>700200112</v>
       </c>
@@ -4332,10 +4546,10 @@
         <v>1</v>
       </c>
       <c r="D233" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
       <c r="A234" s="1">
         <v>700200122</v>
       </c>
@@ -4346,10 +4560,10 @@
         <v>1</v>
       </c>
       <c r="D234" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
       <c r="A235" s="1">
         <v>700200132</v>
       </c>
@@ -4360,10 +4574,10 @@
         <v>1</v>
       </c>
       <c r="D235" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.15">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
       <c r="A236" s="1">
         <v>700200103</v>
       </c>
@@ -4374,10 +4588,10 @@
         <v>1</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
       <c r="A237" s="1">
         <v>700200104</v>
       </c>
@@ -4388,10 +4602,10 @@
         <v>1</v>
       </c>
       <c r="D237" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
       <c r="A238" s="1">
         <v>700200105</v>
       </c>
@@ -4402,10 +4616,10 @@
         <v>1</v>
       </c>
       <c r="D238" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
       <c r="A239" s="1">
         <v>700200106</v>
       </c>
@@ -4416,10 +4630,10 @@
         <v>1</v>
       </c>
       <c r="D239" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
       <c r="A240" s="1">
         <v>700200107</v>
       </c>
@@ -4430,24 +4644,24 @@
         <v>1</v>
       </c>
       <c r="D240" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
       <c r="A241" s="1">
         <v>700200108</v>
       </c>
-      <c r="B241" s="6" t="s">
-        <v>16</v>
+      <c r="B241" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="C241" s="1">
         <v>2</v>
       </c>
       <c r="D241" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
       <c r="A242" s="1">
         <v>700400002</v>
       </c>
@@ -4458,10 +4672,10 @@
         <v>1</v>
       </c>
       <c r="D242" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
       <c r="A243" s="1">
         <v>700400003</v>
       </c>
@@ -4472,10 +4686,10 @@
         <v>1</v>
       </c>
       <c r="D243" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
       <c r="A244" s="1">
         <v>700400004</v>
       </c>
@@ -4486,10 +4700,10 @@
         <v>1</v>
       </c>
       <c r="D244" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
       <c r="A245" s="1">
         <v>700400102</v>
       </c>
@@ -4500,10 +4714,10 @@
         <v>1</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
       <c r="A246" s="1">
         <v>700400103</v>
       </c>
@@ -4514,10 +4728,10 @@
         <v>1</v>
       </c>
       <c r="D246" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
       <c r="A247" s="1">
         <v>700400104</v>
       </c>
@@ -4528,10 +4742,10 @@
         <v>1</v>
       </c>
       <c r="D247" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
       <c r="A248" s="1">
         <v>600100101</v>
       </c>
@@ -4542,16 +4756,16 @@
         <v>1</v>
       </c>
       <c r="D248" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E248" s="7">
+        <v>17</v>
+      </c>
+      <c r="E248" s="2">
         <v>600200101</v>
       </c>
-      <c r="F248" s="7">
+      <c r="F248" s="2">
         <v>6002</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:4">
       <c r="A249" s="1">
         <v>600100102</v>
       </c>
@@ -4562,10 +4776,10 @@
         <v>1</v>
       </c>
       <c r="D249" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
       <c r="A250" s="1">
         <v>600100103</v>
       </c>
@@ -4576,38 +4790,38 @@
         <v>1</v>
       </c>
       <c r="D250" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
       <c r="A251" s="1">
         <v>600100201</v>
       </c>
-      <c r="B251" s="6" t="s">
-        <v>22</v>
+      <c r="B251" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="C251" s="1">
         <v>1</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
       <c r="A252" s="1">
         <v>600100202</v>
       </c>
-      <c r="B252" s="6" t="s">
-        <v>22</v>
+      <c r="B252" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="C252" s="1">
         <v>1</v>
       </c>
       <c r="D252" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
       <c r="A253" s="1">
         <v>600100203</v>
       </c>
@@ -4618,10 +4832,10 @@
         <v>1</v>
       </c>
       <c r="D253" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
       <c r="A254" s="1">
         <v>600100301</v>
       </c>
@@ -4632,10 +4846,10 @@
         <v>1</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
       <c r="A255" s="1">
         <v>600100302</v>
       </c>
@@ -4646,10 +4860,10 @@
         <v>1</v>
       </c>
       <c r="D255" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
       <c r="A256" s="1">
         <v>600100303</v>
       </c>
@@ -4660,38 +4874,38 @@
         <v>1</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
       <c r="A257" s="1">
         <v>600100401</v>
       </c>
-      <c r="B257" s="6" t="s">
-        <v>62</v>
+      <c r="B257" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="C257" s="1">
         <v>1</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
       <c r="A258" s="1">
         <v>600100501</v>
       </c>
-      <c r="B258" s="6" t="s">
-        <v>26</v>
+      <c r="B258" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="C258" s="1">
         <v>1</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.15">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" s="1">
         <v>600200101</v>
       </c>
@@ -4702,16 +4916,16 @@
         <v>1</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E259" s="7">
+        <v>17</v>
+      </c>
+      <c r="E259" s="2">
         <v>600100101</v>
       </c>
-      <c r="F259" s="7">
+      <c r="F259" s="2">
         <v>6001</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:4">
       <c r="A260" s="1">
         <v>600200102</v>
       </c>
@@ -4722,10 +4936,10 @@
         <v>1</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
       <c r="A261" s="1">
         <v>600200112</v>
       </c>
@@ -4736,10 +4950,10 @@
         <v>1</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
       <c r="A262" s="1">
         <v>600200103</v>
       </c>
@@ -4750,10 +4964,10 @@
         <v>1</v>
       </c>
       <c r="D262" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
       <c r="A263" s="1">
         <v>600200201</v>
       </c>
@@ -4764,10 +4978,10 @@
         <v>1</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
       <c r="A264" s="1">
         <v>600200202</v>
       </c>
@@ -4778,10 +4992,10 @@
         <v>1</v>
       </c>
       <c r="D264" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
       <c r="A265" s="1">
         <v>600200203</v>
       </c>
@@ -4792,10 +5006,10 @@
         <v>1</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
       <c r="A266" s="1">
         <v>600200301</v>
       </c>
@@ -4806,10 +5020,10 @@
         <v>1</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.15">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
       <c r="A267" s="1">
         <v>600200302</v>
       </c>
@@ -4820,10 +5034,10 @@
         <v>1</v>
       </c>
       <c r="D267" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.15">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
       <c r="A268" s="1">
         <v>600200303</v>
       </c>
@@ -4834,38 +5048,38 @@
         <v>1</v>
       </c>
       <c r="D268" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.15">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
       <c r="A269" s="1">
         <v>600200401</v>
       </c>
-      <c r="B269" s="6" t="s">
-        <v>30</v>
+      <c r="B269" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C269" s="1">
         <v>1</v>
       </c>
       <c r="D269" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
       <c r="A270" s="1">
         <v>600200501</v>
       </c>
-      <c r="B270" s="6" t="s">
-        <v>31</v>
+      <c r="B270" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="C270" s="1">
         <v>1</v>
       </c>
       <c r="D270" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.15">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271" s="1">
         <v>600300101</v>
       </c>
@@ -4876,16 +5090,16 @@
         <v>1</v>
       </c>
       <c r="D271" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E271" s="7">
+        <v>17</v>
+      </c>
+      <c r="E271" s="2">
         <v>600400101</v>
       </c>
-      <c r="F271" s="7">
+      <c r="F271" s="2">
         <v>6004</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:4">
       <c r="A272" s="1">
         <v>600300102</v>
       </c>
@@ -4896,10 +5110,10 @@
         <v>1</v>
       </c>
       <c r="D272" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
       <c r="A273" s="1">
         <v>600300103</v>
       </c>
@@ -4910,38 +5124,38 @@
         <v>1</v>
       </c>
       <c r="D273" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
       <c r="A274" s="1">
         <v>600300201</v>
       </c>
-      <c r="B274" s="6" t="s">
-        <v>32</v>
+      <c r="B274" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="C274" s="1">
         <v>1</v>
       </c>
       <c r="D274" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
       <c r="A275" s="1">
         <v>600300202</v>
       </c>
-      <c r="B275" s="6" t="s">
-        <v>32</v>
+      <c r="B275" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="C275" s="1">
         <v>1</v>
       </c>
       <c r="D275" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
       <c r="A276" s="1">
         <v>600300203</v>
       </c>
@@ -4952,10 +5166,10 @@
         <v>1</v>
       </c>
       <c r="D276" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
       <c r="A277" s="1">
         <v>600300301</v>
       </c>
@@ -4966,10 +5180,10 @@
         <v>1</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
       <c r="A278" s="1">
         <v>600300302</v>
       </c>
@@ -4980,10 +5194,10 @@
         <v>1</v>
       </c>
       <c r="D278" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
       <c r="A279" s="1">
         <v>600300303</v>
       </c>
@@ -4994,38 +5208,38 @@
         <v>1</v>
       </c>
       <c r="D279" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
       <c r="A280" s="1">
         <v>600300401</v>
       </c>
-      <c r="B280" s="6" t="s">
-        <v>63</v>
+      <c r="B280" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="C280" s="1">
         <v>1</v>
       </c>
       <c r="D280" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
       <c r="A281" s="1">
         <v>600300501</v>
       </c>
-      <c r="B281" s="6" t="s">
-        <v>35</v>
+      <c r="B281" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="C281" s="1">
         <v>1</v>
       </c>
       <c r="D281" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
       <c r="A282" s="1">
         <v>600400101</v>
       </c>
@@ -5036,16 +5250,16 @@
         <v>1</v>
       </c>
       <c r="D282" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E282" s="7">
+        <v>17</v>
+      </c>
+      <c r="E282" s="2">
         <v>600300101</v>
       </c>
-      <c r="F282" s="7">
+      <c r="F282" s="2">
         <v>6003</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:4">
       <c r="A283" s="1">
         <v>600400102</v>
       </c>
@@ -5056,10 +5270,10 @@
         <v>1</v>
       </c>
       <c r="D283" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
       <c r="A284" s="1">
         <v>600400112</v>
       </c>
@@ -5070,10 +5284,10 @@
         <v>1</v>
       </c>
       <c r="D284" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
       <c r="A285" s="1">
         <v>600400103</v>
       </c>
@@ -5084,10 +5298,10 @@
         <v>1</v>
       </c>
       <c r="D285" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
       <c r="A286" s="1">
         <v>600400201</v>
       </c>
@@ -5098,10 +5312,10 @@
         <v>1</v>
       </c>
       <c r="D286" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
       <c r="A287" s="1">
         <v>600400202</v>
       </c>
@@ -5112,10 +5326,10 @@
         <v>1</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
       <c r="A288" s="1">
         <v>600400203</v>
       </c>
@@ -5126,10 +5340,10 @@
         <v>1</v>
       </c>
       <c r="D288" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
       <c r="A289" s="1">
         <v>600400301</v>
       </c>
@@ -5140,10 +5354,10 @@
         <v>1</v>
       </c>
       <c r="D289" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
       <c r="A290" s="1">
         <v>600400302</v>
       </c>
@@ -5154,10 +5368,10 @@
         <v>1</v>
       </c>
       <c r="D290" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
       <c r="A291" s="1">
         <v>600400303</v>
       </c>
@@ -5168,38 +5382,38 @@
         <v>1</v>
       </c>
       <c r="D291" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
       <c r="A292" s="1">
         <v>600400401</v>
       </c>
-      <c r="B292" s="6" t="s">
-        <v>38</v>
+      <c r="B292" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="C292" s="1">
         <v>1</v>
       </c>
       <c r="D292" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.15">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
       <c r="A293" s="1">
         <v>600400501</v>
       </c>
-      <c r="B293" s="6" t="s">
-        <v>40</v>
+      <c r="B293" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="C293" s="1">
         <v>1</v>
       </c>
       <c r="D293" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.15">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
       <c r="A294" s="1">
         <v>600500101</v>
       </c>
@@ -5210,16 +5424,16 @@
         <v>1</v>
       </c>
       <c r="D294" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E294" s="7">
+        <v>17</v>
+      </c>
+      <c r="E294" s="2">
         <v>600600101</v>
       </c>
-      <c r="F294" s="7">
+      <c r="F294" s="2">
         <v>6006</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:4">
       <c r="A295" s="1">
         <v>600500102</v>
       </c>
@@ -5230,10 +5444,10 @@
         <v>1</v>
       </c>
       <c r="D295" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
       <c r="A296" s="1">
         <v>600500103</v>
       </c>
@@ -5244,38 +5458,38 @@
         <v>1</v>
       </c>
       <c r="D296" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
       <c r="A297" s="1">
         <v>600500201</v>
       </c>
-      <c r="B297" s="6" t="s">
-        <v>47</v>
+      <c r="B297" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="C297" s="1">
         <v>1</v>
       </c>
       <c r="D297" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
       <c r="A298" s="1">
         <v>600500202</v>
       </c>
-      <c r="B298" s="6" t="s">
-        <v>47</v>
+      <c r="B298" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="C298" s="1">
         <v>1</v>
       </c>
       <c r="D298" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
       <c r="A299" s="1">
         <v>600500203</v>
       </c>
@@ -5286,10 +5500,10 @@
         <v>1</v>
       </c>
       <c r="D299" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
       <c r="A300" s="1">
         <v>600500301</v>
       </c>
@@ -5300,10 +5514,10 @@
         <v>1</v>
       </c>
       <c r="D300" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
       <c r="A301" s="1">
         <v>600500302</v>
       </c>
@@ -5314,10 +5528,10 @@
         <v>1</v>
       </c>
       <c r="D301" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
       <c r="A302" s="1">
         <v>600500303</v>
       </c>
@@ -5328,38 +5542,38 @@
         <v>1</v>
       </c>
       <c r="D302" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
       <c r="A303" s="1">
         <v>600500401</v>
       </c>
-      <c r="B303" s="6" t="s">
-        <v>64</v>
+      <c r="B303" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="C303" s="1">
         <v>1</v>
       </c>
       <c r="D303" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
       <c r="A304" s="1">
         <v>600500501</v>
       </c>
-      <c r="B304" s="6" t="s">
-        <v>50</v>
+      <c r="B304" s="9" t="s">
+        <v>52</v>
       </c>
       <c r="C304" s="1">
         <v>1</v>
       </c>
       <c r="D304" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.15">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
       <c r="A305" s="1">
         <v>600600101</v>
       </c>
@@ -5370,16 +5584,16 @@
         <v>1</v>
       </c>
       <c r="D305" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E305" s="7">
+        <v>17</v>
+      </c>
+      <c r="E305" s="2">
         <v>600500101</v>
       </c>
-      <c r="F305" s="7">
+      <c r="F305" s="2">
         <v>6005</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:4">
       <c r="A306" s="1">
         <v>600600102</v>
       </c>
@@ -5390,10 +5604,10 @@
         <v>1</v>
       </c>
       <c r="D306" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
       <c r="A307" s="1">
         <v>600600112</v>
       </c>
@@ -5404,10 +5618,10 @@
         <v>1</v>
       </c>
       <c r="D307" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
       <c r="A308" s="1">
         <v>600600103</v>
       </c>
@@ -5418,10 +5632,10 @@
         <v>1</v>
       </c>
       <c r="D308" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
       <c r="A309" s="1">
         <v>600600201</v>
       </c>
@@ -5432,10 +5646,10 @@
         <v>1</v>
       </c>
       <c r="D309" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
       <c r="A310" s="1">
         <v>600600202</v>
       </c>
@@ -5446,10 +5660,10 @@
         <v>1</v>
       </c>
       <c r="D310" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
       <c r="A311" s="1">
         <v>600600203</v>
       </c>
@@ -5460,10 +5674,10 @@
         <v>1</v>
       </c>
       <c r="D311" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
       <c r="A312" s="1">
         <v>600600301</v>
       </c>
@@ -5474,10 +5688,10 @@
         <v>1</v>
       </c>
       <c r="D312" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
       <c r="A313" s="1">
         <v>600600302</v>
       </c>
@@ -5488,10 +5702,10 @@
         <v>1</v>
       </c>
       <c r="D313" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
       <c r="A314" s="1">
         <v>600600303</v>
       </c>
@@ -5502,38 +5716,38 @@
         <v>1</v>
       </c>
       <c r="D314" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
       <c r="A315" s="1">
         <v>600600401</v>
       </c>
-      <c r="B315" s="6" t="s">
-        <v>43</v>
+      <c r="B315" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="C315" s="1">
         <v>1</v>
       </c>
       <c r="D315" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.15">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
       <c r="A316" s="1">
         <v>600600501</v>
       </c>
-      <c r="B316" s="6" t="s">
-        <v>45</v>
+      <c r="B316" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="C316" s="1">
         <v>1</v>
       </c>
       <c r="D316" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.15">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
       <c r="A317" s="1">
         <v>600700101</v>
       </c>
@@ -5544,16 +5758,16 @@
         <v>1</v>
       </c>
       <c r="D317" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E317" s="7">
+        <v>17</v>
+      </c>
+      <c r="E317" s="2">
         <v>600800101</v>
       </c>
-      <c r="F317" s="7">
+      <c r="F317" s="2">
         <v>6008</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:4">
       <c r="A318" s="1">
         <v>600700102</v>
       </c>
@@ -5564,10 +5778,10 @@
         <v>1</v>
       </c>
       <c r="D318" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
       <c r="A319" s="1">
         <v>600700103</v>
       </c>
@@ -5578,38 +5792,38 @@
         <v>1</v>
       </c>
       <c r="D319" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
       <c r="A320" s="1">
         <v>600700201</v>
       </c>
-      <c r="B320" s="6" t="s">
-        <v>52</v>
+      <c r="B320" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="C320" s="1">
         <v>1</v>
       </c>
       <c r="D320" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
       <c r="A321" s="1">
         <v>600700202</v>
       </c>
-      <c r="B321" s="6" t="s">
-        <v>52</v>
+      <c r="B321" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="C321" s="1">
         <v>1</v>
       </c>
       <c r="D321" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
       <c r="A322" s="1">
         <v>600700203</v>
       </c>
@@ -5620,10 +5834,10 @@
         <v>1</v>
       </c>
       <c r="D322" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
       <c r="A323" s="1">
         <v>600700301</v>
       </c>
@@ -5634,10 +5848,10 @@
         <v>1</v>
       </c>
       <c r="D323" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
       <c r="A324" s="1">
         <v>600700302</v>
       </c>
@@ -5648,10 +5862,10 @@
         <v>1</v>
       </c>
       <c r="D324" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
       <c r="A325" s="1">
         <v>600700303</v>
       </c>
@@ -5662,38 +5876,38 @@
         <v>1</v>
       </c>
       <c r="D325" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
       <c r="A326" s="1">
         <v>600700401</v>
       </c>
-      <c r="B326" s="6" t="s">
-        <v>65</v>
+      <c r="B326" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="C326" s="1">
         <v>1</v>
       </c>
       <c r="D326" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.15">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
       <c r="A327" s="1">
         <v>600700501</v>
       </c>
-      <c r="B327" s="6" t="s">
-        <v>55</v>
+      <c r="B327" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="C327" s="1">
         <v>1</v>
       </c>
       <c r="D327" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.15">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
       <c r="A328" s="1">
         <v>600800101</v>
       </c>
@@ -5704,16 +5918,16 @@
         <v>1</v>
       </c>
       <c r="D328" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E328" s="7">
+        <v>17</v>
+      </c>
+      <c r="E328" s="2">
         <v>600700101</v>
       </c>
-      <c r="F328" s="7">
+      <c r="F328" s="2">
         <v>6007</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:4">
       <c r="A329" s="1">
         <v>600800102</v>
       </c>
@@ -5724,10 +5938,10 @@
         <v>1</v>
       </c>
       <c r="D329" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
       <c r="A330" s="1">
         <v>600800112</v>
       </c>
@@ -5738,10 +5952,10 @@
         <v>1</v>
       </c>
       <c r="D330" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
       <c r="A331" s="1">
         <v>600800103</v>
       </c>
@@ -5752,10 +5966,10 @@
         <v>1</v>
       </c>
       <c r="D331" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
       <c r="A332" s="1">
         <v>600800201</v>
       </c>
@@ -5766,10 +5980,10 @@
         <v>1</v>
       </c>
       <c r="D332" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
       <c r="A333" s="1">
         <v>600800202</v>
       </c>
@@ -5780,10 +5994,10 @@
         <v>1</v>
       </c>
       <c r="D333" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
       <c r="A334" s="1">
         <v>600800203</v>
       </c>
@@ -5794,10 +6008,10 @@
         <v>1</v>
       </c>
       <c r="D334" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
       <c r="A335" s="1">
         <v>600800301</v>
       </c>
@@ -5808,10 +6022,10 @@
         <v>1</v>
       </c>
       <c r="D335" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
       <c r="A336" s="1">
         <v>600800302</v>
       </c>
@@ -5822,10 +6036,10 @@
         <v>1</v>
       </c>
       <c r="D336" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
       <c r="A337" s="1">
         <v>600800303</v>
       </c>
@@ -5836,38 +6050,38 @@
         <v>1</v>
       </c>
       <c r="D337" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
       <c r="A338" s="1">
         <v>600800401</v>
       </c>
-      <c r="B338" s="6" t="s">
-        <v>58</v>
+      <c r="B338" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="C338" s="1">
         <v>1</v>
       </c>
       <c r="D338" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.15">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
       <c r="A339" s="1">
         <v>600800501</v>
       </c>
-      <c r="B339" s="6" t="s">
-        <v>60</v>
+      <c r="B339" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="C339" s="1">
         <v>1</v>
       </c>
       <c r="D339" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.15">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
       <c r="A340" s="1">
         <v>600900101</v>
       </c>
@@ -5878,10 +6092,10 @@
         <v>1</v>
       </c>
       <c r="D340" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
       <c r="A341" s="1">
         <v>600900102</v>
       </c>
@@ -5892,113 +6106,113 @@
         <v>1</v>
       </c>
       <c r="D341" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="33" priority="44"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="32" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="29" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="28" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B204:B205 B207:B208">
-    <cfRule type="duplicateValues" dxfId="27" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B211:B213">
-    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B222:B224">
-    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B233:B235">
-    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B242:B244">
-    <cfRule type="duplicateValues" dxfId="23" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="22" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B246:B247">
-    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
+  <conditionalFormatting sqref="E248">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B261">
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B265">
-    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E271">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="15" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B288">
-    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E294">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B299">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B307">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B341">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E248">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E271">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E294">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E317">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B322">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B325">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B330">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B334">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B341">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A$1:A$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B211:B213">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B222:B224">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B233:B235">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B242:B244">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B246:B247">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B204:B205 B207:B208">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73D2C6F-95EF-4B24-831C-065CA0769262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="12225"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_front_v8" sheetId="1" r:id="rId1"/>
@@ -245,14 +251,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,355 +264,26 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -646,253 +317,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -909,63 +338,345 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="34">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -981,6 +692,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1258,14 +972,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F341"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="33" style="1" customWidth="1"/>
@@ -1276,14 +990,14 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1303,7 +1017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1323,7 +1037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -1343,7 +1057,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1010201</v>
       </c>
@@ -1357,7 +1071,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>1010202</v>
       </c>
@@ -1371,7 +1085,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>1010203</v>
       </c>
@@ -1385,7 +1099,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>1010204</v>
       </c>
@@ -1399,7 +1113,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>1010501</v>
       </c>
@@ -1413,7 +1127,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>1010502</v>
       </c>
@@ -1427,7 +1141,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>1010503</v>
       </c>
@@ -1441,7 +1155,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>1010504</v>
       </c>
@@ -1455,7 +1169,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>1010701</v>
       </c>
@@ -1469,7 +1183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>1010702</v>
       </c>
@@ -1483,7 +1197,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>1010703</v>
       </c>
@@ -1497,7 +1211,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>1010704</v>
       </c>
@@ -1511,7 +1225,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>1010801</v>
       </c>
@@ -1525,7 +1239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>1010802</v>
       </c>
@@ -1539,7 +1253,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>1010803</v>
       </c>
@@ -1553,7 +1267,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>1010804</v>
       </c>
@@ -1567,7 +1281,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>1011001</v>
       </c>
@@ -1581,7 +1295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>1011002</v>
       </c>
@@ -1595,7 +1309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>1011003</v>
       </c>
@@ -1609,7 +1323,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>1011004</v>
       </c>
@@ -1623,7 +1337,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>1011101</v>
       </c>
@@ -1637,7 +1351,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>1011102</v>
       </c>
@@ -1651,7 +1365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>1011103</v>
       </c>
@@ -1665,7 +1379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>1011104</v>
       </c>
@@ -1679,7 +1393,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>1011201</v>
       </c>
@@ -1693,7 +1407,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>1011202</v>
       </c>
@@ -1707,7 +1421,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>1011203</v>
       </c>
@@ -1721,7 +1435,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>1011204</v>
       </c>
@@ -1735,7 +1449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>2010101</v>
       </c>
@@ -1749,7 +1463,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>2010102</v>
       </c>
@@ -1763,7 +1477,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>2010103</v>
       </c>
@@ -1777,7 +1491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>2010104</v>
       </c>
@@ -1791,7 +1505,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>2010301</v>
       </c>
@@ -1805,7 +1519,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>2010302</v>
       </c>
@@ -1819,7 +1533,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>2010303</v>
       </c>
@@ -1833,7 +1547,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>2010304</v>
       </c>
@@ -1847,7 +1561,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>2010401</v>
       </c>
@@ -1861,7 +1575,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>2010402</v>
       </c>
@@ -1875,7 +1589,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>2010403</v>
       </c>
@@ -1889,7 +1603,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>2010404</v>
       </c>
@@ -1903,7 +1617,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>3010101</v>
       </c>
@@ -1917,7 +1631,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>3010102</v>
       </c>
@@ -1931,7 +1645,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>3010103</v>
       </c>
@@ -1945,7 +1659,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>3010104</v>
       </c>
@@ -1959,7 +1673,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>3010301</v>
       </c>
@@ -1973,7 +1687,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>3010302</v>
       </c>
@@ -1987,7 +1701,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>3010303</v>
       </c>
@@ -2001,7 +1715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>3010304</v>
       </c>
@@ -2015,7 +1729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>3010401</v>
       </c>
@@ -2029,7 +1743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>3010402</v>
       </c>
@@ -2043,7 +1757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>3010403</v>
       </c>
@@ -2057,7 +1771,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>3010404</v>
       </c>
@@ -2071,7 +1785,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>4010101</v>
       </c>
@@ -2085,7 +1799,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>4010102</v>
       </c>
@@ -2099,7 +1813,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>4010103</v>
       </c>
@@ -2113,7 +1827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>4010104</v>
       </c>
@@ -2127,7 +1841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>4010301</v>
       </c>
@@ -2141,7 +1855,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>4010302</v>
       </c>
@@ -2155,7 +1869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>4010303</v>
       </c>
@@ -2169,7 +1883,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>4010304</v>
       </c>
@@ -2183,7 +1897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>4010401</v>
       </c>
@@ -2197,7 +1911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>4010402</v>
       </c>
@@ -2211,7 +1925,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>4010403</v>
       </c>
@@ -2225,7 +1939,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>4010404</v>
       </c>
@@ -2239,7 +1953,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>5010101</v>
       </c>
@@ -2253,7 +1967,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>5010102</v>
       </c>
@@ -2267,7 +1981,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>5010103</v>
       </c>
@@ -2281,7 +1995,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>5010104</v>
       </c>
@@ -2295,7 +2009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>5010301</v>
       </c>
@@ -2309,7 +2023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>5010302</v>
       </c>
@@ -2323,7 +2037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>5010303</v>
       </c>
@@ -2337,7 +2051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>5010304</v>
       </c>
@@ -2351,7 +2065,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>5010401</v>
       </c>
@@ -2365,7 +2079,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>5010402</v>
       </c>
@@ -2379,7 +2093,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>5010403</v>
       </c>
@@ -2393,7 +2107,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>5010404</v>
       </c>
@@ -2407,7 +2121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>9000101</v>
       </c>
@@ -2421,7 +2135,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>9000102</v>
       </c>
@@ -2435,7 +2149,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>9000103</v>
       </c>
@@ -2449,7 +2163,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>906010202</v>
       </c>
@@ -2463,7 +2177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>906010403</v>
       </c>
@@ -2477,7 +2191,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>20101</v>
       </c>
@@ -2491,7 +2205,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>30101</v>
       </c>
@@ -2505,7 +2219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>40101</v>
       </c>
@@ -2519,7 +2233,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>50101</v>
       </c>
@@ -2533,7 +2247,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>1010901</v>
       </c>
@@ -2547,7 +2261,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>10109011</v>
       </c>
@@ -2561,7 +2275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>10109012</v>
       </c>
@@ -2575,7 +2289,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>1010902</v>
       </c>
@@ -2589,7 +2303,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>1010903</v>
       </c>
@@ -2603,7 +2317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>1010904</v>
       </c>
@@ -2617,7 +2331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>1010905</v>
       </c>
@@ -2631,7 +2345,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>1010906</v>
       </c>
@@ -2645,7 +2359,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>1010907</v>
       </c>
@@ -2659,7 +2373,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>1010908</v>
       </c>
@@ -2673,7 +2387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>1010909</v>
       </c>
@@ -2687,7 +2401,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>1010910</v>
       </c>
@@ -2701,7 +2415,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>905010202</v>
       </c>
@@ -2715,7 +2429,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>905010302</v>
       </c>
@@ -2729,7 +2443,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>905010403</v>
       </c>
@@ -2743,7 +2457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>905010503</v>
       </c>
@@ -2757,7 +2471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>905010604</v>
       </c>
@@ -2771,7 +2485,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>905010704</v>
       </c>
@@ -2785,7 +2499,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>905010805</v>
       </c>
@@ -2799,7 +2513,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>901010202</v>
       </c>
@@ -2813,7 +2527,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>901010302</v>
       </c>
@@ -2827,7 +2541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>901010403</v>
       </c>
@@ -2841,7 +2555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>901010503</v>
       </c>
@@ -2855,7 +2569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>901010604</v>
       </c>
@@ -2869,7 +2583,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>901010704</v>
       </c>
@@ -2883,7 +2597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>901010805</v>
       </c>
@@ -2897,7 +2611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>902010202</v>
       </c>
@@ -2911,7 +2625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>902010302</v>
       </c>
@@ -2925,7 +2639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>902010403</v>
       </c>
@@ -2939,7 +2653,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>902010503</v>
       </c>
@@ -2953,7 +2667,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>902010604</v>
       </c>
@@ -2967,7 +2681,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>902010704</v>
       </c>
@@ -2981,7 +2695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>902010805</v>
       </c>
@@ -2995,7 +2709,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>903010202</v>
       </c>
@@ -3009,7 +2723,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>903010302</v>
       </c>
@@ -3023,7 +2737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>903010403</v>
       </c>
@@ -3037,7 +2751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>903010503</v>
       </c>
@@ -3051,7 +2765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>903010604</v>
       </c>
@@ -3065,7 +2779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>903010704</v>
       </c>
@@ -3079,7 +2793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>903010805</v>
       </c>
@@ -3093,7 +2807,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>900010202</v>
       </c>
@@ -3107,7 +2821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>900010302</v>
       </c>
@@ -3121,7 +2835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>900010403</v>
       </c>
@@ -3135,7 +2849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>900010503</v>
       </c>
@@ -3149,7 +2863,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>900010604</v>
       </c>
@@ -3163,7 +2877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>900010704</v>
       </c>
@@ -3177,7 +2891,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>900010805</v>
       </c>
@@ -3191,7 +2905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>900020202</v>
       </c>
@@ -3205,7 +2919,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>900020302</v>
       </c>
@@ -3219,7 +2933,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>900020403</v>
       </c>
@@ -3233,7 +2947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>900020503</v>
       </c>
@@ -3247,7 +2961,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>900020604</v>
       </c>
@@ -3261,7 +2975,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>900020704</v>
       </c>
@@ -3275,7 +2989,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>900020805</v>
       </c>
@@ -3289,7 +3003,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>901020202</v>
       </c>
@@ -3303,7 +3017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>901020302</v>
       </c>
@@ -3317,7 +3031,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>901020403</v>
       </c>
@@ -3331,7 +3045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>901020503</v>
       </c>
@@ -3345,7 +3059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>901020604</v>
       </c>
@@ -3359,7 +3073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>901020704</v>
       </c>
@@ -3373,7 +3087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>901020805</v>
       </c>
@@ -3387,7 +3101,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>902020202</v>
       </c>
@@ -3401,7 +3115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>902020302</v>
       </c>
@@ -3415,7 +3129,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>902020403</v>
       </c>
@@ -3429,7 +3143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>902020503</v>
       </c>
@@ -3443,7 +3157,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>902020604</v>
       </c>
@@ -3457,7 +3171,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>902020704</v>
       </c>
@@ -3471,7 +3185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>902020805</v>
       </c>
@@ -3485,7 +3199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>903020202</v>
       </c>
@@ -3499,7 +3213,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>903020302</v>
       </c>
@@ -3513,7 +3227,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>903020403</v>
       </c>
@@ -3527,7 +3241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>903020503</v>
       </c>
@@ -3541,7 +3255,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>903020604</v>
       </c>
@@ -3555,7 +3269,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>903020704</v>
       </c>
@@ -3569,7 +3283,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>903020805</v>
       </c>
@@ -3583,7 +3297,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
         <v>800010101</v>
       </c>
@@ -3597,7 +3311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
         <v>800010102</v>
       </c>
@@ -3611,7 +3325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
         <v>800010201</v>
       </c>
@@ -3625,7 +3339,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:4">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
         <v>800010202</v>
       </c>
@@ -3639,7 +3353,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:4">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
         <v>800010301</v>
       </c>
@@ -3653,7 +3367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:4">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
         <v>800010302</v>
       </c>
@@ -3667,7 +3381,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:4">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
         <v>800030101</v>
       </c>
@@ -3681,7 +3395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:4">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
         <v>800030102</v>
       </c>
@@ -3695,7 +3409,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
         <v>800030201</v>
       </c>
@@ -3709,7 +3423,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:4">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
         <v>800030202</v>
       </c>
@@ -3723,7 +3437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
         <v>800110101</v>
       </c>
@@ -3737,7 +3451,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:4">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
         <v>800110102</v>
       </c>
@@ -3751,7 +3465,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:4">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
         <v>800110201</v>
       </c>
@@ -3765,7 +3479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:4">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
         <v>800110202</v>
       </c>
@@ -3779,7 +3493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:4">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
         <v>800110301</v>
       </c>
@@ -3793,7 +3507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:4">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
         <v>800110302</v>
       </c>
@@ -3807,7 +3521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:4">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
         <v>800130101</v>
       </c>
@@ -3821,7 +3535,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:4">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
         <v>800130102</v>
       </c>
@@ -3835,7 +3549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:4">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
         <v>800130201</v>
       </c>
@@ -3849,7 +3563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:4">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
         <v>800130202</v>
       </c>
@@ -3863,7 +3577,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:4">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
         <v>800210101</v>
       </c>
@@ -3877,7 +3591,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:4">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
         <v>800210102</v>
       </c>
@@ -3891,7 +3605,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:4">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
         <v>800210201</v>
       </c>
@@ -3905,7 +3619,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:4">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
         <v>800210202</v>
       </c>
@@ -3919,7 +3633,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:4">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
         <v>800210301</v>
       </c>
@@ -3933,7 +3647,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:4">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
         <v>800210302</v>
       </c>
@@ -3947,7 +3661,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:4">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
         <v>800230101</v>
       </c>
@@ -3961,7 +3675,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:4">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
         <v>800230102</v>
       </c>
@@ -3975,7 +3689,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:4">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
         <v>800230201</v>
       </c>
@@ -3989,7 +3703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:4">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
         <v>800230202</v>
       </c>
@@ -4003,7 +3717,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
         <v>801100102</v>
       </c>
@@ -4017,7 +3731,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:4">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
         <v>801100103</v>
       </c>
@@ -4031,7 +3745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:4">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
         <v>801100201</v>
       </c>
@@ -4045,7 +3759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:4">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
         <v>801100202</v>
       </c>
@@ -4059,7 +3773,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:4">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
         <v>801100203</v>
       </c>
@@ -4073,7 +3787,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:4">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
         <v>801100301</v>
       </c>
@@ -4087,7 +3801,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:4">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
         <v>801100302</v>
       </c>
@@ -4101,7 +3815,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:4">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
         <v>801100303</v>
       </c>
@@ -4115,7 +3829,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:4">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
         <v>801200101</v>
       </c>
@@ -4129,7 +3843,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:4">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
         <v>801200102</v>
       </c>
@@ -4143,7 +3857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:4">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
         <v>801200103</v>
       </c>
@@ -4157,7 +3871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:4">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
         <v>801200201</v>
       </c>
@@ -4171,7 +3885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:4">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
         <v>801200202</v>
       </c>
@@ -4185,7 +3899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:4">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
         <v>801200203</v>
       </c>
@@ -4199,7 +3913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:4">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
         <v>700010101</v>
       </c>
@@ -4213,7 +3927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:4">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
         <v>700010102</v>
       </c>
@@ -4227,7 +3941,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:4">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
         <v>700010112</v>
       </c>
@@ -4241,7 +3955,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:4">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
         <v>700010122</v>
       </c>
@@ -4255,7 +3969,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:4">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
         <v>700010132</v>
       </c>
@@ -4269,7 +3983,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:4">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
         <v>700010103</v>
       </c>
@@ -4283,7 +3997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:4">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
         <v>700010104</v>
       </c>
@@ -4297,7 +4011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:4">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
         <v>700010105</v>
       </c>
@@ -4311,7 +4025,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:4">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
         <v>700010106</v>
       </c>
@@ -4325,7 +4039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:4">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
         <v>700010107</v>
       </c>
@@ -4339,7 +4053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:4">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
         <v>700010108</v>
       </c>
@@ -4353,7 +4067,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:4">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
         <v>700100101</v>
       </c>
@@ -4367,7 +4081,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:4">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
         <v>700100102</v>
       </c>
@@ -4381,7 +4095,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:4">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
         <v>700100112</v>
       </c>
@@ -4395,7 +4109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:4">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
         <v>700100122</v>
       </c>
@@ -4409,7 +4123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:4">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
         <v>700100132</v>
       </c>
@@ -4423,7 +4137,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:4">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
         <v>700100103</v>
       </c>
@@ -4437,7 +4151,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:4">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
         <v>700100104</v>
       </c>
@@ -4451,7 +4165,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:4">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
         <v>700100105</v>
       </c>
@@ -4465,7 +4179,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:4">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
         <v>700100106</v>
       </c>
@@ -4479,7 +4193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
         <v>700100107</v>
       </c>
@@ -4493,7 +4207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
         <v>700100108</v>
       </c>
@@ -4507,7 +4221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
         <v>700200101</v>
       </c>
@@ -4521,7 +4235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:4">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
         <v>700200102</v>
       </c>
@@ -4535,7 +4249,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:4">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
         <v>700200112</v>
       </c>
@@ -4549,7 +4263,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:4">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
         <v>700200122</v>
       </c>
@@ -4563,7 +4277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:4">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
         <v>700200132</v>
       </c>
@@ -4577,7 +4291,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="236" spans="1:4">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
         <v>700200103</v>
       </c>
@@ -4591,7 +4305,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:4">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
         <v>700200104</v>
       </c>
@@ -4605,7 +4319,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:4">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
         <v>700200105</v>
       </c>
@@ -4619,7 +4333,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:4">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
         <v>700200106</v>
       </c>
@@ -4633,7 +4347,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:4">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
         <v>700200107</v>
       </c>
@@ -4647,7 +4361,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
         <v>700200108</v>
       </c>
@@ -4661,7 +4375,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:4">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
         <v>700400002</v>
       </c>
@@ -4675,7 +4389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
         <v>700400003</v>
       </c>
@@ -4689,7 +4403,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:4">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
         <v>700400004</v>
       </c>
@@ -4703,7 +4417,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:4">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
         <v>700400102</v>
       </c>
@@ -4717,7 +4431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:4">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
         <v>700400103</v>
       </c>
@@ -4731,7 +4445,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="247" spans="1:4">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
         <v>700400104</v>
       </c>
@@ -4745,7 +4459,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
         <v>600100101</v>
       </c>
@@ -4765,7 +4479,7 @@
         <v>6002</v>
       </c>
     </row>
-    <row r="249" spans="1:4">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
         <v>600100102</v>
       </c>
@@ -4779,7 +4493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:4">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
         <v>600100103</v>
       </c>
@@ -4793,7 +4507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
         <v>600100201</v>
       </c>
@@ -4807,7 +4521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="252" spans="1:4">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
         <v>600100202</v>
       </c>
@@ -4821,7 +4535,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="253" spans="1:4">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
         <v>600100203</v>
       </c>
@@ -4835,7 +4549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="254" spans="1:4">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
         <v>600100301</v>
       </c>
@@ -4849,7 +4563,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="255" spans="1:4">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
         <v>600100302</v>
       </c>
@@ -4863,7 +4577,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="256" spans="1:4">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
         <v>600100303</v>
       </c>
@@ -4877,7 +4591,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="257" spans="1:4">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
         <v>600100401</v>
       </c>
@@ -4891,7 +4605,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="258" spans="1:4">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
         <v>600100501</v>
       </c>
@@ -4905,7 +4619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="259" spans="1:6">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
         <v>600200101</v>
       </c>
@@ -4925,7 +4639,7 @@
         <v>6001</v>
       </c>
     </row>
-    <row r="260" spans="1:4">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
         <v>600200102</v>
       </c>
@@ -4939,7 +4653,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="261" spans="1:4">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
         <v>600200112</v>
       </c>
@@ -4953,7 +4667,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" spans="1:4">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
         <v>600200103</v>
       </c>
@@ -4967,7 +4681,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:4">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
         <v>600200201</v>
       </c>
@@ -4981,7 +4695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:4">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
         <v>600200202</v>
       </c>
@@ -4995,7 +4709,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="265" spans="1:4">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
         <v>600200203</v>
       </c>
@@ -5009,7 +4723,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:4">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
         <v>600200301</v>
       </c>
@@ -5023,7 +4737,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="267" spans="1:4">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
         <v>600200302</v>
       </c>
@@ -5037,7 +4751,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="268" spans="1:4">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
         <v>600200303</v>
       </c>
@@ -5051,7 +4765,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="269" spans="1:4">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
         <v>600200401</v>
       </c>
@@ -5065,7 +4779,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="270" spans="1:4">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
         <v>600200501</v>
       </c>
@@ -5079,7 +4793,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="271" spans="1:6">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
         <v>600300101</v>
       </c>
@@ -5099,7 +4813,7 @@
         <v>6004</v>
       </c>
     </row>
-    <row r="272" spans="1:4">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
         <v>600300102</v>
       </c>
@@ -5113,7 +4827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="273" spans="1:4">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
         <v>600300103</v>
       </c>
@@ -5127,7 +4841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" spans="1:4">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
         <v>600300201</v>
       </c>
@@ -5141,7 +4855,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="275" spans="1:4">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
         <v>600300202</v>
       </c>
@@ -5155,7 +4869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="276" spans="1:4">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
         <v>600300203</v>
       </c>
@@ -5169,7 +4883,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="277" spans="1:4">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
         <v>600300301</v>
       </c>
@@ -5183,7 +4897,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="278" spans="1:4">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
         <v>600300302</v>
       </c>
@@ -5197,7 +4911,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="279" spans="1:4">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
         <v>600300303</v>
       </c>
@@ -5211,7 +4925,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="280" spans="1:4">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
         <v>600300401</v>
       </c>
@@ -5225,7 +4939,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="281" spans="1:4">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
         <v>600300501</v>
       </c>
@@ -5239,7 +4953,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="282" spans="1:6">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
         <v>600400101</v>
       </c>
@@ -5259,7 +4973,7 @@
         <v>6003</v>
       </c>
     </row>
-    <row r="283" spans="1:4">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
         <v>600400102</v>
       </c>
@@ -5273,7 +4987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="284" spans="1:4">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
         <v>600400112</v>
       </c>
@@ -5287,7 +5001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="285" spans="1:4">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
         <v>600400103</v>
       </c>
@@ -5301,7 +5015,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="286" spans="1:4">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
         <v>600400201</v>
       </c>
@@ -5315,7 +5029,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="287" spans="1:4">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
         <v>600400202</v>
       </c>
@@ -5329,7 +5043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="288" spans="1:4">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
         <v>600400203</v>
       </c>
@@ -5343,7 +5057,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="289" spans="1:4">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
         <v>600400301</v>
       </c>
@@ -5357,7 +5071,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="290" spans="1:4">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
         <v>600400302</v>
       </c>
@@ -5371,7 +5085,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="291" spans="1:4">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
         <v>600400303</v>
       </c>
@@ -5385,7 +5099,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="292" spans="1:4">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
         <v>600400401</v>
       </c>
@@ -5399,7 +5113,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="293" spans="1:4">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
         <v>600400501</v>
       </c>
@@ -5413,7 +5127,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="294" spans="1:6">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
         <v>600500101</v>
       </c>
@@ -5433,7 +5147,7 @@
         <v>6006</v>
       </c>
     </row>
-    <row r="295" spans="1:4">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
         <v>600500102</v>
       </c>
@@ -5447,7 +5161,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="296" spans="1:4">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
         <v>600500103</v>
       </c>
@@ -5461,7 +5175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="297" spans="1:4">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
         <v>600500201</v>
       </c>
@@ -5475,7 +5189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="298" spans="1:4">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
         <v>600500202</v>
       </c>
@@ -5489,7 +5203,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="299" spans="1:4">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
         <v>600500203</v>
       </c>
@@ -5503,7 +5217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="300" spans="1:4">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
         <v>600500301</v>
       </c>
@@ -5517,7 +5231,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="301" spans="1:4">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
         <v>600500302</v>
       </c>
@@ -5531,7 +5245,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="302" spans="1:4">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
         <v>600500303</v>
       </c>
@@ -5545,7 +5259,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="303" spans="1:4">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
         <v>600500401</v>
       </c>
@@ -5559,7 +5273,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="304" spans="1:4">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
         <v>600500501</v>
       </c>
@@ -5573,7 +5287,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="305" spans="1:6">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
         <v>600600101</v>
       </c>
@@ -5593,7 +5307,7 @@
         <v>6005</v>
       </c>
     </row>
-    <row r="306" spans="1:4">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
         <v>600600102</v>
       </c>
@@ -5607,7 +5321,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="307" spans="1:4">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
         <v>600600112</v>
       </c>
@@ -5621,7 +5335,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="308" spans="1:4">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
         <v>600600103</v>
       </c>
@@ -5635,7 +5349,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="309" spans="1:4">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
         <v>600600201</v>
       </c>
@@ -5649,7 +5363,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="310" spans="1:4">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
         <v>600600202</v>
       </c>
@@ -5663,7 +5377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="311" spans="1:4">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
         <v>600600203</v>
       </c>
@@ -5677,7 +5391,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="312" spans="1:4">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
         <v>600600301</v>
       </c>
@@ -5691,7 +5405,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="313" spans="1:4">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
         <v>600600302</v>
       </c>
@@ -5705,7 +5419,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="314" spans="1:4">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
         <v>600600303</v>
       </c>
@@ -5719,7 +5433,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="315" spans="1:4">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
         <v>600600401</v>
       </c>
@@ -5733,7 +5447,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="316" spans="1:4">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
         <v>600600501</v>
       </c>
@@ -5747,7 +5461,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="317" spans="1:6">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
         <v>600700101</v>
       </c>
@@ -5767,7 +5481,7 @@
         <v>6008</v>
       </c>
     </row>
-    <row r="318" spans="1:4">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
         <v>600700102</v>
       </c>
@@ -5781,7 +5495,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="319" spans="1:4">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
         <v>600700103</v>
       </c>
@@ -5795,7 +5509,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="320" spans="1:4">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
         <v>600700201</v>
       </c>
@@ -5809,7 +5523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="321" spans="1:4">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
         <v>600700202</v>
       </c>
@@ -5823,7 +5537,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="322" spans="1:4">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
         <v>600700203</v>
       </c>
@@ -5837,7 +5551,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="323" spans="1:4">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
         <v>600700301</v>
       </c>
@@ -5851,7 +5565,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="324" spans="1:4">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
         <v>600700302</v>
       </c>
@@ -5865,7 +5579,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="325" spans="1:4">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
         <v>600700303</v>
       </c>
@@ -5879,7 +5593,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="326" spans="1:4">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
         <v>600700401</v>
       </c>
@@ -5893,7 +5607,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="327" spans="1:4">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
         <v>600700501</v>
       </c>
@@ -5907,7 +5621,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="328" spans="1:6">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
         <v>600800101</v>
       </c>
@@ -5927,7 +5641,7 @@
         <v>6007</v>
       </c>
     </row>
-    <row r="329" spans="1:4">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
         <v>600800102</v>
       </c>
@@ -5941,7 +5655,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="330" spans="1:4">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
         <v>600800112</v>
       </c>
@@ -5955,7 +5669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="331" spans="1:4">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
         <v>600800103</v>
       </c>
@@ -5969,7 +5683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="332" spans="1:4">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
         <v>600800201</v>
       </c>
@@ -5983,7 +5697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="333" spans="1:4">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
         <v>600800202</v>
       </c>
@@ -5997,7 +5711,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="334" spans="1:4">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
         <v>600800203</v>
       </c>
@@ -6011,7 +5725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="335" spans="1:4">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
         <v>600800301</v>
       </c>
@@ -6025,7 +5739,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="336" spans="1:4">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
         <v>600800302</v>
       </c>
@@ -6039,7 +5753,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="337" spans="1:4">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
         <v>600800303</v>
       </c>
@@ -6053,7 +5767,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="338" spans="1:4">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
         <v>600800401</v>
       </c>
@@ -6067,7 +5781,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="339" spans="1:4">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
         <v>600800501</v>
       </c>
@@ -6081,7 +5795,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="340" spans="1:4">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
         <v>600900101</v>
       </c>
@@ -6095,12 +5809,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="341" spans="1:4">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
         <v>600900102</v>
       </c>
       <c r="B341" s="1">
-        <v>600900101</v>
+        <v>600900001</v>
       </c>
       <c r="C341" s="1">
         <v>1</v>
@@ -6110,109 +5824,106 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="33" priority="44"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B204:B205 B207:B208">
+    <cfRule type="duplicateValues" dxfId="27" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B211:B213">
+    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B222:B224">
+    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B233:B235">
+    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B242:B244">
+    <cfRule type="duplicateValues" dxfId="23" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B246:B247">
+    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B253">
+    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B256">
+    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B261">
+    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B265">
+    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B276">
+    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B279">
+    <cfRule type="duplicateValues" dxfId="15" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B284">
+    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B288">
+    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B299">
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B302">
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B307">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B311">
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B322">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B325">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B330">
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B334">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E248">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B261">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B265">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E271">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B288">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E294">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B299">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B307">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E317">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B341">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A$1:A$1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B211:B213">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B222:B224">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B233:B235">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B242:B244">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B246:B247">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B204:B205 B207:B208">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>